--- a/Archivos_Compartidos/Cursos RH/Copia de Listado para cursos normativos 2025.xlsx
+++ b/Archivos_Compartidos/Cursos RH/Copia de Listado para cursos normativos 2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://santandernet-my.sharepoint.com/personal/n854611_corp_santanderam_com/Documents/Documentos/GitHub/SAM_Santander/SAM_Santander/Archivos_Compartidos/Cursos RH/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SAMMX\Documents\GitHub\SAM_Santander\Archivos_Compartidos\Cursos RH\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{BC2ED754-AB4B-4DD7-966E-76DD954153BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CEB8F394-1A8B-4C4D-9F84-CCF5EE912074}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="12810" windowHeight="15135" xr2:uid="{FF6FD13D-7CB9-4391-90CB-CB63A01A4952}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{FF6FD13D-7CB9-4391-90CB-CB63A01A4952}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -754,12 +754,12 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="14" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1094,32 +1094,32 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AA6F91F3-8D57-4281-84D3-F5D3AFC92A1D}">
-  <dimension ref="B2:W93"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="B2:X93"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="3.140625" customWidth="1"/>
+    <col min="1" max="1" width="3.109375" customWidth="1"/>
     <col min="2" max="2" width="12" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="33.42578125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.140625" hidden="1" customWidth="1"/>
-    <col min="6" max="17" width="10.85546875" hidden="1" customWidth="1"/>
+    <col min="3" max="3" width="33.44140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.109375" hidden="1" customWidth="1"/>
+    <col min="6" max="17" width="10.88671875" hidden="1" customWidth="1"/>
     <col min="18" max="19" width="0" hidden="1" customWidth="1"/>
     <col min="20" max="20" width="18" hidden="1" customWidth="1"/>
     <col min="21" max="21" width="18" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:23" x14ac:dyDescent="0.25">
-      <c r="F2" s="5" t="s">
+    <row r="2" spans="2:24" x14ac:dyDescent="0.3">
+      <c r="F2" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="G2" s="5"/>
-      <c r="H2" s="5"/>
-      <c r="I2" s="5"/>
-      <c r="J2" s="5"/>
-      <c r="K2" s="5"/>
-      <c r="L2" s="5"/>
-      <c r="M2" s="5"/>
-    </row>
-    <row r="3" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="G2" s="8"/>
+      <c r="H2" s="8"/>
+      <c r="I2" s="8"/>
+      <c r="J2" s="8"/>
+      <c r="K2" s="8"/>
+      <c r="L2" s="8"/>
+      <c r="M2" s="8"/>
+    </row>
+    <row r="3" spans="2:24" x14ac:dyDescent="0.3">
       <c r="B3" s="1" t="s">
         <v>1</v>
       </c>
@@ -1175,11 +1175,11 @@
         <v>18</v>
       </c>
     </row>
-    <row r="4" spans="2:23" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:24" ht="14.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B4" s="2">
         <v>100922046</v>
       </c>
-      <c r="C4" s="8" t="s">
+      <c r="C4" s="7" t="s">
         <v>19</v>
       </c>
       <c r="D4" s="4">
@@ -1243,12 +1243,19 @@
       <c r="W4" s="3" t="s">
         <v>124</v>
       </c>
-    </row>
-    <row r="5" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="X4" t="str">
+        <f>"INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,""PASSWORD"",CORREO,DIRECTOR) VALUES (" &amp;
+"SEQ_TB_SAM_USUARIOS.NEXTVAL, 2, '" &amp;
+SUBSTITUTE(C4,"'","''") &amp; "', 'MEX Prevencion de PLD', 'Contraloria Normativa', '" &amp;
+SUBSTITUTE(U4,"'","''") &amp; "', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);"</f>
+        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (SEQ_TB_SAM_USUARIOS.NEXTVAL, 2, 'ALEJANDRO MARTINEZ FERES', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'alejandro.martinez', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
+      </c>
+    </row>
+    <row r="5" spans="2:24" x14ac:dyDescent="0.3">
       <c r="B5" s="2">
         <v>100004927</v>
       </c>
-      <c r="C5" s="6" t="s">
+      <c r="C5" s="5" t="s">
         <v>22</v>
       </c>
       <c r="D5" s="4"/>
@@ -1280,7 +1287,7 @@
         <v>21</v>
       </c>
       <c r="T5" t="str">
-        <f t="shared" ref="T5:U68" si="0">LOWER(LEFT(C5,FIND(" ",C5)-1) &amp; "." &amp; MID(C5,FIND(" ",C5)+1,FIND(" ",C5,FIND(" ",C5)+1)-FIND(" ",C5)-1))</f>
+        <f t="shared" ref="T5:T68" si="0">LOWER(LEFT(C5,FIND(" ",C5)-1) &amp; "." &amp; MID(C5,FIND(" ",C5)+1,FIND(" ",C5,FIND(" ",C5)+1)-FIND(" ",C5)-1))</f>
         <v>vianca.rosalba</v>
       </c>
       <c r="U5" t="s">
@@ -1292,12 +1299,19 @@
       <c r="W5" s="3" t="s">
         <v>124</v>
       </c>
-    </row>
-    <row r="6" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="X5" t="str">
+        <f t="shared" ref="X5:X68" si="1">"INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,""PASSWORD"",CORREO,DIRECTOR) VALUES (" &amp;
+"SEQ_TB_SAM_USUARIOS.NEXTVAL, 2, '" &amp;
+SUBSTITUTE(C5,"'","''") &amp; "', 'MEX Prevencion de PLD', 'Contraloria Normativa', '" &amp;
+SUBSTITUTE(U5,"'","''") &amp; "', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);"</f>
+        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (SEQ_TB_SAM_USUARIOS.NEXTVAL, 2, 'VIANCA ROSALBA ESPINOSA ROMAN', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'vianca.rosalba', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
+      </c>
+    </row>
+    <row r="6" spans="2:24" x14ac:dyDescent="0.3">
       <c r="B6" s="2">
         <v>100500870</v>
       </c>
-      <c r="C6" s="6" t="s">
+      <c r="C6" s="5" t="s">
         <v>24</v>
       </c>
       <c r="D6" s="4">
@@ -1343,12 +1357,16 @@
       <c r="W6" s="3" t="s">
         <v>124</v>
       </c>
-    </row>
-    <row r="7" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="X6" t="str">
+        <f t="shared" si="1"/>
+        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (SEQ_TB_SAM_USUARIOS.NEXTVAL, 2, 'NOEMI NATALY TELLEZ CORREA', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'noemi.nataly', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
+      </c>
+    </row>
+    <row r="7" spans="2:24" x14ac:dyDescent="0.3">
       <c r="B7" s="2">
         <v>100018886</v>
       </c>
-      <c r="C7" s="7" t="s">
+      <c r="C7" s="6" t="s">
         <v>25</v>
       </c>
       <c r="D7" s="4">
@@ -1403,12 +1421,16 @@
       <c r="W7" s="3" t="s">
         <v>124</v>
       </c>
-    </row>
-    <row r="8" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="X7" t="str">
+        <f t="shared" si="1"/>
+        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (SEQ_TB_SAM_USUARIOS.NEXTVAL, 2, 'MARIAELENA ALAMILLA ALVAREZ', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'mariaelena.alamilla', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
+      </c>
+    </row>
+    <row r="8" spans="2:24" x14ac:dyDescent="0.3">
       <c r="B8" s="2">
         <v>100675883</v>
       </c>
-      <c r="C8" s="7" t="s">
+      <c r="C8" s="6" t="s">
         <v>27</v>
       </c>
       <c r="D8" s="4">
@@ -1463,12 +1485,16 @@
       <c r="W8" s="3" t="s">
         <v>124</v>
       </c>
-    </row>
-    <row r="9" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="X8" t="str">
+        <f t="shared" si="1"/>
+        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (SEQ_TB_SAM_USUARIOS.NEXTVAL, 2, 'DINA ROMAN LIZARRAGA', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'dina.roman', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
+      </c>
+    </row>
+    <row r="9" spans="2:24" x14ac:dyDescent="0.3">
       <c r="B9" s="2">
         <v>100572137</v>
       </c>
-      <c r="C9" s="7" t="s">
+      <c r="C9" s="6" t="s">
         <v>28</v>
       </c>
       <c r="D9" s="4">
@@ -1523,12 +1549,16 @@
       <c r="W9" s="3" t="s">
         <v>124</v>
       </c>
-    </row>
-    <row r="10" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="X9" t="str">
+        <f t="shared" si="1"/>
+        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (SEQ_TB_SAM_USUARIOS.NEXTVAL, 2, 'ALEJANDRO PEREZ JIMENEZ', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'alejandro.perez', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
+      </c>
+    </row>
+    <row r="10" spans="2:24" x14ac:dyDescent="0.3">
       <c r="B10" s="2">
         <v>100985454</v>
       </c>
-      <c r="C10" s="8" t="s">
+      <c r="C10" s="7" t="s">
         <v>29</v>
       </c>
       <c r="D10" s="4">
@@ -1586,12 +1616,16 @@
       <c r="W10" s="3" t="s">
         <v>124</v>
       </c>
-    </row>
-    <row r="11" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="X10" t="str">
+        <f t="shared" si="1"/>
+        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (SEQ_TB_SAM_USUARIOS.NEXTVAL, 2, 'ALEJANDRO CALANDA MORALES', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'alejandro.calanda', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
+      </c>
+    </row>
+    <row r="11" spans="2:24" x14ac:dyDescent="0.3">
       <c r="B11" s="2">
         <v>100677152</v>
       </c>
-      <c r="C11" s="6" t="s">
+      <c r="C11" s="5" t="s">
         <v>30</v>
       </c>
       <c r="D11" s="4">
@@ -1646,12 +1680,16 @@
       <c r="W11" s="3" t="s">
         <v>124</v>
       </c>
-    </row>
-    <row r="12" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="X11" t="str">
+        <f t="shared" si="1"/>
+        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (SEQ_TB_SAM_USUARIOS.NEXTVAL, 2, 'CARLOS AGUAYO SANCHEZ', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'carlos.aguayo', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
+      </c>
+    </row>
+    <row r="12" spans="2:24" x14ac:dyDescent="0.3">
       <c r="B12" s="2">
         <v>100000263</v>
       </c>
-      <c r="C12" s="6" t="s">
+      <c r="C12" s="5" t="s">
         <v>31</v>
       </c>
       <c r="D12" s="4"/>
@@ -1711,12 +1749,16 @@
       <c r="W12" s="3" t="s">
         <v>124</v>
       </c>
-    </row>
-    <row r="13" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="X12" t="str">
+        <f t="shared" si="1"/>
+        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (SEQ_TB_SAM_USUARIOS.NEXTVAL, 2, 'ADRIANA TAPIA GONZALEZ', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'adriana.tapia', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
+      </c>
+    </row>
+    <row r="13" spans="2:24" x14ac:dyDescent="0.3">
       <c r="B13" s="2">
         <v>100854877</v>
       </c>
-      <c r="C13" s="8" t="s">
+      <c r="C13" s="7" t="s">
         <v>33</v>
       </c>
       <c r="D13" s="4">
@@ -1778,12 +1820,16 @@
       <c r="W13" s="3" t="s">
         <v>124</v>
       </c>
-    </row>
-    <row r="14" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="X13" t="str">
+        <f t="shared" si="1"/>
+        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (SEQ_TB_SAM_USUARIOS.NEXTVAL, 2, 'JOSE FERNANDO PUENTE PLATA', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'jose.fernando', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
+      </c>
+    </row>
+    <row r="14" spans="2:24" x14ac:dyDescent="0.3">
       <c r="B14" s="2">
         <v>100019203</v>
       </c>
-      <c r="C14" s="6" t="s">
+      <c r="C14" s="5" t="s">
         <v>34</v>
       </c>
       <c r="D14" s="4">
@@ -1837,12 +1883,16 @@
       <c r="W14" s="3" t="s">
         <v>124</v>
       </c>
-    </row>
-    <row r="15" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="X14" t="str">
+        <f t="shared" si="1"/>
+        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (SEQ_TB_SAM_USUARIOS.NEXTVAL, 2, 'CARLOS RAMON SANDOVAL MINERO', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'carlos.ramon', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
+      </c>
+    </row>
+    <row r="15" spans="2:24" x14ac:dyDescent="0.3">
       <c r="B15" s="2">
         <v>100019200</v>
       </c>
-      <c r="C15" s="6" t="s">
+      <c r="C15" s="5" t="s">
         <v>36</v>
       </c>
       <c r="D15" s="4">
@@ -1896,8 +1946,12 @@
       <c r="W15" s="3" t="s">
         <v>124</v>
       </c>
-    </row>
-    <row r="16" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="X15" t="str">
+        <f t="shared" si="1"/>
+        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (SEQ_TB_SAM_USUARIOS.NEXTVAL, 2, 'GRACIELA AGUILAR MARTINEZ', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'graciela.aguilar', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
+      </c>
+    </row>
+    <row r="16" spans="2:24" x14ac:dyDescent="0.3">
       <c r="B16" s="2">
         <v>100019204</v>
       </c>
@@ -1955,8 +2009,12 @@
       <c r="W16" s="3" t="s">
         <v>124</v>
       </c>
-    </row>
-    <row r="17" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="X16" t="str">
+        <f t="shared" si="1"/>
+        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (SEQ_TB_SAM_USUARIOS.NEXTVAL, 2, 'ALEJANDRO CESAR SANCHEZ CERVANTES', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'alejandro.cesar', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
+      </c>
+    </row>
+    <row r="17" spans="2:24" x14ac:dyDescent="0.3">
       <c r="B17" s="2">
         <v>100327492</v>
       </c>
@@ -2014,8 +2072,12 @@
       <c r="W17" s="3" t="s">
         <v>124</v>
       </c>
-    </row>
-    <row r="18" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="X17" t="str">
+        <f t="shared" si="1"/>
+        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (SEQ_TB_SAM_USUARIOS.NEXTVAL, 2, 'LEONARDO DAVID PLATA MARTINEZ', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'leonardo.david', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
+      </c>
+    </row>
+    <row r="18" spans="2:24" x14ac:dyDescent="0.3">
       <c r="B18" s="2">
         <v>100327494</v>
       </c>
@@ -2069,8 +2131,12 @@
       <c r="W18" s="3" t="s">
         <v>124</v>
       </c>
-    </row>
-    <row r="19" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="X18" t="str">
+        <f t="shared" si="1"/>
+        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (SEQ_TB_SAM_USUARIOS.NEXTVAL, 2, 'VERONICA MARTELL ESPINOSA', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'veronica.martell', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
+      </c>
+    </row>
+    <row r="19" spans="2:24" x14ac:dyDescent="0.3">
       <c r="B19" s="2">
         <v>100000056</v>
       </c>
@@ -2128,8 +2194,12 @@
       <c r="W19" s="3" t="s">
         <v>124</v>
       </c>
-    </row>
-    <row r="20" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="X19" t="str">
+        <f t="shared" si="1"/>
+        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (SEQ_TB_SAM_USUARIOS.NEXTVAL, 2, 'CARLOS ALBERTO RAMIREZ JUAREZ', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'carlos.alberto', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
+      </c>
+    </row>
+    <row r="20" spans="2:24" x14ac:dyDescent="0.3">
       <c r="B20" s="2">
         <v>100384479</v>
       </c>
@@ -2187,8 +2257,12 @@
       <c r="W20" s="3" t="s">
         <v>124</v>
       </c>
-    </row>
-    <row r="21" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="X20" t="str">
+        <f t="shared" si="1"/>
+        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (SEQ_TB_SAM_USUARIOS.NEXTVAL, 2, 'OCTAVIO AUGUSTO DIAZ LOPEZ', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'octavio.augusto', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
+      </c>
+    </row>
+    <row r="21" spans="2:24" x14ac:dyDescent="0.3">
       <c r="B21" s="2">
         <v>100545348</v>
       </c>
@@ -2246,8 +2320,12 @@
       <c r="W21" s="3" t="s">
         <v>124</v>
       </c>
-    </row>
-    <row r="22" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="X21" t="str">
+        <f t="shared" si="1"/>
+        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (SEQ_TB_SAM_USUARIOS.NEXTVAL, 2, 'ANGEL DANIEL RUIZ ACUÑA', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'angel.daniel', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
+      </c>
+    </row>
+    <row r="22" spans="2:24" x14ac:dyDescent="0.3">
       <c r="B22" s="2">
         <v>100003814</v>
       </c>
@@ -2311,8 +2389,12 @@
       <c r="W22" s="3" t="s">
         <v>124</v>
       </c>
-    </row>
-    <row r="23" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="X22" t="str">
+        <f t="shared" si="1"/>
+        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (SEQ_TB_SAM_USUARIOS.NEXTVAL, 2, 'SARA MALDONADO VILCHIS', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'sara.maldonado', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
+      </c>
+    </row>
+    <row r="23" spans="2:24" x14ac:dyDescent="0.3">
       <c r="B23" s="2">
         <v>100019864</v>
       </c>
@@ -2376,8 +2458,12 @@
       <c r="W23" s="3" t="s">
         <v>124</v>
       </c>
-    </row>
-    <row r="24" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="X23" t="str">
+        <f t="shared" si="1"/>
+        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (SEQ_TB_SAM_USUARIOS.NEXTVAL, 2, 'PAOLA MARIANA DOMINGUEZ MAS', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'paola.mariana', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
+      </c>
+    </row>
+    <row r="24" spans="2:24" x14ac:dyDescent="0.3">
       <c r="B24" s="2">
         <v>100018887</v>
       </c>
@@ -2441,8 +2527,12 @@
       <c r="W24" s="3" t="s">
         <v>124</v>
       </c>
-    </row>
-    <row r="25" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="X24" t="str">
+        <f t="shared" si="1"/>
+        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (SEQ_TB_SAM_USUARIOS.NEXTVAL, 2, 'ANDRES IGNACIO MUÑETON RODRIGUEZ', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'andres.ignacio', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
+      </c>
+    </row>
+    <row r="25" spans="2:24" x14ac:dyDescent="0.3">
       <c r="B25" s="2">
         <v>100018888</v>
       </c>
@@ -2506,8 +2596,12 @@
       <c r="W25" s="3" t="s">
         <v>124</v>
       </c>
-    </row>
-    <row r="26" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="X25" t="str">
+        <f t="shared" si="1"/>
+        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (SEQ_TB_SAM_USUARIOS.NEXTVAL, 2, 'JOSE URIBE CEDILLO', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'jose.uribe', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
+      </c>
+    </row>
+    <row r="26" spans="2:24" x14ac:dyDescent="0.3">
       <c r="B26" s="2">
         <v>100015250</v>
       </c>
@@ -2571,8 +2665,12 @@
       <c r="W26" s="3" t="s">
         <v>124</v>
       </c>
-    </row>
-    <row r="27" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="X26" t="str">
+        <f t="shared" si="1"/>
+        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (SEQ_TB_SAM_USUARIOS.NEXTVAL, 2, 'MARCOS CAMACHO PARADA', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'marcos.camacho', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
+      </c>
+    </row>
+    <row r="27" spans="2:24" x14ac:dyDescent="0.3">
       <c r="B27" s="2">
         <v>100018636</v>
       </c>
@@ -2636,8 +2734,12 @@
       <c r="W27" s="3" t="s">
         <v>124</v>
       </c>
-    </row>
-    <row r="28" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="X27" t="str">
+        <f t="shared" si="1"/>
+        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (SEQ_TB_SAM_USUARIOS.NEXTVAL, 2, 'LUIS ARTURO FLORES SANCHEZ', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'luis.arturo', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
+      </c>
+    </row>
+    <row r="28" spans="2:24" x14ac:dyDescent="0.3">
       <c r="B28" s="2">
         <v>100009066</v>
       </c>
@@ -2701,8 +2803,12 @@
       <c r="W28" s="3" t="s">
         <v>124</v>
       </c>
-    </row>
-    <row r="29" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="X28" t="str">
+        <f t="shared" si="1"/>
+        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (SEQ_TB_SAM_USUARIOS.NEXTVAL, 2, 'RAFAEL BUERBA GOMEZ', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'rafael.buerba', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
+      </c>
+    </row>
+    <row r="29" spans="2:24" x14ac:dyDescent="0.3">
       <c r="B29" s="2">
         <v>100401809</v>
       </c>
@@ -2766,8 +2872,12 @@
       <c r="W29" s="3" t="s">
         <v>124</v>
       </c>
-    </row>
-    <row r="30" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="X29" t="str">
+        <f t="shared" si="1"/>
+        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (SEQ_TB_SAM_USUARIOS.NEXTVAL, 2, 'JUAN PABLO ARIZALETA BARQUIN', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'juan.pablo', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
+      </c>
+    </row>
+    <row r="30" spans="2:24" x14ac:dyDescent="0.3">
       <c r="B30" s="2">
         <v>100416647</v>
       </c>
@@ -2831,8 +2941,12 @@
       <c r="W30" s="3" t="s">
         <v>124</v>
       </c>
-    </row>
-    <row r="31" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="X30" t="str">
+        <f t="shared" si="1"/>
+        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (SEQ_TB_SAM_USUARIOS.NEXTVAL, 2, 'ALEJANDRO LAVIN TREVIÑO', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'alejandro.lavin', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
+      </c>
+    </row>
+    <row r="31" spans="2:24" x14ac:dyDescent="0.3">
       <c r="B31" s="2">
         <v>100253304</v>
       </c>
@@ -2896,8 +3010,12 @@
       <c r="W31" s="3" t="s">
         <v>124</v>
       </c>
-    </row>
-    <row r="32" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="X31" t="str">
+        <f t="shared" si="1"/>
+        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (SEQ_TB_SAM_USUARIOS.NEXTVAL, 2, 'RAFAEL BENJAMIN VEGA ORTEGA', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'rafael.benjamin', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
+      </c>
+    </row>
+    <row r="32" spans="2:24" x14ac:dyDescent="0.3">
       <c r="B32" s="2">
         <v>100523258</v>
       </c>
@@ -2961,8 +3079,12 @@
       <c r="W32" s="3" t="s">
         <v>124</v>
       </c>
-    </row>
-    <row r="33" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="X32" t="str">
+        <f t="shared" si="1"/>
+        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (SEQ_TB_SAM_USUARIOS.NEXTVAL, 2, 'LUIS FERNANDO YANCE CHARRIA', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'luis.fernando', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
+      </c>
+    </row>
+    <row r="33" spans="2:24" x14ac:dyDescent="0.3">
       <c r="B33" s="2">
         <v>100016803</v>
       </c>
@@ -3026,8 +3148,12 @@
       <c r="W33" s="3" t="s">
         <v>124</v>
       </c>
-    </row>
-    <row r="34" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="X33" t="str">
+        <f t="shared" si="1"/>
+        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (SEQ_TB_SAM_USUARIOS.NEXTVAL, 2, 'MAURO VAZQUEZ FLORES', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'mauro.vazquez', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
+      </c>
+    </row>
+    <row r="34" spans="2:24" x14ac:dyDescent="0.3">
       <c r="B34" s="2">
         <v>100574048</v>
       </c>
@@ -3091,8 +3217,12 @@
       <c r="W34" s="3" t="s">
         <v>124</v>
       </c>
-    </row>
-    <row r="35" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="X34" t="str">
+        <f t="shared" si="1"/>
+        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (SEQ_TB_SAM_USUARIOS.NEXTVAL, 2, 'JORGE OMAR VARGAS VEGA', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'jorge.omar', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
+      </c>
+    </row>
+    <row r="35" spans="2:24" x14ac:dyDescent="0.3">
       <c r="B35" s="2">
         <v>100613246</v>
       </c>
@@ -3156,8 +3286,12 @@
       <c r="W35" s="3" t="s">
         <v>124</v>
       </c>
-    </row>
-    <row r="36" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="X35" t="str">
+        <f t="shared" si="1"/>
+        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (SEQ_TB_SAM_USUARIOS.NEXTVAL, 2, 'BERNARDO MALPICA DONDE', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'bernardo.malpica', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
+      </c>
+    </row>
+    <row r="36" spans="2:24" x14ac:dyDescent="0.3">
       <c r="B36" s="2">
         <v>100854836</v>
       </c>
@@ -3223,8 +3357,12 @@
       <c r="W36" s="3" t="s">
         <v>124</v>
       </c>
-    </row>
-    <row r="37" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="X36" t="str">
+        <f t="shared" si="1"/>
+        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (SEQ_TB_SAM_USUARIOS.NEXTVAL, 2, 'MONICA BARRIGA ROBLES', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'monica.barriga', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
+      </c>
+    </row>
+    <row r="37" spans="2:24" x14ac:dyDescent="0.3">
       <c r="B37" s="2">
         <v>100861962</v>
       </c>
@@ -3290,8 +3428,12 @@
       <c r="W37" s="3" t="s">
         <v>124</v>
       </c>
-    </row>
-    <row r="38" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="X37" t="str">
+        <f t="shared" si="1"/>
+        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (SEQ_TB_SAM_USUARIOS.NEXTVAL, 2, 'PATRICIA MARTINEZ GUTIERREZ', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'patricia.martinez', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
+      </c>
+    </row>
+    <row r="38" spans="2:24" x14ac:dyDescent="0.3">
       <c r="B38" s="2">
         <v>100362615</v>
       </c>
@@ -3355,8 +3497,12 @@
       <c r="W38" s="3" t="s">
         <v>124</v>
       </c>
-    </row>
-    <row r="39" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="X38" t="str">
+        <f t="shared" si="1"/>
+        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (SEQ_TB_SAM_USUARIOS.NEXTVAL, 2, 'BRENDA GISELL GIRON MAY', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'brenda.gisell', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
+      </c>
+    </row>
+    <row r="39" spans="2:24" x14ac:dyDescent="0.3">
       <c r="B39" s="2">
         <v>100591294</v>
       </c>
@@ -3420,8 +3566,12 @@
       <c r="W39" s="3" t="s">
         <v>124</v>
       </c>
-    </row>
-    <row r="40" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="X39" t="str">
+        <f t="shared" si="1"/>
+        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (SEQ_TB_SAM_USUARIOS.NEXTVAL, 2, 'SANTIAGO PALAZUELOS VON BERTRAB', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'santiago.palazuelos', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
+      </c>
+    </row>
+    <row r="40" spans="2:24" x14ac:dyDescent="0.3">
       <c r="B40" s="2">
         <v>100685301</v>
       </c>
@@ -3485,8 +3635,12 @@
       <c r="W40" s="3" t="s">
         <v>124</v>
       </c>
-    </row>
-    <row r="41" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="X40" t="str">
+        <f t="shared" si="1"/>
+        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (SEQ_TB_SAM_USUARIOS.NEXTVAL, 2, 'RODRIGO EDUARDO SANHUEZA VEGA', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'rodrigo.eduardo', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
+      </c>
+    </row>
+    <row r="41" spans="2:24" x14ac:dyDescent="0.3">
       <c r="B41" s="2">
         <v>100559745</v>
       </c>
@@ -3550,8 +3704,12 @@
       <c r="W41" s="3" t="s">
         <v>124</v>
       </c>
-    </row>
-    <row r="42" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="X41" t="str">
+        <f t="shared" si="1"/>
+        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (SEQ_TB_SAM_USUARIOS.NEXTVAL, 2, 'NADINE ORNELAS ESQUINCA', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'nadine.ornelas', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
+      </c>
+    </row>
+    <row r="42" spans="2:24" x14ac:dyDescent="0.3">
       <c r="B42" s="2">
         <v>100251487</v>
       </c>
@@ -3611,8 +3769,12 @@
       <c r="W42" s="3" t="s">
         <v>124</v>
       </c>
-    </row>
-    <row r="43" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="X42" t="str">
+        <f t="shared" si="1"/>
+        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (SEQ_TB_SAM_USUARIOS.NEXTVAL, 2, 'LUIS ANTONIO TOVAR ACUÑA', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'luis.antonio', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
+      </c>
+    </row>
+    <row r="43" spans="2:24" x14ac:dyDescent="0.3">
       <c r="B43" s="2">
         <v>100014520</v>
       </c>
@@ -3672,8 +3834,12 @@
       <c r="W43" s="3" t="s">
         <v>124</v>
       </c>
-    </row>
-    <row r="44" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="X43" t="str">
+        <f t="shared" si="1"/>
+        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (SEQ_TB_SAM_USUARIOS.NEXTVAL, 2, 'DANIEL LOPEZ IBARRA', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'daniel.lopez', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
+      </c>
+    </row>
+    <row r="44" spans="2:24" x14ac:dyDescent="0.3">
       <c r="B44" s="2">
         <v>100014960</v>
       </c>
@@ -3733,8 +3899,12 @@
       <c r="W44" s="3" t="s">
         <v>124</v>
       </c>
-    </row>
-    <row r="45" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="X44" t="str">
+        <f t="shared" si="1"/>
+        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (SEQ_TB_SAM_USUARIOS.NEXTVAL, 2, 'PABLO RUIZ HERRERA', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'pablo.ruiz', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
+      </c>
+    </row>
+    <row r="45" spans="2:24" x14ac:dyDescent="0.3">
       <c r="B45" s="2">
         <v>100015893</v>
       </c>
@@ -3792,8 +3962,12 @@
       <c r="W45" s="3" t="s">
         <v>124</v>
       </c>
-    </row>
-    <row r="46" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="X45" t="str">
+        <f t="shared" si="1"/>
+        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (SEQ_TB_SAM_USUARIOS.NEXTVAL, 2, 'ADRIANA GONZALEZ PALACIOS', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'adriana.gonzalez', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
+      </c>
+    </row>
+    <row r="46" spans="2:24" x14ac:dyDescent="0.3">
       <c r="B46" s="2">
         <v>100017815</v>
       </c>
@@ -3849,8 +4023,12 @@
       <c r="W46" s="3" t="s">
         <v>124</v>
       </c>
-    </row>
-    <row r="47" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="X46" t="str">
+        <f t="shared" si="1"/>
+        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (SEQ_TB_SAM_USUARIOS.NEXTVAL, 2, 'ALVARO ALBERTO OCHOA PICHARDO', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'alvaro.alberto', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
+      </c>
+    </row>
+    <row r="47" spans="2:24" x14ac:dyDescent="0.3">
       <c r="B47" s="2">
         <v>100267204</v>
       </c>
@@ -3906,8 +4084,12 @@
       <c r="W47" s="3" t="s">
         <v>124</v>
       </c>
-    </row>
-    <row r="48" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="X47" t="str">
+        <f t="shared" si="1"/>
+        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (SEQ_TB_SAM_USUARIOS.NEXTVAL, 2, 'JAVIER PACHECO LOPEZ', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'javier.pacheco', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
+      </c>
+    </row>
+    <row r="48" spans="2:24" x14ac:dyDescent="0.3">
       <c r="B48" s="2">
         <v>100018765</v>
       </c>
@@ -3967,8 +4149,12 @@
       <c r="W48" s="3" t="s">
         <v>124</v>
       </c>
-    </row>
-    <row r="49" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="X48" t="str">
+        <f t="shared" si="1"/>
+        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (SEQ_TB_SAM_USUARIOS.NEXTVAL, 2, 'BRENDA LIZBETH MONTEAGUDO RAMIREZ', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'brenda.lizbeth', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
+      </c>
+    </row>
+    <row r="49" spans="2:24" x14ac:dyDescent="0.3">
       <c r="B49" s="2">
         <v>100383461</v>
       </c>
@@ -4028,8 +4214,12 @@
       <c r="W49" s="3" t="s">
         <v>124</v>
       </c>
-    </row>
-    <row r="50" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="X49" t="str">
+        <f t="shared" si="1"/>
+        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (SEQ_TB_SAM_USUARIOS.NEXTVAL, 2, 'ROQUE DANIEL TORRES TENORIO', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'roque.daniel', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
+      </c>
+    </row>
+    <row r="50" spans="2:24" x14ac:dyDescent="0.3">
       <c r="B50" s="2">
         <v>100383462</v>
       </c>
@@ -4089,8 +4279,12 @@
       <c r="W50" s="3" t="s">
         <v>124</v>
       </c>
-    </row>
-    <row r="51" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="X50" t="str">
+        <f t="shared" si="1"/>
+        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (SEQ_TB_SAM_USUARIOS.NEXTVAL, 2, 'KATHIA AIDEE SOLIS ESCOBAR', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'kathia.aidee', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
+      </c>
+    </row>
+    <row r="51" spans="2:24" x14ac:dyDescent="0.3">
       <c r="B51" s="2">
         <v>100018274</v>
       </c>
@@ -4148,8 +4342,12 @@
       <c r="W51" s="3" t="s">
         <v>124</v>
       </c>
-    </row>
-    <row r="52" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="X51" t="str">
+        <f t="shared" si="1"/>
+        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (SEQ_TB_SAM_USUARIOS.NEXTVAL, 2, 'VERONICA INES LEON MOCTEZUMA', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'veronica.ines', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
+      </c>
+    </row>
+    <row r="52" spans="2:24" x14ac:dyDescent="0.3">
       <c r="B52" s="2">
         <v>100404797</v>
       </c>
@@ -4209,8 +4407,12 @@
       <c r="W52" s="3" t="s">
         <v>124</v>
       </c>
-    </row>
-    <row r="53" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="X52" t="str">
+        <f t="shared" si="1"/>
+        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (SEQ_TB_SAM_USUARIOS.NEXTVAL, 2, 'DANIELA ARAIZA MACIAS', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'daniela.araiza', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
+      </c>
+    </row>
+    <row r="53" spans="2:24" x14ac:dyDescent="0.3">
       <c r="B53" s="2">
         <v>100533479</v>
       </c>
@@ -4270,8 +4472,12 @@
       <c r="W53" s="3" t="s">
         <v>124</v>
       </c>
-    </row>
-    <row r="54" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="X53" t="str">
+        <f t="shared" si="1"/>
+        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (SEQ_TB_SAM_USUARIOS.NEXTVAL, 2, 'LAURA SARAI NAJERA HERNANDEZ', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'laura.sarai', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
+      </c>
+    </row>
+    <row r="54" spans="2:24" x14ac:dyDescent="0.3">
       <c r="B54" s="2">
         <v>100533482</v>
       </c>
@@ -4331,8 +4537,12 @@
       <c r="W54" s="3" t="s">
         <v>124</v>
       </c>
-    </row>
-    <row r="55" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="X54" t="str">
+        <f t="shared" si="1"/>
+        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (SEQ_TB_SAM_USUARIOS.NEXTVAL, 2, 'ALFREDO MARQUEZ GUTIERREZ', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'alfredo.marquez', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
+      </c>
+    </row>
+    <row r="55" spans="2:24" x14ac:dyDescent="0.3">
       <c r="B55" s="2">
         <v>100549886</v>
       </c>
@@ -4392,8 +4602,12 @@
       <c r="W55" s="3" t="s">
         <v>124</v>
       </c>
-    </row>
-    <row r="56" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="X55" t="str">
+        <f t="shared" si="1"/>
+        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (SEQ_TB_SAM_USUARIOS.NEXTVAL, 2, 'RICARDO MENDOZA VILLEGAS', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'ricardo.mendoza', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
+      </c>
+    </row>
+    <row r="56" spans="2:24" x14ac:dyDescent="0.3">
       <c r="B56" s="2">
         <v>100664258</v>
       </c>
@@ -4453,8 +4667,12 @@
       <c r="W56" s="3" t="s">
         <v>124</v>
       </c>
-    </row>
-    <row r="57" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="X56" t="str">
+        <f t="shared" si="1"/>
+        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (SEQ_TB_SAM_USUARIOS.NEXTVAL, 2, 'EDGAR RENDON RAMIREZ', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'edgar.rendon', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
+      </c>
+    </row>
+    <row r="57" spans="2:24" x14ac:dyDescent="0.3">
       <c r="B57" s="2">
         <v>100696339</v>
       </c>
@@ -4514,8 +4732,12 @@
       <c r="W57" s="3" t="s">
         <v>124</v>
       </c>
-    </row>
-    <row r="58" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="X57" t="str">
+        <f t="shared" si="1"/>
+        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (SEQ_TB_SAM_USUARIOS.NEXTVAL, 2, 'LUIS IGNACIO HERNANDEZ SANTIAGO', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'luis.ignacio', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
+      </c>
+    </row>
+    <row r="58" spans="2:24" x14ac:dyDescent="0.3">
       <c r="B58" s="2">
         <v>100854847</v>
       </c>
@@ -4577,8 +4799,12 @@
       <c r="W58" s="3" t="s">
         <v>124</v>
       </c>
-    </row>
-    <row r="59" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="X58" t="str">
+        <f t="shared" si="1"/>
+        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (SEQ_TB_SAM_USUARIOS.NEXTVAL, 2, 'MIGUEL GONZALEZ MARTINEZ', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'miguel.gonzalez', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
+      </c>
+    </row>
+    <row r="59" spans="2:24" x14ac:dyDescent="0.3">
       <c r="B59" s="2">
         <v>100854852</v>
       </c>
@@ -4640,8 +4866,12 @@
       <c r="W59" s="3" t="s">
         <v>124</v>
       </c>
-    </row>
-    <row r="60" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="X59" t="str">
+        <f t="shared" si="1"/>
+        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (SEQ_TB_SAM_USUARIOS.NEXTVAL, 2, 'JOSE ANGEL GASPAR ANDRADE', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'jose.angel', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
+      </c>
+    </row>
+    <row r="60" spans="2:24" x14ac:dyDescent="0.3">
       <c r="B60" s="2">
         <v>100854866</v>
       </c>
@@ -4703,8 +4933,12 @@
       <c r="W60" s="3" t="s">
         <v>124</v>
       </c>
-    </row>
-    <row r="61" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="X60" t="str">
+        <f t="shared" si="1"/>
+        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (SEQ_TB_SAM_USUARIOS.NEXTVAL, 2, 'JOSE LUIS ZAVALA NAVARRO', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'jose.luis', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
+      </c>
+    </row>
+    <row r="61" spans="2:24" x14ac:dyDescent="0.3">
       <c r="B61" s="2">
         <v>100861981</v>
       </c>
@@ -4766,8 +5000,12 @@
       <c r="W61" s="3" t="s">
         <v>124</v>
       </c>
-    </row>
-    <row r="62" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="X61" t="str">
+        <f t="shared" si="1"/>
+        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (SEQ_TB_SAM_USUARIOS.NEXTVAL, 2, 'LAURA CECILIA HERNANDEZ FERREYRA', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'laura.cecilia', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
+      </c>
+    </row>
+    <row r="62" spans="2:24" x14ac:dyDescent="0.3">
       <c r="B62" s="2">
         <v>100861980</v>
       </c>
@@ -4825,8 +5063,12 @@
       <c r="W62" s="3" t="s">
         <v>124</v>
       </c>
-    </row>
-    <row r="63" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="X62" t="str">
+        <f t="shared" si="1"/>
+        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (SEQ_TB_SAM_USUARIOS.NEXTVAL, 2, 'ADRIANA VALDOVINOS MACIEL', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'adriana.valdovinos', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
+      </c>
+    </row>
+    <row r="63" spans="2:24" x14ac:dyDescent="0.3">
       <c r="B63" s="2">
         <v>100358833</v>
       </c>
@@ -4886,8 +5128,12 @@
       <c r="W63" s="3" t="s">
         <v>124</v>
       </c>
-    </row>
-    <row r="64" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="X63" t="str">
+        <f t="shared" si="1"/>
+        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (SEQ_TB_SAM_USUARIOS.NEXTVAL, 2, 'CARLOS IVAN REVILLA FACIO', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'carlos.ivan', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
+      </c>
+    </row>
+    <row r="64" spans="2:24" x14ac:dyDescent="0.3">
       <c r="B64" s="2">
         <v>100009612</v>
       </c>
@@ -4943,8 +5189,12 @@
       <c r="W64" s="3" t="s">
         <v>124</v>
       </c>
-    </row>
-    <row r="65" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="X64" t="str">
+        <f t="shared" si="1"/>
+        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (SEQ_TB_SAM_USUARIOS.NEXTVAL, 2, 'MARINA JOSA ALMELA', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'marina.josa', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
+      </c>
+    </row>
+    <row r="65" spans="2:24" x14ac:dyDescent="0.3">
       <c r="B65" s="2">
         <v>100327493</v>
       </c>
@@ -5000,8 +5250,12 @@
       <c r="W65" s="3" t="s">
         <v>124</v>
       </c>
-    </row>
-    <row r="66" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="X65" t="str">
+        <f t="shared" si="1"/>
+        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (SEQ_TB_SAM_USUARIOS.NEXTVAL, 2, 'LUZ MARIA DE LA LUZ TELLES DIAZ', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'luz.maria', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
+      </c>
+    </row>
+    <row r="66" spans="2:24" x14ac:dyDescent="0.3">
       <c r="B66" s="2">
         <v>100348704</v>
       </c>
@@ -5067,8 +5321,12 @@
       <c r="W66" s="3" t="s">
         <v>124</v>
       </c>
-    </row>
-    <row r="67" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="X66" t="str">
+        <f t="shared" si="1"/>
+        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (SEQ_TB_SAM_USUARIOS.NEXTVAL, 2, 'GLORIA PAOLA FRAGOSO CONTRERAS', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'gloria.paola', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
+      </c>
+    </row>
+    <row r="67" spans="2:24" x14ac:dyDescent="0.3">
       <c r="B67" s="2">
         <v>100695304</v>
       </c>
@@ -5124,8 +5382,12 @@
       <c r="W67" s="3" t="s">
         <v>124</v>
       </c>
-    </row>
-    <row r="68" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="X67" t="str">
+        <f t="shared" si="1"/>
+        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (SEQ_TB_SAM_USUARIOS.NEXTVAL, 2, 'JAVIER VILCHIS GARCIA', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'javier.vilchis', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
+      </c>
+    </row>
+    <row r="68" spans="2:24" x14ac:dyDescent="0.3">
       <c r="B68" s="2">
         <v>100980209</v>
       </c>
@@ -5183,8 +5445,12 @@
       <c r="W68" s="3" t="s">
         <v>124</v>
       </c>
-    </row>
-    <row r="69" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="X68" t="str">
+        <f t="shared" si="1"/>
+        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (SEQ_TB_SAM_USUARIOS.NEXTVAL, 2, 'JUAN PABLO OLIVERA CATRIP', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'juan.pablo', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
+      </c>
+    </row>
+    <row r="69" spans="2:24" x14ac:dyDescent="0.3">
       <c r="B69" s="2">
         <v>100980197</v>
       </c>
@@ -5230,7 +5496,7 @@
         <v>21</v>
       </c>
       <c r="T69" t="str">
-        <f t="shared" ref="T69:U92" si="1">LOWER(LEFT(C69,FIND(" ",C69)-1) &amp; "." &amp; MID(C69,FIND(" ",C69)+1,FIND(" ",C69,FIND(" ",C69)+1)-FIND(" ",C69)-1))</f>
+        <f t="shared" ref="T69:T92" si="2">LOWER(LEFT(C69,FIND(" ",C69)-1) &amp; "." &amp; MID(C69,FIND(" ",C69)+1,FIND(" ",C69,FIND(" ",C69)+1)-FIND(" ",C69)-1))</f>
         <v>sofia.ginebra</v>
       </c>
       <c r="U69" t="s">
@@ -5242,8 +5508,15 @@
       <c r="W69" s="3" t="s">
         <v>124</v>
       </c>
-    </row>
-    <row r="70" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="X69" t="str">
+        <f t="shared" ref="X69:X92" si="3">"INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,""PASSWORD"",CORREO,DIRECTOR) VALUES (" &amp;
+"SEQ_TB_SAM_USUARIOS.NEXTVAL, 2, '" &amp;
+SUBSTITUTE(C69,"'","''") &amp; "', 'MEX Prevencion de PLD', 'Contraloria Normativa', '" &amp;
+SUBSTITUTE(U69,"'","''") &amp; "', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);"</f>
+        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (SEQ_TB_SAM_USUARIOS.NEXTVAL, 2, 'SOFIA GINEBRA ZARANDONA', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'sofia.ginebra', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
+      </c>
+    </row>
+    <row r="70" spans="2:24" x14ac:dyDescent="0.3">
       <c r="B70" s="2">
         <v>100980202</v>
       </c>
@@ -5289,7 +5562,7 @@
         <v>21</v>
       </c>
       <c r="T70" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>jesus.patricio</v>
       </c>
       <c r="U70" t="s">
@@ -5301,8 +5574,12 @@
       <c r="W70" s="3" t="s">
         <v>124</v>
       </c>
-    </row>
-    <row r="71" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="X70" t="str">
+        <f t="shared" si="3"/>
+        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (SEQ_TB_SAM_USUARIOS.NEXTVAL, 2, 'JESUS PATRICIO AVALOS DIAZ BARREIRO', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'jesus.patricio', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
+      </c>
+    </row>
+    <row r="71" spans="2:24" x14ac:dyDescent="0.3">
       <c r="B71" s="2">
         <v>100980206</v>
       </c>
@@ -5348,7 +5625,7 @@
         <v>21</v>
       </c>
       <c r="T71" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>mauricio.fabian</v>
       </c>
       <c r="U71" t="s">
@@ -5360,8 +5637,12 @@
       <c r="W71" s="3" t="s">
         <v>124</v>
       </c>
-    </row>
-    <row r="72" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="X71" t="str">
+        <f t="shared" si="3"/>
+        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (SEQ_TB_SAM_USUARIOS.NEXTVAL, 2, 'MAURICIO FABIAN RODRIGUEZ JUAREZ', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'mauricio.fabian', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
+      </c>
+    </row>
+    <row r="72" spans="2:24" x14ac:dyDescent="0.3">
       <c r="B72" s="2">
         <v>100854856</v>
       </c>
@@ -5413,7 +5694,7 @@
         <v>21</v>
       </c>
       <c r="T72" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>jose.juan</v>
       </c>
       <c r="U72" t="s">
@@ -5425,8 +5706,12 @@
       <c r="W72" s="3" t="s">
         <v>124</v>
       </c>
-    </row>
-    <row r="73" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="X72" t="str">
+        <f t="shared" si="3"/>
+        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (SEQ_TB_SAM_USUARIOS.NEXTVAL, 2, 'JOSE JUAN LOPEZ PIÑERO', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'jose.juan', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
+      </c>
+    </row>
+    <row r="73" spans="2:24" x14ac:dyDescent="0.3">
       <c r="B73" s="2">
         <v>100002387</v>
       </c>
@@ -5476,7 +5761,7 @@
       </c>
       <c r="S73" s="3"/>
       <c r="T73" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>miguel.angel</v>
       </c>
       <c r="U73" t="s">
@@ -5488,8 +5773,12 @@
       <c r="W73" s="3" t="s">
         <v>124</v>
       </c>
-    </row>
-    <row r="74" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="X73" t="str">
+        <f t="shared" si="3"/>
+        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (SEQ_TB_SAM_USUARIOS.NEXTVAL, 2, 'MIGUEL ANGEL CARO DEL CASTILLO TREVIÑO', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'miguel.angel', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
+      </c>
+    </row>
+    <row r="74" spans="2:24" x14ac:dyDescent="0.3">
       <c r="B74" s="2">
         <v>100003523</v>
       </c>
@@ -5539,7 +5828,7 @@
       </c>
       <c r="S74" s="3"/>
       <c r="T74" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>oliver.igor</v>
       </c>
       <c r="U74" t="s">
@@ -5551,8 +5840,12 @@
       <c r="W74" s="3" t="s">
         <v>124</v>
       </c>
-    </row>
-    <row r="75" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="X74" t="str">
+        <f t="shared" si="3"/>
+        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (SEQ_TB_SAM_USUARIOS.NEXTVAL, 2, 'OLIVER IGOR YAÑEZ GONZALEZ', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'oliver.igor', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
+      </c>
+    </row>
+    <row r="75" spans="2:24" x14ac:dyDescent="0.3">
       <c r="B75" s="2">
         <v>100008885</v>
       </c>
@@ -5600,7 +5893,7 @@
       <c r="R75" s="3"/>
       <c r="S75" s="3"/>
       <c r="T75" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>maria.del</v>
       </c>
       <c r="U75" t="s">
@@ -5612,8 +5905,12 @@
       <c r="W75" s="3" t="s">
         <v>124</v>
       </c>
-    </row>
-    <row r="76" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="X75" t="str">
+        <f t="shared" si="3"/>
+        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (SEQ_TB_SAM_USUARIOS.NEXTVAL, 2, 'MARIA DEL SOCORRO RAMIREZ RICARDEZ', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'maria.del', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
+      </c>
+    </row>
+    <row r="76" spans="2:24" x14ac:dyDescent="0.3">
       <c r="B76" s="2">
         <v>100009187</v>
       </c>
@@ -5663,7 +5960,7 @@
       </c>
       <c r="S76" s="3"/>
       <c r="T76" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>mikhail.mora</v>
       </c>
       <c r="U76" t="s">
@@ -5675,8 +5972,12 @@
       <c r="W76" s="3" t="s">
         <v>124</v>
       </c>
-    </row>
-    <row r="77" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="X76" t="str">
+        <f t="shared" si="3"/>
+        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (SEQ_TB_SAM_USUARIOS.NEXTVAL, 2, 'MIKHAIL MORA APONTE', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'mikhail.mora', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
+      </c>
+    </row>
+    <row r="77" spans="2:24" x14ac:dyDescent="0.3">
       <c r="B77" s="2">
         <v>100396371</v>
       </c>
@@ -5724,7 +6025,7 @@
       <c r="R77" s="3"/>
       <c r="S77" s="3"/>
       <c r="T77" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>brenda.daniela</v>
       </c>
       <c r="U77" t="s">
@@ -5736,8 +6037,12 @@
       <c r="W77" s="3" t="s">
         <v>124</v>
       </c>
-    </row>
-    <row r="78" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="X77" t="str">
+        <f t="shared" si="3"/>
+        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (SEQ_TB_SAM_USUARIOS.NEXTVAL, 2, 'BRENDA DANIELA VELASCO ROJAS', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'brenda.daniela', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
+      </c>
+    </row>
+    <row r="78" spans="2:24" x14ac:dyDescent="0.3">
       <c r="B78" s="2">
         <v>100539130</v>
       </c>
@@ -5787,7 +6092,7 @@
       </c>
       <c r="S78" s="3"/>
       <c r="T78" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>elizandra.cardoso</v>
       </c>
       <c r="U78" t="s">
@@ -5799,8 +6104,12 @@
       <c r="W78" s="3" t="s">
         <v>124</v>
       </c>
-    </row>
-    <row r="79" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="X78" t="str">
+        <f t="shared" si="3"/>
+        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (SEQ_TB_SAM_USUARIOS.NEXTVAL, 2, 'ELIZANDRA CARDOSO AZCOITIA', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'elizandra.cardoso', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
+      </c>
+    </row>
+    <row r="79" spans="2:24" x14ac:dyDescent="0.3">
       <c r="B79" s="2">
         <v>100018885</v>
       </c>
@@ -5848,7 +6157,7 @@
       </c>
       <c r="S79" s="3"/>
       <c r="T79" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>juliana.perez</v>
       </c>
       <c r="U79" t="s">
@@ -5860,8 +6169,12 @@
       <c r="W79" s="3" t="s">
         <v>124</v>
       </c>
-    </row>
-    <row r="80" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="X79" t="str">
+        <f t="shared" si="3"/>
+        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (SEQ_TB_SAM_USUARIOS.NEXTVAL, 2, 'JULIANA PEREZ MARTIN DEL CAMPO', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'juliana.perez', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
+      </c>
+    </row>
+    <row r="80" spans="2:24" x14ac:dyDescent="0.3">
       <c r="B80" s="2">
         <v>100005847</v>
       </c>
@@ -5905,7 +6218,7 @@
       <c r="R80" s="3"/>
       <c r="S80" s="3"/>
       <c r="T80" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>diego.martinez</v>
       </c>
       <c r="U80" t="s">
@@ -5917,8 +6230,12 @@
       <c r="W80" s="3" t="s">
         <v>124</v>
       </c>
-    </row>
-    <row r="81" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="X80" t="str">
+        <f t="shared" si="3"/>
+        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (SEQ_TB_SAM_USUARIOS.NEXTVAL, 2, 'DIEGO MARTINEZ CORTES', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'diego.martinez', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
+      </c>
+    </row>
+    <row r="81" spans="2:24" x14ac:dyDescent="0.3">
       <c r="B81" s="2">
         <v>100018889</v>
       </c>
@@ -5964,7 +6281,7 @@
       </c>
       <c r="S81" s="3"/>
       <c r="T81" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>yolanda.perdomo</v>
       </c>
       <c r="U81" t="s">
@@ -5976,8 +6293,12 @@
       <c r="W81" s="3" t="s">
         <v>124</v>
       </c>
-    </row>
-    <row r="82" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="X81" t="str">
+        <f t="shared" si="3"/>
+        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (SEQ_TB_SAM_USUARIOS.NEXTVAL, 2, 'YOLANDA PERDOMO JIMENEZ', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'yolanda.perdomo', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
+      </c>
+    </row>
+    <row r="82" spans="2:24" x14ac:dyDescent="0.3">
       <c r="B82" s="2">
         <v>100546470</v>
       </c>
@@ -6023,7 +6344,7 @@
       </c>
       <c r="S82" s="3"/>
       <c r="T82" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>mercedes.sanchez</v>
       </c>
       <c r="U82" t="s">
@@ -6035,8 +6356,12 @@
       <c r="W82" s="3" t="s">
         <v>124</v>
       </c>
-    </row>
-    <row r="83" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="X82" t="str">
+        <f t="shared" si="3"/>
+        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (SEQ_TB_SAM_USUARIOS.NEXTVAL, 2, 'MERCEDES SANCHEZ REYES RETANA', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'mercedes.sanchez', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
+      </c>
+    </row>
+    <row r="83" spans="2:24" x14ac:dyDescent="0.3">
       <c r="B83" s="2">
         <v>100550630</v>
       </c>
@@ -6084,7 +6409,7 @@
       </c>
       <c r="S83" s="3"/>
       <c r="T83" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>alejandra.martinez</v>
       </c>
       <c r="U83" t="s">
@@ -6096,8 +6421,12 @@
       <c r="W83" s="3" t="s">
         <v>124</v>
       </c>
-    </row>
-    <row r="84" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="X83" t="str">
+        <f t="shared" si="3"/>
+        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (SEQ_TB_SAM_USUARIOS.NEXTVAL, 2, 'ALEJANDRA MARTINEZ NIETO', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'alejandra.martinez', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
+      </c>
+    </row>
+    <row r="84" spans="2:24" x14ac:dyDescent="0.3">
       <c r="B84" s="2">
         <v>100015156</v>
       </c>
@@ -6149,7 +6478,7 @@
       </c>
       <c r="S84" s="3"/>
       <c r="T84" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>julian.gomez</v>
       </c>
       <c r="U84" t="s">
@@ -6161,8 +6490,12 @@
       <c r="W84" s="3" t="s">
         <v>124</v>
       </c>
-    </row>
-    <row r="85" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="X84" t="str">
+        <f t="shared" si="3"/>
+        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (SEQ_TB_SAM_USUARIOS.NEXTVAL, 2, 'JULIAN GOMEZ FAUSTINO', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'julian.gomez', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
+      </c>
+    </row>
+    <row r="85" spans="2:24" x14ac:dyDescent="0.3">
       <c r="B85" s="2">
         <v>100019199</v>
       </c>
@@ -6212,7 +6545,7 @@
       <c r="R85" s="3"/>
       <c r="S85" s="3"/>
       <c r="T85" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>cesar.alejandro</v>
       </c>
       <c r="U85" t="s">
@@ -6224,8 +6557,12 @@
       <c r="W85" s="3" t="s">
         <v>124</v>
       </c>
-    </row>
-    <row r="86" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="X85" t="str">
+        <f t="shared" si="3"/>
+        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (SEQ_TB_SAM_USUARIOS.NEXTVAL, 2, 'CESAR ALEJANDRO ARAIZA ITURRIA', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'cesar.alejandro', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
+      </c>
+    </row>
+    <row r="86" spans="2:24" x14ac:dyDescent="0.3">
       <c r="B86" s="2">
         <v>100404799</v>
       </c>
@@ -6275,7 +6612,7 @@
       <c r="R86" s="3"/>
       <c r="S86" s="3"/>
       <c r="T86" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>mariana.chavez</v>
       </c>
       <c r="U86" t="s">
@@ -6287,8 +6624,12 @@
       <c r="W86" s="3" t="s">
         <v>124</v>
       </c>
-    </row>
-    <row r="87" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="X86" t="str">
+        <f t="shared" si="3"/>
+        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (SEQ_TB_SAM_USUARIOS.NEXTVAL, 2, 'MARIANA CHAVEZ GARCIA', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'mariana.chavez', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
+      </c>
+    </row>
+    <row r="87" spans="2:24" x14ac:dyDescent="0.3">
       <c r="B87" s="2">
         <v>100019201</v>
       </c>
@@ -6338,7 +6679,7 @@
       <c r="R87" s="3"/>
       <c r="S87" s="3"/>
       <c r="T87" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>luis.alfonso</v>
       </c>
       <c r="U87" t="s">
@@ -6350,8 +6691,12 @@
       <c r="W87" s="3" t="s">
         <v>124</v>
       </c>
-    </row>
-    <row r="88" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="X87" t="str">
+        <f t="shared" si="3"/>
+        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (SEQ_TB_SAM_USUARIOS.NEXTVAL, 2, 'LUIS ALFONSO VILLEGAS MORENO', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'luis.alfonso', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
+      </c>
+    </row>
+    <row r="88" spans="2:24" x14ac:dyDescent="0.3">
       <c r="B88" s="2">
         <v>100462092</v>
       </c>
@@ -6401,7 +6746,7 @@
       <c r="R88" s="3"/>
       <c r="S88" s="3"/>
       <c r="T88" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>jesus.gabriel</v>
       </c>
       <c r="U88" t="s">
@@ -6413,8 +6758,12 @@
       <c r="W88" s="3" t="s">
         <v>124</v>
       </c>
-    </row>
-    <row r="89" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="X88" t="str">
+        <f t="shared" si="3"/>
+        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (SEQ_TB_SAM_USUARIOS.NEXTVAL, 2, 'JESUS GABRIEL SANCHEZ CANALES', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'jesus.gabriel', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
+      </c>
+    </row>
+    <row r="89" spans="2:24" x14ac:dyDescent="0.3">
       <c r="B89" s="2">
         <v>100861987</v>
       </c>
@@ -6466,7 +6815,7 @@
         <v>21</v>
       </c>
       <c r="T89" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>perla.cristina</v>
       </c>
       <c r="U89" t="s">
@@ -6478,8 +6827,12 @@
       <c r="W89" s="3" t="s">
         <v>124</v>
       </c>
-    </row>
-    <row r="90" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="X89" t="str">
+        <f t="shared" si="3"/>
+        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (SEQ_TB_SAM_USUARIOS.NEXTVAL, 2, 'PERLA CRISTINA GONZALEZ ESPINOSA', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'perla.cristina', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
+      </c>
+    </row>
+    <row r="90" spans="2:24" x14ac:dyDescent="0.3">
       <c r="B90" s="2">
         <v>100664282</v>
       </c>
@@ -6529,7 +6882,7 @@
       <c r="R90" s="3"/>
       <c r="S90" s="3"/>
       <c r="T90" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>katerine.itzel</v>
       </c>
       <c r="U90" t="s">
@@ -6541,8 +6894,12 @@
       <c r="W90" s="3" t="s">
         <v>124</v>
       </c>
-    </row>
-    <row r="91" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="X90" t="str">
+        <f t="shared" si="3"/>
+        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (SEQ_TB_SAM_USUARIOS.NEXTVAL, 2, 'KATERINE ITZEL JIMENEZ MIGUEL', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'katerine.itzel', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
+      </c>
+    </row>
+    <row r="91" spans="2:24" x14ac:dyDescent="0.3">
       <c r="B91" s="2">
         <v>100019224</v>
       </c>
@@ -6586,7 +6943,7 @@
       <c r="R91" s="3"/>
       <c r="S91" s="3"/>
       <c r="T91" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>maria.del</v>
       </c>
       <c r="U91" t="s">
@@ -6598,8 +6955,12 @@
       <c r="W91" s="3" t="s">
         <v>124</v>
       </c>
-    </row>
-    <row r="92" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="X91" t="str">
+        <f t="shared" si="3"/>
+        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (SEQ_TB_SAM_USUARIOS.NEXTVAL, 2, 'MARIA DEL PILAR CERRILLA NORIEGA', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'maria.del', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
+      </c>
+    </row>
+    <row r="92" spans="2:24" x14ac:dyDescent="0.3">
       <c r="B92" s="2">
         <v>100561793</v>
       </c>
@@ -6649,7 +7010,7 @@
       </c>
       <c r="S92" s="3"/>
       <c r="T92" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>francisco.jose</v>
       </c>
       <c r="U92" t="s">
@@ -6661,8 +7022,12 @@
       <c r="W92" s="3" t="s">
         <v>124</v>
       </c>
-    </row>
-    <row r="93" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="X92" t="str">
+        <f t="shared" si="3"/>
+        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (SEQ_TB_SAM_USUARIOS.NEXTVAL, 2, 'FRANCISCO JOSE BRUNET NAVARRETE', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'francisco.jose', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
+      </c>
+    </row>
+    <row r="93" spans="2:24" x14ac:dyDescent="0.3">
       <c r="D93" s="4"/>
       <c r="N93" s="3"/>
       <c r="O93" s="3"/>

--- a/Archivos_Compartidos/Cursos RH/Copia de Listado para cursos normativos 2025.xlsx
+++ b/Archivos_Compartidos/Cursos RH/Copia de Listado para cursos normativos 2025.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SAMMX\Documents\GitHub\SAM_Santander\Archivos_Compartidos\Cursos RH\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CEB8F394-1A8B-4C4D-9F84-CCF5EE912074}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6DEF5C92-9930-474D-BB05-F0177294301A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{FF6FD13D-7CB9-4391-90CB-CB63A01A4952}"/>
   </bookViews>
@@ -1245,10 +1245,10 @@
       </c>
       <c r="X4" t="str">
         <f>"INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,""PASSWORD"",CORREO,DIRECTOR) VALUES (" &amp;
-"SEQ_TB_SAM_USUARIOS.NEXTVAL, 2, '" &amp;
+B4 &amp; ", 2, '" &amp;
 SUBSTITUTE(C4,"'","''") &amp; "', 'MEX Prevencion de PLD', 'Contraloria Normativa', '" &amp;
 SUBSTITUTE(U4,"'","''") &amp; "', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);"</f>
-        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (SEQ_TB_SAM_USUARIOS.NEXTVAL, 2, 'ALEJANDRO MARTINEZ FERES', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'alejandro.martinez', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
+        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (100922046, 2, 'ALEJANDRO MARTINEZ FERES', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'alejandro.martinez', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
       </c>
     </row>
     <row r="5" spans="2:24" x14ac:dyDescent="0.3">
@@ -1301,10 +1301,10 @@
       </c>
       <c r="X5" t="str">
         <f t="shared" ref="X5:X68" si="1">"INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,""PASSWORD"",CORREO,DIRECTOR) VALUES (" &amp;
-"SEQ_TB_SAM_USUARIOS.NEXTVAL, 2, '" &amp;
+B5 &amp; ", 2, '" &amp;
 SUBSTITUTE(C5,"'","''") &amp; "', 'MEX Prevencion de PLD', 'Contraloria Normativa', '" &amp;
 SUBSTITUTE(U5,"'","''") &amp; "', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);"</f>
-        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (SEQ_TB_SAM_USUARIOS.NEXTVAL, 2, 'VIANCA ROSALBA ESPINOSA ROMAN', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'vianca.rosalba', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
+        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (100004927, 2, 'VIANCA ROSALBA ESPINOSA ROMAN', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'vianca.rosalba', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
       </c>
     </row>
     <row r="6" spans="2:24" x14ac:dyDescent="0.3">
@@ -1359,7 +1359,7 @@
       </c>
       <c r="X6" t="str">
         <f t="shared" si="1"/>
-        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (SEQ_TB_SAM_USUARIOS.NEXTVAL, 2, 'NOEMI NATALY TELLEZ CORREA', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'noemi.nataly', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
+        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (100500870, 2, 'NOEMI NATALY TELLEZ CORREA', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'noemi.nataly', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
       </c>
     </row>
     <row r="7" spans="2:24" x14ac:dyDescent="0.3">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="X7" t="str">
         <f t="shared" si="1"/>
-        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (SEQ_TB_SAM_USUARIOS.NEXTVAL, 2, 'MARIAELENA ALAMILLA ALVAREZ', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'mariaelena.alamilla', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
+        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (100018886, 2, 'MARIAELENA ALAMILLA ALVAREZ', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'mariaelena.alamilla', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
       </c>
     </row>
     <row r="8" spans="2:24" x14ac:dyDescent="0.3">
@@ -1487,7 +1487,7 @@
       </c>
       <c r="X8" t="str">
         <f t="shared" si="1"/>
-        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (SEQ_TB_SAM_USUARIOS.NEXTVAL, 2, 'DINA ROMAN LIZARRAGA', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'dina.roman', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
+        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (100675883, 2, 'DINA ROMAN LIZARRAGA', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'dina.roman', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
       </c>
     </row>
     <row r="9" spans="2:24" x14ac:dyDescent="0.3">
@@ -1551,7 +1551,7 @@
       </c>
       <c r="X9" t="str">
         <f t="shared" si="1"/>
-        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (SEQ_TB_SAM_USUARIOS.NEXTVAL, 2, 'ALEJANDRO PEREZ JIMENEZ', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'alejandro.perez', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
+        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (100572137, 2, 'ALEJANDRO PEREZ JIMENEZ', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'alejandro.perez', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
       </c>
     </row>
     <row r="10" spans="2:24" x14ac:dyDescent="0.3">
@@ -1618,7 +1618,7 @@
       </c>
       <c r="X10" t="str">
         <f t="shared" si="1"/>
-        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (SEQ_TB_SAM_USUARIOS.NEXTVAL, 2, 'ALEJANDRO CALANDA MORALES', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'alejandro.calanda', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
+        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (100985454, 2, 'ALEJANDRO CALANDA MORALES', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'alejandro.calanda', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
       </c>
     </row>
     <row r="11" spans="2:24" x14ac:dyDescent="0.3">
@@ -1682,7 +1682,7 @@
       </c>
       <c r="X11" t="str">
         <f t="shared" si="1"/>
-        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (SEQ_TB_SAM_USUARIOS.NEXTVAL, 2, 'CARLOS AGUAYO SANCHEZ', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'carlos.aguayo', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
+        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (100677152, 2, 'CARLOS AGUAYO SANCHEZ', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'carlos.aguayo', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
       </c>
     </row>
     <row r="12" spans="2:24" x14ac:dyDescent="0.3">
@@ -1751,7 +1751,7 @@
       </c>
       <c r="X12" t="str">
         <f t="shared" si="1"/>
-        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (SEQ_TB_SAM_USUARIOS.NEXTVAL, 2, 'ADRIANA TAPIA GONZALEZ', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'adriana.tapia', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
+        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (100000263, 2, 'ADRIANA TAPIA GONZALEZ', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'adriana.tapia', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
       </c>
     </row>
     <row r="13" spans="2:24" x14ac:dyDescent="0.3">
@@ -1822,7 +1822,7 @@
       </c>
       <c r="X13" t="str">
         <f t="shared" si="1"/>
-        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (SEQ_TB_SAM_USUARIOS.NEXTVAL, 2, 'JOSE FERNANDO PUENTE PLATA', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'jose.fernando', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
+        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (100854877, 2, 'JOSE FERNANDO PUENTE PLATA', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'jose.fernando', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
       </c>
     </row>
     <row r="14" spans="2:24" x14ac:dyDescent="0.3">
@@ -1885,7 +1885,7 @@
       </c>
       <c r="X14" t="str">
         <f t="shared" si="1"/>
-        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (SEQ_TB_SAM_USUARIOS.NEXTVAL, 2, 'CARLOS RAMON SANDOVAL MINERO', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'carlos.ramon', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
+        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (100019203, 2, 'CARLOS RAMON SANDOVAL MINERO', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'carlos.ramon', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
       </c>
     </row>
     <row r="15" spans="2:24" x14ac:dyDescent="0.3">
@@ -1948,7 +1948,7 @@
       </c>
       <c r="X15" t="str">
         <f t="shared" si="1"/>
-        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (SEQ_TB_SAM_USUARIOS.NEXTVAL, 2, 'GRACIELA AGUILAR MARTINEZ', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'graciela.aguilar', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
+        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (100019200, 2, 'GRACIELA AGUILAR MARTINEZ', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'graciela.aguilar', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
       </c>
     </row>
     <row r="16" spans="2:24" x14ac:dyDescent="0.3">
@@ -2011,7 +2011,7 @@
       </c>
       <c r="X16" t="str">
         <f t="shared" si="1"/>
-        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (SEQ_TB_SAM_USUARIOS.NEXTVAL, 2, 'ALEJANDRO CESAR SANCHEZ CERVANTES', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'alejandro.cesar', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
+        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (100019204, 2, 'ALEJANDRO CESAR SANCHEZ CERVANTES', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'alejandro.cesar', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
       </c>
     </row>
     <row r="17" spans="2:24" x14ac:dyDescent="0.3">
@@ -2074,7 +2074,7 @@
       </c>
       <c r="X17" t="str">
         <f t="shared" si="1"/>
-        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (SEQ_TB_SAM_USUARIOS.NEXTVAL, 2, 'LEONARDO DAVID PLATA MARTINEZ', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'leonardo.david', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
+        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (100327492, 2, 'LEONARDO DAVID PLATA MARTINEZ', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'leonardo.david', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
       </c>
     </row>
     <row r="18" spans="2:24" x14ac:dyDescent="0.3">
@@ -2133,7 +2133,7 @@
       </c>
       <c r="X18" t="str">
         <f t="shared" si="1"/>
-        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (SEQ_TB_SAM_USUARIOS.NEXTVAL, 2, 'VERONICA MARTELL ESPINOSA', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'veronica.martell', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
+        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (100327494, 2, 'VERONICA MARTELL ESPINOSA', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'veronica.martell', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
       </c>
     </row>
     <row r="19" spans="2:24" x14ac:dyDescent="0.3">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="X19" t="str">
         <f t="shared" si="1"/>
-        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (SEQ_TB_SAM_USUARIOS.NEXTVAL, 2, 'CARLOS ALBERTO RAMIREZ JUAREZ', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'carlos.alberto', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
+        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (100000056, 2, 'CARLOS ALBERTO RAMIREZ JUAREZ', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'carlos.alberto', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
       </c>
     </row>
     <row r="20" spans="2:24" x14ac:dyDescent="0.3">
@@ -2259,7 +2259,7 @@
       </c>
       <c r="X20" t="str">
         <f t="shared" si="1"/>
-        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (SEQ_TB_SAM_USUARIOS.NEXTVAL, 2, 'OCTAVIO AUGUSTO DIAZ LOPEZ', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'octavio.augusto', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
+        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (100384479, 2, 'OCTAVIO AUGUSTO DIAZ LOPEZ', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'octavio.augusto', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
       </c>
     </row>
     <row r="21" spans="2:24" x14ac:dyDescent="0.3">
@@ -2322,7 +2322,7 @@
       </c>
       <c r="X21" t="str">
         <f t="shared" si="1"/>
-        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (SEQ_TB_SAM_USUARIOS.NEXTVAL, 2, 'ANGEL DANIEL RUIZ ACUÑA', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'angel.daniel', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
+        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (100545348, 2, 'ANGEL DANIEL RUIZ ACUÑA', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'angel.daniel', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
       </c>
     </row>
     <row r="22" spans="2:24" x14ac:dyDescent="0.3">
@@ -2391,7 +2391,7 @@
       </c>
       <c r="X22" t="str">
         <f t="shared" si="1"/>
-        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (SEQ_TB_SAM_USUARIOS.NEXTVAL, 2, 'SARA MALDONADO VILCHIS', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'sara.maldonado', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
+        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (100003814, 2, 'SARA MALDONADO VILCHIS', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'sara.maldonado', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
       </c>
     </row>
     <row r="23" spans="2:24" x14ac:dyDescent="0.3">
@@ -2460,7 +2460,7 @@
       </c>
       <c r="X23" t="str">
         <f t="shared" si="1"/>
-        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (SEQ_TB_SAM_USUARIOS.NEXTVAL, 2, 'PAOLA MARIANA DOMINGUEZ MAS', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'paola.mariana', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
+        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (100019864, 2, 'PAOLA MARIANA DOMINGUEZ MAS', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'paola.mariana', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
       </c>
     </row>
     <row r="24" spans="2:24" x14ac:dyDescent="0.3">
@@ -2529,7 +2529,7 @@
       </c>
       <c r="X24" t="str">
         <f t="shared" si="1"/>
-        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (SEQ_TB_SAM_USUARIOS.NEXTVAL, 2, 'ANDRES IGNACIO MUÑETON RODRIGUEZ', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'andres.ignacio', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
+        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (100018887, 2, 'ANDRES IGNACIO MUÑETON RODRIGUEZ', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'andres.ignacio', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
       </c>
     </row>
     <row r="25" spans="2:24" x14ac:dyDescent="0.3">
@@ -2598,7 +2598,7 @@
       </c>
       <c r="X25" t="str">
         <f t="shared" si="1"/>
-        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (SEQ_TB_SAM_USUARIOS.NEXTVAL, 2, 'JOSE URIBE CEDILLO', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'jose.uribe', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
+        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (100018888, 2, 'JOSE URIBE CEDILLO', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'jose.uribe', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
       </c>
     </row>
     <row r="26" spans="2:24" x14ac:dyDescent="0.3">
@@ -2667,7 +2667,7 @@
       </c>
       <c r="X26" t="str">
         <f t="shared" si="1"/>
-        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (SEQ_TB_SAM_USUARIOS.NEXTVAL, 2, 'MARCOS CAMACHO PARADA', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'marcos.camacho', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
+        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (100015250, 2, 'MARCOS CAMACHO PARADA', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'marcos.camacho', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
       </c>
     </row>
     <row r="27" spans="2:24" x14ac:dyDescent="0.3">
@@ -2736,7 +2736,7 @@
       </c>
       <c r="X27" t="str">
         <f t="shared" si="1"/>
-        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (SEQ_TB_SAM_USUARIOS.NEXTVAL, 2, 'LUIS ARTURO FLORES SANCHEZ', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'luis.arturo', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
+        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (100018636, 2, 'LUIS ARTURO FLORES SANCHEZ', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'luis.arturo', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
       </c>
     </row>
     <row r="28" spans="2:24" x14ac:dyDescent="0.3">
@@ -2805,7 +2805,7 @@
       </c>
       <c r="X28" t="str">
         <f t="shared" si="1"/>
-        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (SEQ_TB_SAM_USUARIOS.NEXTVAL, 2, 'RAFAEL BUERBA GOMEZ', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'rafael.buerba', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
+        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (100009066, 2, 'RAFAEL BUERBA GOMEZ', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'rafael.buerba', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
       </c>
     </row>
     <row r="29" spans="2:24" x14ac:dyDescent="0.3">
@@ -2874,7 +2874,7 @@
       </c>
       <c r="X29" t="str">
         <f t="shared" si="1"/>
-        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (SEQ_TB_SAM_USUARIOS.NEXTVAL, 2, 'JUAN PABLO ARIZALETA BARQUIN', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'juan.pablo', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
+        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (100401809, 2, 'JUAN PABLO ARIZALETA BARQUIN', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'juan.pablo', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
       </c>
     </row>
     <row r="30" spans="2:24" x14ac:dyDescent="0.3">
@@ -2943,7 +2943,7 @@
       </c>
       <c r="X30" t="str">
         <f t="shared" si="1"/>
-        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (SEQ_TB_SAM_USUARIOS.NEXTVAL, 2, 'ALEJANDRO LAVIN TREVIÑO', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'alejandro.lavin', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
+        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (100416647, 2, 'ALEJANDRO LAVIN TREVIÑO', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'alejandro.lavin', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
       </c>
     </row>
     <row r="31" spans="2:24" x14ac:dyDescent="0.3">
@@ -3012,7 +3012,7 @@
       </c>
       <c r="X31" t="str">
         <f t="shared" si="1"/>
-        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (SEQ_TB_SAM_USUARIOS.NEXTVAL, 2, 'RAFAEL BENJAMIN VEGA ORTEGA', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'rafael.benjamin', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
+        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (100253304, 2, 'RAFAEL BENJAMIN VEGA ORTEGA', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'rafael.benjamin', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
       </c>
     </row>
     <row r="32" spans="2:24" x14ac:dyDescent="0.3">
@@ -3081,7 +3081,7 @@
       </c>
       <c r="X32" t="str">
         <f t="shared" si="1"/>
-        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (SEQ_TB_SAM_USUARIOS.NEXTVAL, 2, 'LUIS FERNANDO YANCE CHARRIA', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'luis.fernando', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
+        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (100523258, 2, 'LUIS FERNANDO YANCE CHARRIA', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'luis.fernando', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
       </c>
     </row>
     <row r="33" spans="2:24" x14ac:dyDescent="0.3">
@@ -3150,7 +3150,7 @@
       </c>
       <c r="X33" t="str">
         <f t="shared" si="1"/>
-        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (SEQ_TB_SAM_USUARIOS.NEXTVAL, 2, 'MAURO VAZQUEZ FLORES', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'mauro.vazquez', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
+        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (100016803, 2, 'MAURO VAZQUEZ FLORES', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'mauro.vazquez', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
       </c>
     </row>
     <row r="34" spans="2:24" x14ac:dyDescent="0.3">
@@ -3219,7 +3219,7 @@
       </c>
       <c r="X34" t="str">
         <f t="shared" si="1"/>
-        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (SEQ_TB_SAM_USUARIOS.NEXTVAL, 2, 'JORGE OMAR VARGAS VEGA', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'jorge.omar', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
+        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (100574048, 2, 'JORGE OMAR VARGAS VEGA', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'jorge.omar', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
       </c>
     </row>
     <row r="35" spans="2:24" x14ac:dyDescent="0.3">
@@ -3288,7 +3288,7 @@
       </c>
       <c r="X35" t="str">
         <f t="shared" si="1"/>
-        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (SEQ_TB_SAM_USUARIOS.NEXTVAL, 2, 'BERNARDO MALPICA DONDE', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'bernardo.malpica', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
+        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (100613246, 2, 'BERNARDO MALPICA DONDE', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'bernardo.malpica', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
       </c>
     </row>
     <row r="36" spans="2:24" x14ac:dyDescent="0.3">
@@ -3359,7 +3359,7 @@
       </c>
       <c r="X36" t="str">
         <f t="shared" si="1"/>
-        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (SEQ_TB_SAM_USUARIOS.NEXTVAL, 2, 'MONICA BARRIGA ROBLES', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'monica.barriga', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
+        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (100854836, 2, 'MONICA BARRIGA ROBLES', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'monica.barriga', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
       </c>
     </row>
     <row r="37" spans="2:24" x14ac:dyDescent="0.3">
@@ -3430,7 +3430,7 @@
       </c>
       <c r="X37" t="str">
         <f t="shared" si="1"/>
-        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (SEQ_TB_SAM_USUARIOS.NEXTVAL, 2, 'PATRICIA MARTINEZ GUTIERREZ', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'patricia.martinez', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
+        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (100861962, 2, 'PATRICIA MARTINEZ GUTIERREZ', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'patricia.martinez', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
       </c>
     </row>
     <row r="38" spans="2:24" x14ac:dyDescent="0.3">
@@ -3499,7 +3499,7 @@
       </c>
       <c r="X38" t="str">
         <f t="shared" si="1"/>
-        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (SEQ_TB_SAM_USUARIOS.NEXTVAL, 2, 'BRENDA GISELL GIRON MAY', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'brenda.gisell', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
+        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (100362615, 2, 'BRENDA GISELL GIRON MAY', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'brenda.gisell', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
       </c>
     </row>
     <row r="39" spans="2:24" x14ac:dyDescent="0.3">
@@ -3568,7 +3568,7 @@
       </c>
       <c r="X39" t="str">
         <f t="shared" si="1"/>
-        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (SEQ_TB_SAM_USUARIOS.NEXTVAL, 2, 'SANTIAGO PALAZUELOS VON BERTRAB', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'santiago.palazuelos', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
+        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (100591294, 2, 'SANTIAGO PALAZUELOS VON BERTRAB', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'santiago.palazuelos', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
       </c>
     </row>
     <row r="40" spans="2:24" x14ac:dyDescent="0.3">
@@ -3637,7 +3637,7 @@
       </c>
       <c r="X40" t="str">
         <f t="shared" si="1"/>
-        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (SEQ_TB_SAM_USUARIOS.NEXTVAL, 2, 'RODRIGO EDUARDO SANHUEZA VEGA', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'rodrigo.eduardo', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
+        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (100685301, 2, 'RODRIGO EDUARDO SANHUEZA VEGA', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'rodrigo.eduardo', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
       </c>
     </row>
     <row r="41" spans="2:24" x14ac:dyDescent="0.3">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="X41" t="str">
         <f t="shared" si="1"/>
-        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (SEQ_TB_SAM_USUARIOS.NEXTVAL, 2, 'NADINE ORNELAS ESQUINCA', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'nadine.ornelas', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
+        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (100559745, 2, 'NADINE ORNELAS ESQUINCA', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'nadine.ornelas', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
       </c>
     </row>
     <row r="42" spans="2:24" x14ac:dyDescent="0.3">
@@ -3771,7 +3771,7 @@
       </c>
       <c r="X42" t="str">
         <f t="shared" si="1"/>
-        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (SEQ_TB_SAM_USUARIOS.NEXTVAL, 2, 'LUIS ANTONIO TOVAR ACUÑA', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'luis.antonio', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
+        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (100251487, 2, 'LUIS ANTONIO TOVAR ACUÑA', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'luis.antonio', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
       </c>
     </row>
     <row r="43" spans="2:24" x14ac:dyDescent="0.3">
@@ -3836,7 +3836,7 @@
       </c>
       <c r="X43" t="str">
         <f t="shared" si="1"/>
-        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (SEQ_TB_SAM_USUARIOS.NEXTVAL, 2, 'DANIEL LOPEZ IBARRA', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'daniel.lopez', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
+        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (100014520, 2, 'DANIEL LOPEZ IBARRA', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'daniel.lopez', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
       </c>
     </row>
     <row r="44" spans="2:24" x14ac:dyDescent="0.3">
@@ -3901,7 +3901,7 @@
       </c>
       <c r="X44" t="str">
         <f t="shared" si="1"/>
-        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (SEQ_TB_SAM_USUARIOS.NEXTVAL, 2, 'PABLO RUIZ HERRERA', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'pablo.ruiz', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
+        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (100014960, 2, 'PABLO RUIZ HERRERA', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'pablo.ruiz', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
       </c>
     </row>
     <row r="45" spans="2:24" x14ac:dyDescent="0.3">
@@ -3964,7 +3964,7 @@
       </c>
       <c r="X45" t="str">
         <f t="shared" si="1"/>
-        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (SEQ_TB_SAM_USUARIOS.NEXTVAL, 2, 'ADRIANA GONZALEZ PALACIOS', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'adriana.gonzalez', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
+        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (100015893, 2, 'ADRIANA GONZALEZ PALACIOS', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'adriana.gonzalez', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
       </c>
     </row>
     <row r="46" spans="2:24" x14ac:dyDescent="0.3">
@@ -4025,7 +4025,7 @@
       </c>
       <c r="X46" t="str">
         <f t="shared" si="1"/>
-        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (SEQ_TB_SAM_USUARIOS.NEXTVAL, 2, 'ALVARO ALBERTO OCHOA PICHARDO', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'alvaro.alberto', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
+        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (100017815, 2, 'ALVARO ALBERTO OCHOA PICHARDO', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'alvaro.alberto', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
       </c>
     </row>
     <row r="47" spans="2:24" x14ac:dyDescent="0.3">
@@ -4086,7 +4086,7 @@
       </c>
       <c r="X47" t="str">
         <f t="shared" si="1"/>
-        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (SEQ_TB_SAM_USUARIOS.NEXTVAL, 2, 'JAVIER PACHECO LOPEZ', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'javier.pacheco', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
+        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (100267204, 2, 'JAVIER PACHECO LOPEZ', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'javier.pacheco', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
       </c>
     </row>
     <row r="48" spans="2:24" x14ac:dyDescent="0.3">
@@ -4151,7 +4151,7 @@
       </c>
       <c r="X48" t="str">
         <f t="shared" si="1"/>
-        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (SEQ_TB_SAM_USUARIOS.NEXTVAL, 2, 'BRENDA LIZBETH MONTEAGUDO RAMIREZ', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'brenda.lizbeth', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
+        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (100018765, 2, 'BRENDA LIZBETH MONTEAGUDO RAMIREZ', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'brenda.lizbeth', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
       </c>
     </row>
     <row r="49" spans="2:24" x14ac:dyDescent="0.3">
@@ -4216,7 +4216,7 @@
       </c>
       <c r="X49" t="str">
         <f t="shared" si="1"/>
-        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (SEQ_TB_SAM_USUARIOS.NEXTVAL, 2, 'ROQUE DANIEL TORRES TENORIO', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'roque.daniel', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
+        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (100383461, 2, 'ROQUE DANIEL TORRES TENORIO', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'roque.daniel', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
       </c>
     </row>
     <row r="50" spans="2:24" x14ac:dyDescent="0.3">
@@ -4281,7 +4281,7 @@
       </c>
       <c r="X50" t="str">
         <f t="shared" si="1"/>
-        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (SEQ_TB_SAM_USUARIOS.NEXTVAL, 2, 'KATHIA AIDEE SOLIS ESCOBAR', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'kathia.aidee', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
+        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (100383462, 2, 'KATHIA AIDEE SOLIS ESCOBAR', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'kathia.aidee', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
       </c>
     </row>
     <row r="51" spans="2:24" x14ac:dyDescent="0.3">
@@ -4344,7 +4344,7 @@
       </c>
       <c r="X51" t="str">
         <f t="shared" si="1"/>
-        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (SEQ_TB_SAM_USUARIOS.NEXTVAL, 2, 'VERONICA INES LEON MOCTEZUMA', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'veronica.ines', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
+        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (100018274, 2, 'VERONICA INES LEON MOCTEZUMA', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'veronica.ines', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
       </c>
     </row>
     <row r="52" spans="2:24" x14ac:dyDescent="0.3">
@@ -4409,7 +4409,7 @@
       </c>
       <c r="X52" t="str">
         <f t="shared" si="1"/>
-        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (SEQ_TB_SAM_USUARIOS.NEXTVAL, 2, 'DANIELA ARAIZA MACIAS', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'daniela.araiza', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
+        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (100404797, 2, 'DANIELA ARAIZA MACIAS', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'daniela.araiza', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
       </c>
     </row>
     <row r="53" spans="2:24" x14ac:dyDescent="0.3">
@@ -4474,7 +4474,7 @@
       </c>
       <c r="X53" t="str">
         <f t="shared" si="1"/>
-        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (SEQ_TB_SAM_USUARIOS.NEXTVAL, 2, 'LAURA SARAI NAJERA HERNANDEZ', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'laura.sarai', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
+        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (100533479, 2, 'LAURA SARAI NAJERA HERNANDEZ', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'laura.sarai', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
       </c>
     </row>
     <row r="54" spans="2:24" x14ac:dyDescent="0.3">
@@ -4539,7 +4539,7 @@
       </c>
       <c r="X54" t="str">
         <f t="shared" si="1"/>
-        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (SEQ_TB_SAM_USUARIOS.NEXTVAL, 2, 'ALFREDO MARQUEZ GUTIERREZ', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'alfredo.marquez', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
+        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (100533482, 2, 'ALFREDO MARQUEZ GUTIERREZ', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'alfredo.marquez', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
       </c>
     </row>
     <row r="55" spans="2:24" x14ac:dyDescent="0.3">
@@ -4604,7 +4604,7 @@
       </c>
       <c r="X55" t="str">
         <f t="shared" si="1"/>
-        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (SEQ_TB_SAM_USUARIOS.NEXTVAL, 2, 'RICARDO MENDOZA VILLEGAS', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'ricardo.mendoza', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
+        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (100549886, 2, 'RICARDO MENDOZA VILLEGAS', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'ricardo.mendoza', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
       </c>
     </row>
     <row r="56" spans="2:24" x14ac:dyDescent="0.3">
@@ -4669,7 +4669,7 @@
       </c>
       <c r="X56" t="str">
         <f t="shared" si="1"/>
-        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (SEQ_TB_SAM_USUARIOS.NEXTVAL, 2, 'EDGAR RENDON RAMIREZ', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'edgar.rendon', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
+        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (100664258, 2, 'EDGAR RENDON RAMIREZ', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'edgar.rendon', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
       </c>
     </row>
     <row r="57" spans="2:24" x14ac:dyDescent="0.3">
@@ -4734,7 +4734,7 @@
       </c>
       <c r="X57" t="str">
         <f t="shared" si="1"/>
-        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (SEQ_TB_SAM_USUARIOS.NEXTVAL, 2, 'LUIS IGNACIO HERNANDEZ SANTIAGO', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'luis.ignacio', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
+        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (100696339, 2, 'LUIS IGNACIO HERNANDEZ SANTIAGO', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'luis.ignacio', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
       </c>
     </row>
     <row r="58" spans="2:24" x14ac:dyDescent="0.3">
@@ -4801,7 +4801,7 @@
       </c>
       <c r="X58" t="str">
         <f t="shared" si="1"/>
-        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (SEQ_TB_SAM_USUARIOS.NEXTVAL, 2, 'MIGUEL GONZALEZ MARTINEZ', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'miguel.gonzalez', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
+        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (100854847, 2, 'MIGUEL GONZALEZ MARTINEZ', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'miguel.gonzalez', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
       </c>
     </row>
     <row r="59" spans="2:24" x14ac:dyDescent="0.3">
@@ -4868,7 +4868,7 @@
       </c>
       <c r="X59" t="str">
         <f t="shared" si="1"/>
-        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (SEQ_TB_SAM_USUARIOS.NEXTVAL, 2, 'JOSE ANGEL GASPAR ANDRADE', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'jose.angel', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
+        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (100854852, 2, 'JOSE ANGEL GASPAR ANDRADE', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'jose.angel', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
       </c>
     </row>
     <row r="60" spans="2:24" x14ac:dyDescent="0.3">
@@ -4935,7 +4935,7 @@
       </c>
       <c r="X60" t="str">
         <f t="shared" si="1"/>
-        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (SEQ_TB_SAM_USUARIOS.NEXTVAL, 2, 'JOSE LUIS ZAVALA NAVARRO', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'jose.luis', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
+        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (100854866, 2, 'JOSE LUIS ZAVALA NAVARRO', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'jose.luis', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
       </c>
     </row>
     <row r="61" spans="2:24" x14ac:dyDescent="0.3">
@@ -5002,7 +5002,7 @@
       </c>
       <c r="X61" t="str">
         <f t="shared" si="1"/>
-        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (SEQ_TB_SAM_USUARIOS.NEXTVAL, 2, 'LAURA CECILIA HERNANDEZ FERREYRA', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'laura.cecilia', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
+        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (100861981, 2, 'LAURA CECILIA HERNANDEZ FERREYRA', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'laura.cecilia', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
       </c>
     </row>
     <row r="62" spans="2:24" x14ac:dyDescent="0.3">
@@ -5065,7 +5065,7 @@
       </c>
       <c r="X62" t="str">
         <f t="shared" si="1"/>
-        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (SEQ_TB_SAM_USUARIOS.NEXTVAL, 2, 'ADRIANA VALDOVINOS MACIEL', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'adriana.valdovinos', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
+        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (100861980, 2, 'ADRIANA VALDOVINOS MACIEL', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'adriana.valdovinos', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
       </c>
     </row>
     <row r="63" spans="2:24" x14ac:dyDescent="0.3">
@@ -5130,7 +5130,7 @@
       </c>
       <c r="X63" t="str">
         <f t="shared" si="1"/>
-        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (SEQ_TB_SAM_USUARIOS.NEXTVAL, 2, 'CARLOS IVAN REVILLA FACIO', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'carlos.ivan', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
+        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (100358833, 2, 'CARLOS IVAN REVILLA FACIO', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'carlos.ivan', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
       </c>
     </row>
     <row r="64" spans="2:24" x14ac:dyDescent="0.3">
@@ -5191,7 +5191,7 @@
       </c>
       <c r="X64" t="str">
         <f t="shared" si="1"/>
-        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (SEQ_TB_SAM_USUARIOS.NEXTVAL, 2, 'MARINA JOSA ALMELA', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'marina.josa', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
+        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (100009612, 2, 'MARINA JOSA ALMELA', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'marina.josa', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
       </c>
     </row>
     <row r="65" spans="2:24" x14ac:dyDescent="0.3">
@@ -5252,7 +5252,7 @@
       </c>
       <c r="X65" t="str">
         <f t="shared" si="1"/>
-        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (SEQ_TB_SAM_USUARIOS.NEXTVAL, 2, 'LUZ MARIA DE LA LUZ TELLES DIAZ', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'luz.maria', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
+        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (100327493, 2, 'LUZ MARIA DE LA LUZ TELLES DIAZ', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'luz.maria', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
       </c>
     </row>
     <row r="66" spans="2:24" x14ac:dyDescent="0.3">
@@ -5323,7 +5323,7 @@
       </c>
       <c r="X66" t="str">
         <f t="shared" si="1"/>
-        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (SEQ_TB_SAM_USUARIOS.NEXTVAL, 2, 'GLORIA PAOLA FRAGOSO CONTRERAS', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'gloria.paola', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
+        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (100348704, 2, 'GLORIA PAOLA FRAGOSO CONTRERAS', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'gloria.paola', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
       </c>
     </row>
     <row r="67" spans="2:24" x14ac:dyDescent="0.3">
@@ -5384,7 +5384,7 @@
       </c>
       <c r="X67" t="str">
         <f t="shared" si="1"/>
-        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (SEQ_TB_SAM_USUARIOS.NEXTVAL, 2, 'JAVIER VILCHIS GARCIA', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'javier.vilchis', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
+        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (100695304, 2, 'JAVIER VILCHIS GARCIA', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'javier.vilchis', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
       </c>
     </row>
     <row r="68" spans="2:24" x14ac:dyDescent="0.3">
@@ -5447,7 +5447,7 @@
       </c>
       <c r="X68" t="str">
         <f t="shared" si="1"/>
-        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (SEQ_TB_SAM_USUARIOS.NEXTVAL, 2, 'JUAN PABLO OLIVERA CATRIP', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'juan.pablo', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
+        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (100980209, 2, 'JUAN PABLO OLIVERA CATRIP', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'juan.pablo', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
       </c>
     </row>
     <row r="69" spans="2:24" x14ac:dyDescent="0.3">
@@ -5510,10 +5510,10 @@
       </c>
       <c r="X69" t="str">
         <f t="shared" ref="X69:X92" si="3">"INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,""PASSWORD"",CORREO,DIRECTOR) VALUES (" &amp;
-"SEQ_TB_SAM_USUARIOS.NEXTVAL, 2, '" &amp;
+B69 &amp; ", 2, '" &amp;
 SUBSTITUTE(C69,"'","''") &amp; "', 'MEX Prevencion de PLD', 'Contraloria Normativa', '" &amp;
 SUBSTITUTE(U69,"'","''") &amp; "', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);"</f>
-        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (SEQ_TB_SAM_USUARIOS.NEXTVAL, 2, 'SOFIA GINEBRA ZARANDONA', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'sofia.ginebra', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
+        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (100980197, 2, 'SOFIA GINEBRA ZARANDONA', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'sofia.ginebra', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
       </c>
     </row>
     <row r="70" spans="2:24" x14ac:dyDescent="0.3">
@@ -5576,7 +5576,7 @@
       </c>
       <c r="X70" t="str">
         <f t="shared" si="3"/>
-        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (SEQ_TB_SAM_USUARIOS.NEXTVAL, 2, 'JESUS PATRICIO AVALOS DIAZ BARREIRO', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'jesus.patricio', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
+        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (100980202, 2, 'JESUS PATRICIO AVALOS DIAZ BARREIRO', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'jesus.patricio', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
       </c>
     </row>
     <row r="71" spans="2:24" x14ac:dyDescent="0.3">
@@ -5639,7 +5639,7 @@
       </c>
       <c r="X71" t="str">
         <f t="shared" si="3"/>
-        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (SEQ_TB_SAM_USUARIOS.NEXTVAL, 2, 'MAURICIO FABIAN RODRIGUEZ JUAREZ', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'mauricio.fabian', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
+        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (100980206, 2, 'MAURICIO FABIAN RODRIGUEZ JUAREZ', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'mauricio.fabian', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
       </c>
     </row>
     <row r="72" spans="2:24" x14ac:dyDescent="0.3">
@@ -5708,7 +5708,7 @@
       </c>
       <c r="X72" t="str">
         <f t="shared" si="3"/>
-        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (SEQ_TB_SAM_USUARIOS.NEXTVAL, 2, 'JOSE JUAN LOPEZ PIÑERO', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'jose.juan', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
+        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (100854856, 2, 'JOSE JUAN LOPEZ PIÑERO', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'jose.juan', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
       </c>
     </row>
     <row r="73" spans="2:24" x14ac:dyDescent="0.3">
@@ -5775,7 +5775,7 @@
       </c>
       <c r="X73" t="str">
         <f t="shared" si="3"/>
-        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (SEQ_TB_SAM_USUARIOS.NEXTVAL, 2, 'MIGUEL ANGEL CARO DEL CASTILLO TREVIÑO', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'miguel.angel', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
+        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (100002387, 2, 'MIGUEL ANGEL CARO DEL CASTILLO TREVIÑO', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'miguel.angel', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
       </c>
     </row>
     <row r="74" spans="2:24" x14ac:dyDescent="0.3">
@@ -5842,7 +5842,7 @@
       </c>
       <c r="X74" t="str">
         <f t="shared" si="3"/>
-        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (SEQ_TB_SAM_USUARIOS.NEXTVAL, 2, 'OLIVER IGOR YAÑEZ GONZALEZ', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'oliver.igor', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
+        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (100003523, 2, 'OLIVER IGOR YAÑEZ GONZALEZ', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'oliver.igor', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
       </c>
     </row>
     <row r="75" spans="2:24" x14ac:dyDescent="0.3">
@@ -5907,7 +5907,7 @@
       </c>
       <c r="X75" t="str">
         <f t="shared" si="3"/>
-        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (SEQ_TB_SAM_USUARIOS.NEXTVAL, 2, 'MARIA DEL SOCORRO RAMIREZ RICARDEZ', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'maria.del', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
+        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (100008885, 2, 'MARIA DEL SOCORRO RAMIREZ RICARDEZ', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'maria.del', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
       </c>
     </row>
     <row r="76" spans="2:24" x14ac:dyDescent="0.3">
@@ -5974,7 +5974,7 @@
       </c>
       <c r="X76" t="str">
         <f t="shared" si="3"/>
-        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (SEQ_TB_SAM_USUARIOS.NEXTVAL, 2, 'MIKHAIL MORA APONTE', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'mikhail.mora', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
+        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (100009187, 2, 'MIKHAIL MORA APONTE', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'mikhail.mora', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
       </c>
     </row>
     <row r="77" spans="2:24" x14ac:dyDescent="0.3">
@@ -6039,7 +6039,7 @@
       </c>
       <c r="X77" t="str">
         <f t="shared" si="3"/>
-        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (SEQ_TB_SAM_USUARIOS.NEXTVAL, 2, 'BRENDA DANIELA VELASCO ROJAS', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'brenda.daniela', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
+        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (100396371, 2, 'BRENDA DANIELA VELASCO ROJAS', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'brenda.daniela', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
       </c>
     </row>
     <row r="78" spans="2:24" x14ac:dyDescent="0.3">
@@ -6106,7 +6106,7 @@
       </c>
       <c r="X78" t="str">
         <f t="shared" si="3"/>
-        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (SEQ_TB_SAM_USUARIOS.NEXTVAL, 2, 'ELIZANDRA CARDOSO AZCOITIA', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'elizandra.cardoso', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
+        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (100539130, 2, 'ELIZANDRA CARDOSO AZCOITIA', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'elizandra.cardoso', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
       </c>
     </row>
     <row r="79" spans="2:24" x14ac:dyDescent="0.3">
@@ -6171,7 +6171,7 @@
       </c>
       <c r="X79" t="str">
         <f t="shared" si="3"/>
-        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (SEQ_TB_SAM_USUARIOS.NEXTVAL, 2, 'JULIANA PEREZ MARTIN DEL CAMPO', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'juliana.perez', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
+        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (100018885, 2, 'JULIANA PEREZ MARTIN DEL CAMPO', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'juliana.perez', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
       </c>
     </row>
     <row r="80" spans="2:24" x14ac:dyDescent="0.3">
@@ -6232,7 +6232,7 @@
       </c>
       <c r="X80" t="str">
         <f t="shared" si="3"/>
-        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (SEQ_TB_SAM_USUARIOS.NEXTVAL, 2, 'DIEGO MARTINEZ CORTES', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'diego.martinez', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
+        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (100005847, 2, 'DIEGO MARTINEZ CORTES', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'diego.martinez', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
       </c>
     </row>
     <row r="81" spans="2:24" x14ac:dyDescent="0.3">
@@ -6295,7 +6295,7 @@
       </c>
       <c r="X81" t="str">
         <f t="shared" si="3"/>
-        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (SEQ_TB_SAM_USUARIOS.NEXTVAL, 2, 'YOLANDA PERDOMO JIMENEZ', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'yolanda.perdomo', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
+        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (100018889, 2, 'YOLANDA PERDOMO JIMENEZ', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'yolanda.perdomo', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
       </c>
     </row>
     <row r="82" spans="2:24" x14ac:dyDescent="0.3">
@@ -6358,7 +6358,7 @@
       </c>
       <c r="X82" t="str">
         <f t="shared" si="3"/>
-        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (SEQ_TB_SAM_USUARIOS.NEXTVAL, 2, 'MERCEDES SANCHEZ REYES RETANA', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'mercedes.sanchez', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
+        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (100546470, 2, 'MERCEDES SANCHEZ REYES RETANA', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'mercedes.sanchez', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
       </c>
     </row>
     <row r="83" spans="2:24" x14ac:dyDescent="0.3">
@@ -6423,7 +6423,7 @@
       </c>
       <c r="X83" t="str">
         <f t="shared" si="3"/>
-        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (SEQ_TB_SAM_USUARIOS.NEXTVAL, 2, 'ALEJANDRA MARTINEZ NIETO', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'alejandra.martinez', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
+        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (100550630, 2, 'ALEJANDRA MARTINEZ NIETO', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'alejandra.martinez', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
       </c>
     </row>
     <row r="84" spans="2:24" x14ac:dyDescent="0.3">
@@ -6492,7 +6492,7 @@
       </c>
       <c r="X84" t="str">
         <f t="shared" si="3"/>
-        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (SEQ_TB_SAM_USUARIOS.NEXTVAL, 2, 'JULIAN GOMEZ FAUSTINO', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'julian.gomez', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
+        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (100015156, 2, 'JULIAN GOMEZ FAUSTINO', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'julian.gomez', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
       </c>
     </row>
     <row r="85" spans="2:24" x14ac:dyDescent="0.3">
@@ -6559,7 +6559,7 @@
       </c>
       <c r="X85" t="str">
         <f t="shared" si="3"/>
-        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (SEQ_TB_SAM_USUARIOS.NEXTVAL, 2, 'CESAR ALEJANDRO ARAIZA ITURRIA', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'cesar.alejandro', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
+        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (100019199, 2, 'CESAR ALEJANDRO ARAIZA ITURRIA', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'cesar.alejandro', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
       </c>
     </row>
     <row r="86" spans="2:24" x14ac:dyDescent="0.3">
@@ -6626,7 +6626,7 @@
       </c>
       <c r="X86" t="str">
         <f t="shared" si="3"/>
-        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (SEQ_TB_SAM_USUARIOS.NEXTVAL, 2, 'MARIANA CHAVEZ GARCIA', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'mariana.chavez', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
+        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (100404799, 2, 'MARIANA CHAVEZ GARCIA', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'mariana.chavez', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
       </c>
     </row>
     <row r="87" spans="2:24" x14ac:dyDescent="0.3">
@@ -6693,7 +6693,7 @@
       </c>
       <c r="X87" t="str">
         <f t="shared" si="3"/>
-        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (SEQ_TB_SAM_USUARIOS.NEXTVAL, 2, 'LUIS ALFONSO VILLEGAS MORENO', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'luis.alfonso', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
+        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (100019201, 2, 'LUIS ALFONSO VILLEGAS MORENO', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'luis.alfonso', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
       </c>
     </row>
     <row r="88" spans="2:24" x14ac:dyDescent="0.3">
@@ -6760,7 +6760,7 @@
       </c>
       <c r="X88" t="str">
         <f t="shared" si="3"/>
-        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (SEQ_TB_SAM_USUARIOS.NEXTVAL, 2, 'JESUS GABRIEL SANCHEZ CANALES', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'jesus.gabriel', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
+        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (100462092, 2, 'JESUS GABRIEL SANCHEZ CANALES', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'jesus.gabriel', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
       </c>
     </row>
     <row r="89" spans="2:24" x14ac:dyDescent="0.3">
@@ -6829,7 +6829,7 @@
       </c>
       <c r="X89" t="str">
         <f t="shared" si="3"/>
-        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (SEQ_TB_SAM_USUARIOS.NEXTVAL, 2, 'PERLA CRISTINA GONZALEZ ESPINOSA', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'perla.cristina', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
+        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (100861987, 2, 'PERLA CRISTINA GONZALEZ ESPINOSA', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'perla.cristina', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
       </c>
     </row>
     <row r="90" spans="2:24" x14ac:dyDescent="0.3">
@@ -6896,7 +6896,7 @@
       </c>
       <c r="X90" t="str">
         <f t="shared" si="3"/>
-        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (SEQ_TB_SAM_USUARIOS.NEXTVAL, 2, 'KATERINE ITZEL JIMENEZ MIGUEL', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'katerine.itzel', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
+        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (100664282, 2, 'KATERINE ITZEL JIMENEZ MIGUEL', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'katerine.itzel', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
       </c>
     </row>
     <row r="91" spans="2:24" x14ac:dyDescent="0.3">
@@ -6957,7 +6957,7 @@
       </c>
       <c r="X91" t="str">
         <f t="shared" si="3"/>
-        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (SEQ_TB_SAM_USUARIOS.NEXTVAL, 2, 'MARIA DEL PILAR CERRILLA NORIEGA', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'maria.del', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
+        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (100019224, 2, 'MARIA DEL PILAR CERRILLA NORIEGA', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'maria.del', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
       </c>
     </row>
     <row r="92" spans="2:24" x14ac:dyDescent="0.3">
@@ -7024,7 +7024,7 @@
       </c>
       <c r="X92" t="str">
         <f t="shared" si="3"/>
-        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (SEQ_TB_SAM_USUARIOS.NEXTVAL, 2, 'FRANCISCO JOSE BRUNET NAVARRETE', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'francisco.jose', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
+        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (100561793, 2, 'FRANCISCO JOSE BRUNET NAVARRETE', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'francisco.jose', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
       </c>
     </row>
     <row r="93" spans="2:24" x14ac:dyDescent="0.3">

--- a/Archivos_Compartidos/Cursos RH/Copia de Listado para cursos normativos 2025.xlsx
+++ b/Archivos_Compartidos/Cursos RH/Copia de Listado para cursos normativos 2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SAMMX\Documents\GitHub\SAM_Santander\Archivos_Compartidos\Cursos RH\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://santandernet-my.sharepoint.com/personal/n854611_corp_santanderam_com/Documents/Documentos/GitHub/SAM_Santander/SAM_Santander/Archivos_Compartidos/Cursos RH/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CEB8F394-1A8B-4C4D-9F84-CCF5EE912074}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="4" documentId="13_ncr:1_{CEB8F394-1A8B-4C4D-9F84-CCF5EE912074}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6B2C252A-B25A-4F98-B23B-58F02FEDEC45}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{FF6FD13D-7CB9-4391-90CB-CB63A01A4952}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15270" xr2:uid="{FF6FD13D-7CB9-4391-90CB-CB63A01A4952}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -1095,19 +1095,19 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AA6F91F3-8D57-4281-84D3-F5D3AFC92A1D}">
   <dimension ref="B2:X93"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="3.109375" customWidth="1"/>
+    <col min="1" max="1" width="3.140625" customWidth="1"/>
     <col min="2" max="2" width="12" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="33.44140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.109375" hidden="1" customWidth="1"/>
-    <col min="6" max="17" width="10.88671875" hidden="1" customWidth="1"/>
+    <col min="3" max="3" width="33.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.140625" hidden="1" customWidth="1"/>
+    <col min="6" max="17" width="10.85546875" hidden="1" customWidth="1"/>
     <col min="18" max="19" width="0" hidden="1" customWidth="1"/>
     <col min="20" max="20" width="18" hidden="1" customWidth="1"/>
     <col min="21" max="21" width="18" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:24" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:24" x14ac:dyDescent="0.25">
       <c r="F2" s="8" t="s">
         <v>0</v>
       </c>
@@ -1119,7 +1119,7 @@
       <c r="L2" s="8"/>
       <c r="M2" s="8"/>
     </row>
-    <row r="3" spans="2:24" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B3" s="1" t="s">
         <v>1</v>
       </c>
@@ -1175,7 +1175,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="4" spans="2:24" ht="14.1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:24" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B4" s="2">
         <v>100922046</v>
       </c>
@@ -1251,7 +1251,7 @@
         <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (SEQ_TB_SAM_USUARIOS.NEXTVAL, 2, 'ALEJANDRO MARTINEZ FERES', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'alejandro.martinez', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
       </c>
     </row>
-    <row r="5" spans="2:24" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B5" s="2">
         <v>100004927</v>
       </c>
@@ -1307,7 +1307,7 @@
         <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (SEQ_TB_SAM_USUARIOS.NEXTVAL, 2, 'VIANCA ROSALBA ESPINOSA ROMAN', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'vianca.rosalba', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
       </c>
     </row>
-    <row r="6" spans="2:24" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B6" s="2">
         <v>100500870</v>
       </c>
@@ -1362,7 +1362,7 @@
         <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (SEQ_TB_SAM_USUARIOS.NEXTVAL, 2, 'NOEMI NATALY TELLEZ CORREA', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'noemi.nataly', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
       </c>
     </row>
-    <row r="7" spans="2:24" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B7" s="2">
         <v>100018886</v>
       </c>
@@ -1426,7 +1426,7 @@
         <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (SEQ_TB_SAM_USUARIOS.NEXTVAL, 2, 'MARIAELENA ALAMILLA ALVAREZ', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'mariaelena.alamilla', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
       </c>
     </row>
-    <row r="8" spans="2:24" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B8" s="2">
         <v>100675883</v>
       </c>
@@ -1490,7 +1490,7 @@
         <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (SEQ_TB_SAM_USUARIOS.NEXTVAL, 2, 'DINA ROMAN LIZARRAGA', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'dina.roman', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
       </c>
     </row>
-    <row r="9" spans="2:24" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B9" s="2">
         <v>100572137</v>
       </c>
@@ -1554,7 +1554,7 @@
         <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (SEQ_TB_SAM_USUARIOS.NEXTVAL, 2, 'ALEJANDRO PEREZ JIMENEZ', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'alejandro.perez', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
       </c>
     </row>
-    <row r="10" spans="2:24" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B10" s="2">
         <v>100985454</v>
       </c>
@@ -1621,7 +1621,7 @@
         <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (SEQ_TB_SAM_USUARIOS.NEXTVAL, 2, 'ALEJANDRO CALANDA MORALES', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'alejandro.calanda', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
       </c>
     </row>
-    <row r="11" spans="2:24" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B11" s="2">
         <v>100677152</v>
       </c>
@@ -1685,7 +1685,7 @@
         <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (SEQ_TB_SAM_USUARIOS.NEXTVAL, 2, 'CARLOS AGUAYO SANCHEZ', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'carlos.aguayo', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
       </c>
     </row>
-    <row r="12" spans="2:24" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B12" s="2">
         <v>100000263</v>
       </c>
@@ -1754,7 +1754,7 @@
         <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (SEQ_TB_SAM_USUARIOS.NEXTVAL, 2, 'ADRIANA TAPIA GONZALEZ', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'adriana.tapia', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
       </c>
     </row>
-    <row r="13" spans="2:24" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B13" s="2">
         <v>100854877</v>
       </c>
@@ -1825,7 +1825,7 @@
         <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (SEQ_TB_SAM_USUARIOS.NEXTVAL, 2, 'JOSE FERNANDO PUENTE PLATA', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'jose.fernando', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
       </c>
     </row>
-    <row r="14" spans="2:24" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B14" s="2">
         <v>100019203</v>
       </c>
@@ -1888,7 +1888,7 @@
         <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (SEQ_TB_SAM_USUARIOS.NEXTVAL, 2, 'CARLOS RAMON SANDOVAL MINERO', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'carlos.ramon', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
       </c>
     </row>
-    <row r="15" spans="2:24" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B15" s="2">
         <v>100019200</v>
       </c>
@@ -1951,7 +1951,7 @@
         <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (SEQ_TB_SAM_USUARIOS.NEXTVAL, 2, 'GRACIELA AGUILAR MARTINEZ', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'graciela.aguilar', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
       </c>
     </row>
-    <row r="16" spans="2:24" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B16" s="2">
         <v>100019204</v>
       </c>
@@ -2014,7 +2014,7 @@
         <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (SEQ_TB_SAM_USUARIOS.NEXTVAL, 2, 'ALEJANDRO CESAR SANCHEZ CERVANTES', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'alejandro.cesar', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
       </c>
     </row>
-    <row r="17" spans="2:24" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B17" s="2">
         <v>100327492</v>
       </c>
@@ -2077,7 +2077,7 @@
         <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (SEQ_TB_SAM_USUARIOS.NEXTVAL, 2, 'LEONARDO DAVID PLATA MARTINEZ', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'leonardo.david', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
       </c>
     </row>
-    <row r="18" spans="2:24" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B18" s="2">
         <v>100327494</v>
       </c>
@@ -2136,7 +2136,7 @@
         <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (SEQ_TB_SAM_USUARIOS.NEXTVAL, 2, 'VERONICA MARTELL ESPINOSA', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'veronica.martell', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
       </c>
     </row>
-    <row r="19" spans="2:24" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B19" s="2">
         <v>100000056</v>
       </c>
@@ -2199,7 +2199,7 @@
         <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (SEQ_TB_SAM_USUARIOS.NEXTVAL, 2, 'CARLOS ALBERTO RAMIREZ JUAREZ', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'carlos.alberto', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
       </c>
     </row>
-    <row r="20" spans="2:24" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B20" s="2">
         <v>100384479</v>
       </c>
@@ -2262,7 +2262,7 @@
         <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (SEQ_TB_SAM_USUARIOS.NEXTVAL, 2, 'OCTAVIO AUGUSTO DIAZ LOPEZ', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'octavio.augusto', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
       </c>
     </row>
-    <row r="21" spans="2:24" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B21" s="2">
         <v>100545348</v>
       </c>
@@ -2325,7 +2325,7 @@
         <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (SEQ_TB_SAM_USUARIOS.NEXTVAL, 2, 'ANGEL DANIEL RUIZ ACUÑA', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'angel.daniel', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
       </c>
     </row>
-    <row r="22" spans="2:24" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B22" s="2">
         <v>100003814</v>
       </c>
@@ -2394,7 +2394,7 @@
         <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (SEQ_TB_SAM_USUARIOS.NEXTVAL, 2, 'SARA MALDONADO VILCHIS', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'sara.maldonado', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
       </c>
     </row>
-    <row r="23" spans="2:24" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B23" s="2">
         <v>100019864</v>
       </c>
@@ -2463,7 +2463,7 @@
         <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (SEQ_TB_SAM_USUARIOS.NEXTVAL, 2, 'PAOLA MARIANA DOMINGUEZ MAS', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'paola.mariana', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
       </c>
     </row>
-    <row r="24" spans="2:24" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B24" s="2">
         <v>100018887</v>
       </c>
@@ -2532,7 +2532,7 @@
         <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (SEQ_TB_SAM_USUARIOS.NEXTVAL, 2, 'ANDRES IGNACIO MUÑETON RODRIGUEZ', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'andres.ignacio', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
       </c>
     </row>
-    <row r="25" spans="2:24" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B25" s="2">
         <v>100018888</v>
       </c>
@@ -2601,7 +2601,7 @@
         <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (SEQ_TB_SAM_USUARIOS.NEXTVAL, 2, 'JOSE URIBE CEDILLO', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'jose.uribe', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
       </c>
     </row>
-    <row r="26" spans="2:24" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B26" s="2">
         <v>100015250</v>
       </c>
@@ -2670,7 +2670,7 @@
         <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (SEQ_TB_SAM_USUARIOS.NEXTVAL, 2, 'MARCOS CAMACHO PARADA', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'marcos.camacho', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
       </c>
     </row>
-    <row r="27" spans="2:24" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B27" s="2">
         <v>100018636</v>
       </c>
@@ -2739,7 +2739,7 @@
         <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (SEQ_TB_SAM_USUARIOS.NEXTVAL, 2, 'LUIS ARTURO FLORES SANCHEZ', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'luis.arturo', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
       </c>
     </row>
-    <row r="28" spans="2:24" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B28" s="2">
         <v>100009066</v>
       </c>
@@ -2808,7 +2808,7 @@
         <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (SEQ_TB_SAM_USUARIOS.NEXTVAL, 2, 'RAFAEL BUERBA GOMEZ', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'rafael.buerba', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
       </c>
     </row>
-    <row r="29" spans="2:24" x14ac:dyDescent="0.3">
+    <row r="29" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B29" s="2">
         <v>100401809</v>
       </c>
@@ -2877,7 +2877,7 @@
         <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (SEQ_TB_SAM_USUARIOS.NEXTVAL, 2, 'JUAN PABLO ARIZALETA BARQUIN', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'juan.pablo', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
       </c>
     </row>
-    <row r="30" spans="2:24" x14ac:dyDescent="0.3">
+    <row r="30" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B30" s="2">
         <v>100416647</v>
       </c>
@@ -2946,7 +2946,7 @@
         <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (SEQ_TB_SAM_USUARIOS.NEXTVAL, 2, 'ALEJANDRO LAVIN TREVIÑO', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'alejandro.lavin', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
       </c>
     </row>
-    <row r="31" spans="2:24" x14ac:dyDescent="0.3">
+    <row r="31" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B31" s="2">
         <v>100253304</v>
       </c>
@@ -3015,7 +3015,7 @@
         <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (SEQ_TB_SAM_USUARIOS.NEXTVAL, 2, 'RAFAEL BENJAMIN VEGA ORTEGA', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'rafael.benjamin', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
       </c>
     </row>
-    <row r="32" spans="2:24" x14ac:dyDescent="0.3">
+    <row r="32" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B32" s="2">
         <v>100523258</v>
       </c>
@@ -3084,7 +3084,7 @@
         <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (SEQ_TB_SAM_USUARIOS.NEXTVAL, 2, 'LUIS FERNANDO YANCE CHARRIA', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'luis.fernando', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
       </c>
     </row>
-    <row r="33" spans="2:24" x14ac:dyDescent="0.3">
+    <row r="33" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B33" s="2">
         <v>100016803</v>
       </c>
@@ -3153,7 +3153,7 @@
         <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (SEQ_TB_SAM_USUARIOS.NEXTVAL, 2, 'MAURO VAZQUEZ FLORES', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'mauro.vazquez', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
       </c>
     </row>
-    <row r="34" spans="2:24" x14ac:dyDescent="0.3">
+    <row r="34" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B34" s="2">
         <v>100574048</v>
       </c>
@@ -3222,7 +3222,7 @@
         <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (SEQ_TB_SAM_USUARIOS.NEXTVAL, 2, 'JORGE OMAR VARGAS VEGA', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'jorge.omar', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
       </c>
     </row>
-    <row r="35" spans="2:24" x14ac:dyDescent="0.3">
+    <row r="35" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B35" s="2">
         <v>100613246</v>
       </c>
@@ -3291,7 +3291,7 @@
         <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (SEQ_TB_SAM_USUARIOS.NEXTVAL, 2, 'BERNARDO MALPICA DONDE', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'bernardo.malpica', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
       </c>
     </row>
-    <row r="36" spans="2:24" x14ac:dyDescent="0.3">
+    <row r="36" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B36" s="2">
         <v>100854836</v>
       </c>
@@ -3362,7 +3362,7 @@
         <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (SEQ_TB_SAM_USUARIOS.NEXTVAL, 2, 'MONICA BARRIGA ROBLES', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'monica.barriga', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
       </c>
     </row>
-    <row r="37" spans="2:24" x14ac:dyDescent="0.3">
+    <row r="37" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B37" s="2">
         <v>100861962</v>
       </c>
@@ -3433,7 +3433,7 @@
         <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (SEQ_TB_SAM_USUARIOS.NEXTVAL, 2, 'PATRICIA MARTINEZ GUTIERREZ', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'patricia.martinez', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
       </c>
     </row>
-    <row r="38" spans="2:24" x14ac:dyDescent="0.3">
+    <row r="38" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B38" s="2">
         <v>100362615</v>
       </c>
@@ -3502,7 +3502,7 @@
         <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (SEQ_TB_SAM_USUARIOS.NEXTVAL, 2, 'BRENDA GISELL GIRON MAY', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'brenda.gisell', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
       </c>
     </row>
-    <row r="39" spans="2:24" x14ac:dyDescent="0.3">
+    <row r="39" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B39" s="2">
         <v>100591294</v>
       </c>
@@ -3571,7 +3571,7 @@
         <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (SEQ_TB_SAM_USUARIOS.NEXTVAL, 2, 'SANTIAGO PALAZUELOS VON BERTRAB', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'santiago.palazuelos', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
       </c>
     </row>
-    <row r="40" spans="2:24" x14ac:dyDescent="0.3">
+    <row r="40" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B40" s="2">
         <v>100685301</v>
       </c>
@@ -3640,7 +3640,7 @@
         <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (SEQ_TB_SAM_USUARIOS.NEXTVAL, 2, 'RODRIGO EDUARDO SANHUEZA VEGA', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'rodrigo.eduardo', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
       </c>
     </row>
-    <row r="41" spans="2:24" x14ac:dyDescent="0.3">
+    <row r="41" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B41" s="2">
         <v>100559745</v>
       </c>
@@ -3709,7 +3709,7 @@
         <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (SEQ_TB_SAM_USUARIOS.NEXTVAL, 2, 'NADINE ORNELAS ESQUINCA', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'nadine.ornelas', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
       </c>
     </row>
-    <row r="42" spans="2:24" x14ac:dyDescent="0.3">
+    <row r="42" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B42" s="2">
         <v>100251487</v>
       </c>
@@ -3774,7 +3774,7 @@
         <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (SEQ_TB_SAM_USUARIOS.NEXTVAL, 2, 'LUIS ANTONIO TOVAR ACUÑA', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'luis.antonio', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
       </c>
     </row>
-    <row r="43" spans="2:24" x14ac:dyDescent="0.3">
+    <row r="43" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B43" s="2">
         <v>100014520</v>
       </c>
@@ -3839,7 +3839,7 @@
         <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (SEQ_TB_SAM_USUARIOS.NEXTVAL, 2, 'DANIEL LOPEZ IBARRA', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'daniel.lopez', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
       </c>
     </row>
-    <row r="44" spans="2:24" x14ac:dyDescent="0.3">
+    <row r="44" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B44" s="2">
         <v>100014960</v>
       </c>
@@ -3904,7 +3904,7 @@
         <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (SEQ_TB_SAM_USUARIOS.NEXTVAL, 2, 'PABLO RUIZ HERRERA', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'pablo.ruiz', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
       </c>
     </row>
-    <row r="45" spans="2:24" x14ac:dyDescent="0.3">
+    <row r="45" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B45" s="2">
         <v>100015893</v>
       </c>
@@ -3967,7 +3967,7 @@
         <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (SEQ_TB_SAM_USUARIOS.NEXTVAL, 2, 'ADRIANA GONZALEZ PALACIOS', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'adriana.gonzalez', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
       </c>
     </row>
-    <row r="46" spans="2:24" x14ac:dyDescent="0.3">
+    <row r="46" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B46" s="2">
         <v>100017815</v>
       </c>
@@ -4028,7 +4028,7 @@
         <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (SEQ_TB_SAM_USUARIOS.NEXTVAL, 2, 'ALVARO ALBERTO OCHOA PICHARDO', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'alvaro.alberto', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
       </c>
     </row>
-    <row r="47" spans="2:24" x14ac:dyDescent="0.3">
+    <row r="47" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B47" s="2">
         <v>100267204</v>
       </c>
@@ -4089,7 +4089,7 @@
         <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (SEQ_TB_SAM_USUARIOS.NEXTVAL, 2, 'JAVIER PACHECO LOPEZ', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'javier.pacheco', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
       </c>
     </row>
-    <row r="48" spans="2:24" x14ac:dyDescent="0.3">
+    <row r="48" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B48" s="2">
         <v>100018765</v>
       </c>
@@ -4154,7 +4154,7 @@
         <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (SEQ_TB_SAM_USUARIOS.NEXTVAL, 2, 'BRENDA LIZBETH MONTEAGUDO RAMIREZ', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'brenda.lizbeth', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
       </c>
     </row>
-    <row r="49" spans="2:24" x14ac:dyDescent="0.3">
+    <row r="49" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B49" s="2">
         <v>100383461</v>
       </c>
@@ -4219,7 +4219,7 @@
         <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (SEQ_TB_SAM_USUARIOS.NEXTVAL, 2, 'ROQUE DANIEL TORRES TENORIO', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'roque.daniel', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
       </c>
     </row>
-    <row r="50" spans="2:24" x14ac:dyDescent="0.3">
+    <row r="50" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B50" s="2">
         <v>100383462</v>
       </c>
@@ -4284,7 +4284,7 @@
         <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (SEQ_TB_SAM_USUARIOS.NEXTVAL, 2, 'KATHIA AIDEE SOLIS ESCOBAR', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'kathia.aidee', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
       </c>
     </row>
-    <row r="51" spans="2:24" x14ac:dyDescent="0.3">
+    <row r="51" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B51" s="2">
         <v>100018274</v>
       </c>
@@ -4347,7 +4347,7 @@
         <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (SEQ_TB_SAM_USUARIOS.NEXTVAL, 2, 'VERONICA INES LEON MOCTEZUMA', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'veronica.ines', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
       </c>
     </row>
-    <row r="52" spans="2:24" x14ac:dyDescent="0.3">
+    <row r="52" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B52" s="2">
         <v>100404797</v>
       </c>
@@ -4412,7 +4412,7 @@
         <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (SEQ_TB_SAM_USUARIOS.NEXTVAL, 2, 'DANIELA ARAIZA MACIAS', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'daniela.araiza', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
       </c>
     </row>
-    <row r="53" spans="2:24" x14ac:dyDescent="0.3">
+    <row r="53" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B53" s="2">
         <v>100533479</v>
       </c>
@@ -4477,7 +4477,7 @@
         <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (SEQ_TB_SAM_USUARIOS.NEXTVAL, 2, 'LAURA SARAI NAJERA HERNANDEZ', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'laura.sarai', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
       </c>
     </row>
-    <row r="54" spans="2:24" x14ac:dyDescent="0.3">
+    <row r="54" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B54" s="2">
         <v>100533482</v>
       </c>
@@ -4542,7 +4542,7 @@
         <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (SEQ_TB_SAM_USUARIOS.NEXTVAL, 2, 'ALFREDO MARQUEZ GUTIERREZ', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'alfredo.marquez', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
       </c>
     </row>
-    <row r="55" spans="2:24" x14ac:dyDescent="0.3">
+    <row r="55" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B55" s="2">
         <v>100549886</v>
       </c>
@@ -4607,7 +4607,7 @@
         <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (SEQ_TB_SAM_USUARIOS.NEXTVAL, 2, 'RICARDO MENDOZA VILLEGAS', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'ricardo.mendoza', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
       </c>
     </row>
-    <row r="56" spans="2:24" x14ac:dyDescent="0.3">
+    <row r="56" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B56" s="2">
         <v>100664258</v>
       </c>
@@ -4672,7 +4672,7 @@
         <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (SEQ_TB_SAM_USUARIOS.NEXTVAL, 2, 'EDGAR RENDON RAMIREZ', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'edgar.rendon', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
       </c>
     </row>
-    <row r="57" spans="2:24" x14ac:dyDescent="0.3">
+    <row r="57" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B57" s="2">
         <v>100696339</v>
       </c>
@@ -4737,7 +4737,7 @@
         <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (SEQ_TB_SAM_USUARIOS.NEXTVAL, 2, 'LUIS IGNACIO HERNANDEZ SANTIAGO', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'luis.ignacio', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
       </c>
     </row>
-    <row r="58" spans="2:24" x14ac:dyDescent="0.3">
+    <row r="58" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B58" s="2">
         <v>100854847</v>
       </c>
@@ -4804,7 +4804,7 @@
         <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (SEQ_TB_SAM_USUARIOS.NEXTVAL, 2, 'MIGUEL GONZALEZ MARTINEZ', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'miguel.gonzalez', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
       </c>
     </row>
-    <row r="59" spans="2:24" x14ac:dyDescent="0.3">
+    <row r="59" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B59" s="2">
         <v>100854852</v>
       </c>
@@ -4871,7 +4871,7 @@
         <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (SEQ_TB_SAM_USUARIOS.NEXTVAL, 2, 'JOSE ANGEL GASPAR ANDRADE', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'jose.angel', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
       </c>
     </row>
-    <row r="60" spans="2:24" x14ac:dyDescent="0.3">
+    <row r="60" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B60" s="2">
         <v>100854866</v>
       </c>
@@ -4938,7 +4938,7 @@
         <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (SEQ_TB_SAM_USUARIOS.NEXTVAL, 2, 'JOSE LUIS ZAVALA NAVARRO', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'jose.luis', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
       </c>
     </row>
-    <row r="61" spans="2:24" x14ac:dyDescent="0.3">
+    <row r="61" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B61" s="2">
         <v>100861981</v>
       </c>
@@ -5005,7 +5005,7 @@
         <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (SEQ_TB_SAM_USUARIOS.NEXTVAL, 2, 'LAURA CECILIA HERNANDEZ FERREYRA', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'laura.cecilia', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
       </c>
     </row>
-    <row r="62" spans="2:24" x14ac:dyDescent="0.3">
+    <row r="62" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B62" s="2">
         <v>100861980</v>
       </c>
@@ -5068,7 +5068,7 @@
         <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (SEQ_TB_SAM_USUARIOS.NEXTVAL, 2, 'ADRIANA VALDOVINOS MACIEL', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'adriana.valdovinos', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
       </c>
     </row>
-    <row r="63" spans="2:24" x14ac:dyDescent="0.3">
+    <row r="63" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B63" s="2">
         <v>100358833</v>
       </c>
@@ -5133,7 +5133,7 @@
         <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (SEQ_TB_SAM_USUARIOS.NEXTVAL, 2, 'CARLOS IVAN REVILLA FACIO', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'carlos.ivan', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
       </c>
     </row>
-    <row r="64" spans="2:24" x14ac:dyDescent="0.3">
+    <row r="64" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B64" s="2">
         <v>100009612</v>
       </c>
@@ -5194,7 +5194,7 @@
         <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (SEQ_TB_SAM_USUARIOS.NEXTVAL, 2, 'MARINA JOSA ALMELA', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'marina.josa', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
       </c>
     </row>
-    <row r="65" spans="2:24" x14ac:dyDescent="0.3">
+    <row r="65" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B65" s="2">
         <v>100327493</v>
       </c>
@@ -5255,7 +5255,7 @@
         <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (SEQ_TB_SAM_USUARIOS.NEXTVAL, 2, 'LUZ MARIA DE LA LUZ TELLES DIAZ', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'luz.maria', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
       </c>
     </row>
-    <row r="66" spans="2:24" x14ac:dyDescent="0.3">
+    <row r="66" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B66" s="2">
         <v>100348704</v>
       </c>
@@ -5326,7 +5326,7 @@
         <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (SEQ_TB_SAM_USUARIOS.NEXTVAL, 2, 'GLORIA PAOLA FRAGOSO CONTRERAS', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'gloria.paola', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
       </c>
     </row>
-    <row r="67" spans="2:24" x14ac:dyDescent="0.3">
+    <row r="67" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B67" s="2">
         <v>100695304</v>
       </c>
@@ -5387,7 +5387,7 @@
         <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (SEQ_TB_SAM_USUARIOS.NEXTVAL, 2, 'JAVIER VILCHIS GARCIA', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'javier.vilchis', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
       </c>
     </row>
-    <row r="68" spans="2:24" x14ac:dyDescent="0.3">
+    <row r="68" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B68" s="2">
         <v>100980209</v>
       </c>
@@ -5450,7 +5450,7 @@
         <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (SEQ_TB_SAM_USUARIOS.NEXTVAL, 2, 'JUAN PABLO OLIVERA CATRIP', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'juan.pablo', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
       </c>
     </row>
-    <row r="69" spans="2:24" x14ac:dyDescent="0.3">
+    <row r="69" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B69" s="2">
         <v>100980197</v>
       </c>
@@ -5516,7 +5516,7 @@
         <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (SEQ_TB_SAM_USUARIOS.NEXTVAL, 2, 'SOFIA GINEBRA ZARANDONA', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'sofia.ginebra', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
       </c>
     </row>
-    <row r="70" spans="2:24" x14ac:dyDescent="0.3">
+    <row r="70" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B70" s="2">
         <v>100980202</v>
       </c>
@@ -5579,7 +5579,7 @@
         <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (SEQ_TB_SAM_USUARIOS.NEXTVAL, 2, 'JESUS PATRICIO AVALOS DIAZ BARREIRO', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'jesus.patricio', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
       </c>
     </row>
-    <row r="71" spans="2:24" x14ac:dyDescent="0.3">
+    <row r="71" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B71" s="2">
         <v>100980206</v>
       </c>
@@ -5642,7 +5642,7 @@
         <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (SEQ_TB_SAM_USUARIOS.NEXTVAL, 2, 'MAURICIO FABIAN RODRIGUEZ JUAREZ', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'mauricio.fabian', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
       </c>
     </row>
-    <row r="72" spans="2:24" x14ac:dyDescent="0.3">
+    <row r="72" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B72" s="2">
         <v>100854856</v>
       </c>
@@ -5711,7 +5711,7 @@
         <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (SEQ_TB_SAM_USUARIOS.NEXTVAL, 2, 'JOSE JUAN LOPEZ PIÑERO', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'jose.juan', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
       </c>
     </row>
-    <row r="73" spans="2:24" x14ac:dyDescent="0.3">
+    <row r="73" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B73" s="2">
         <v>100002387</v>
       </c>
@@ -5778,7 +5778,7 @@
         <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (SEQ_TB_SAM_USUARIOS.NEXTVAL, 2, 'MIGUEL ANGEL CARO DEL CASTILLO TREVIÑO', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'miguel.angel', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
       </c>
     </row>
-    <row r="74" spans="2:24" x14ac:dyDescent="0.3">
+    <row r="74" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B74" s="2">
         <v>100003523</v>
       </c>
@@ -5845,7 +5845,7 @@
         <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (SEQ_TB_SAM_USUARIOS.NEXTVAL, 2, 'OLIVER IGOR YAÑEZ GONZALEZ', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'oliver.igor', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
       </c>
     </row>
-    <row r="75" spans="2:24" x14ac:dyDescent="0.3">
+    <row r="75" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B75" s="2">
         <v>100008885</v>
       </c>
@@ -5910,7 +5910,7 @@
         <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (SEQ_TB_SAM_USUARIOS.NEXTVAL, 2, 'MARIA DEL SOCORRO RAMIREZ RICARDEZ', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'maria.del', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
       </c>
     </row>
-    <row r="76" spans="2:24" x14ac:dyDescent="0.3">
+    <row r="76" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B76" s="2">
         <v>100009187</v>
       </c>
@@ -5977,7 +5977,7 @@
         <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (SEQ_TB_SAM_USUARIOS.NEXTVAL, 2, 'MIKHAIL MORA APONTE', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'mikhail.mora', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
       </c>
     </row>
-    <row r="77" spans="2:24" x14ac:dyDescent="0.3">
+    <row r="77" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B77" s="2">
         <v>100396371</v>
       </c>
@@ -6042,7 +6042,7 @@
         <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (SEQ_TB_SAM_USUARIOS.NEXTVAL, 2, 'BRENDA DANIELA VELASCO ROJAS', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'brenda.daniela', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
       </c>
     </row>
-    <row r="78" spans="2:24" x14ac:dyDescent="0.3">
+    <row r="78" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B78" s="2">
         <v>100539130</v>
       </c>
@@ -6109,7 +6109,7 @@
         <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (SEQ_TB_SAM_USUARIOS.NEXTVAL, 2, 'ELIZANDRA CARDOSO AZCOITIA', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'elizandra.cardoso', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
       </c>
     </row>
-    <row r="79" spans="2:24" x14ac:dyDescent="0.3">
+    <row r="79" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B79" s="2">
         <v>100018885</v>
       </c>
@@ -6174,7 +6174,7 @@
         <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (SEQ_TB_SAM_USUARIOS.NEXTVAL, 2, 'JULIANA PEREZ MARTIN DEL CAMPO', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'juliana.perez', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
       </c>
     </row>
-    <row r="80" spans="2:24" x14ac:dyDescent="0.3">
+    <row r="80" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B80" s="2">
         <v>100005847</v>
       </c>
@@ -6235,7 +6235,7 @@
         <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (SEQ_TB_SAM_USUARIOS.NEXTVAL, 2, 'DIEGO MARTINEZ CORTES', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'diego.martinez', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
       </c>
     </row>
-    <row r="81" spans="2:24" x14ac:dyDescent="0.3">
+    <row r="81" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B81" s="2">
         <v>100018889</v>
       </c>
@@ -6298,7 +6298,7 @@
         <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (SEQ_TB_SAM_USUARIOS.NEXTVAL, 2, 'YOLANDA PERDOMO JIMENEZ', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'yolanda.perdomo', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
       </c>
     </row>
-    <row r="82" spans="2:24" x14ac:dyDescent="0.3">
+    <row r="82" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B82" s="2">
         <v>100546470</v>
       </c>
@@ -6361,7 +6361,7 @@
         <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (SEQ_TB_SAM_USUARIOS.NEXTVAL, 2, 'MERCEDES SANCHEZ REYES RETANA', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'mercedes.sanchez', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
       </c>
     </row>
-    <row r="83" spans="2:24" x14ac:dyDescent="0.3">
+    <row r="83" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B83" s="2">
         <v>100550630</v>
       </c>
@@ -6426,7 +6426,7 @@
         <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (SEQ_TB_SAM_USUARIOS.NEXTVAL, 2, 'ALEJANDRA MARTINEZ NIETO', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'alejandra.martinez', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
       </c>
     </row>
-    <row r="84" spans="2:24" x14ac:dyDescent="0.3">
+    <row r="84" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B84" s="2">
         <v>100015156</v>
       </c>
@@ -6495,7 +6495,7 @@
         <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (SEQ_TB_SAM_USUARIOS.NEXTVAL, 2, 'JULIAN GOMEZ FAUSTINO', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'julian.gomez', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
       </c>
     </row>
-    <row r="85" spans="2:24" x14ac:dyDescent="0.3">
+    <row r="85" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B85" s="2">
         <v>100019199</v>
       </c>
@@ -6562,7 +6562,7 @@
         <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (SEQ_TB_SAM_USUARIOS.NEXTVAL, 2, 'CESAR ALEJANDRO ARAIZA ITURRIA', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'cesar.alejandro', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
       </c>
     </row>
-    <row r="86" spans="2:24" x14ac:dyDescent="0.3">
+    <row r="86" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B86" s="2">
         <v>100404799</v>
       </c>
@@ -6629,7 +6629,7 @@
         <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (SEQ_TB_SAM_USUARIOS.NEXTVAL, 2, 'MARIANA CHAVEZ GARCIA', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'mariana.chavez', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
       </c>
     </row>
-    <row r="87" spans="2:24" x14ac:dyDescent="0.3">
+    <row r="87" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B87" s="2">
         <v>100019201</v>
       </c>
@@ -6696,7 +6696,7 @@
         <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (SEQ_TB_SAM_USUARIOS.NEXTVAL, 2, 'LUIS ALFONSO VILLEGAS MORENO', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'luis.alfonso', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
       </c>
     </row>
-    <row r="88" spans="2:24" x14ac:dyDescent="0.3">
+    <row r="88" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B88" s="2">
         <v>100462092</v>
       </c>
@@ -6763,7 +6763,7 @@
         <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (SEQ_TB_SAM_USUARIOS.NEXTVAL, 2, 'JESUS GABRIEL SANCHEZ CANALES', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'jesus.gabriel', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
       </c>
     </row>
-    <row r="89" spans="2:24" x14ac:dyDescent="0.3">
+    <row r="89" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B89" s="2">
         <v>100861987</v>
       </c>
@@ -6832,7 +6832,7 @@
         <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (SEQ_TB_SAM_USUARIOS.NEXTVAL, 2, 'PERLA CRISTINA GONZALEZ ESPINOSA', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'perla.cristina', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
       </c>
     </row>
-    <row r="90" spans="2:24" x14ac:dyDescent="0.3">
+    <row r="90" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B90" s="2">
         <v>100664282</v>
       </c>
@@ -6899,7 +6899,7 @@
         <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (SEQ_TB_SAM_USUARIOS.NEXTVAL, 2, 'KATERINE ITZEL JIMENEZ MIGUEL', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'katerine.itzel', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
       </c>
     </row>
-    <row r="91" spans="2:24" x14ac:dyDescent="0.3">
+    <row r="91" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B91" s="2">
         <v>100019224</v>
       </c>
@@ -6960,7 +6960,7 @@
         <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (SEQ_TB_SAM_USUARIOS.NEXTVAL, 2, 'MARIA DEL PILAR CERRILLA NORIEGA', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'maria.del', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
       </c>
     </row>
-    <row r="92" spans="2:24" x14ac:dyDescent="0.3">
+    <row r="92" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B92" s="2">
         <v>100561793</v>
       </c>
@@ -7027,7 +7027,7 @@
         <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (SEQ_TB_SAM_USUARIOS.NEXTVAL, 2, 'FRANCISCO JOSE BRUNET NAVARRETE', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'francisco.jose', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
       </c>
     </row>
-    <row r="93" spans="2:24" x14ac:dyDescent="0.3">
+    <row r="93" spans="2:24" x14ac:dyDescent="0.25">
       <c r="D93" s="4"/>
       <c r="N93" s="3"/>
       <c r="O93" s="3"/>

--- a/Archivos_Compartidos/Cursos RH/Copia de Listado para cursos normativos 2025.xlsx
+++ b/Archivos_Compartidos/Cursos RH/Copia de Listado para cursos normativos 2025.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://santandernet-my.sharepoint.com/personal/n854611_corp_santanderam_com/Documents/Documentos/GitHub/SAM_Santander/SAM_Santander/Archivos_Compartidos/Cursos RH/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4" documentId="13_ncr:1_{CEB8F394-1A8B-4C4D-9F84-CCF5EE912074}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6B2C252A-B25A-4F98-B23B-58F02FEDEC45}"/>
+  <xr:revisionPtr revIDLastSave="122" documentId="13_ncr:1_{CEB8F394-1A8B-4C4D-9F84-CCF5EE912074}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D05A6A9F-B60B-41AF-9702-BF4A4AA64B1A}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15270" xr2:uid="{FF6FD13D-7CB9-4391-90CB-CB63A01A4952}"/>
+    <workbookView xWindow="-105" yWindow="0" windowWidth="12810" windowHeight="15135" xr2:uid="{FF6FD13D-7CB9-4391-90CB-CB63A01A4952}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1402" uniqueCount="212">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1402" uniqueCount="214">
   <si>
     <t>TODO EL PERSONAL DE SAM</t>
   </si>
@@ -587,60 +587,24 @@
     <t>jose.luis</t>
   </si>
   <si>
-    <t>laura.cecilia</t>
-  </si>
-  <si>
     <t>adriana.valdovinos</t>
   </si>
   <si>
-    <t>carlos.ivan</t>
-  </si>
-  <si>
     <t>marina.josa</t>
   </si>
   <si>
-    <t>luz.maria</t>
-  </si>
-  <si>
-    <t>gloria.paola</t>
-  </si>
-  <si>
     <t>javier.vilchis</t>
   </si>
   <si>
     <t>sofia.ginebra</t>
   </si>
   <si>
-    <t>jesus.patricio</t>
-  </si>
-  <si>
-    <t>mauricio.fabian</t>
-  </si>
-  <si>
-    <t>jose.juan</t>
-  </si>
-  <si>
-    <t>miguel.angel</t>
-  </si>
-  <si>
-    <t>oliver.igor</t>
-  </si>
-  <si>
-    <t>maria.del</t>
-  </si>
-  <si>
     <t>mikhail.mora</t>
   </si>
   <si>
-    <t>brenda.daniela</t>
-  </si>
-  <si>
     <t>elizandra.cardoso</t>
   </si>
   <si>
-    <t>juliana.perez</t>
-  </si>
-  <si>
     <t>diego.martinez</t>
   </si>
   <si>
@@ -656,25 +620,67 @@
     <t>julian.gomez</t>
   </si>
   <si>
-    <t>cesar.alejandro</t>
-  </si>
-  <si>
     <t>mariana.chavez</t>
   </si>
   <si>
-    <t>luis.alfonso</t>
-  </si>
-  <si>
-    <t>jesus.gabriel</t>
-  </si>
-  <si>
-    <t>perla.cristina</t>
-  </si>
-  <si>
-    <t>katerine.itzel</t>
-  </si>
-  <si>
-    <t>francisco.jose</t>
+    <t>laura.hernandez</t>
+  </si>
+  <si>
+    <t>carlos.revilla</t>
+  </si>
+  <si>
+    <t>luz.telles</t>
+  </si>
+  <si>
+    <t>gloria.fragoso</t>
+  </si>
+  <si>
+    <t>juan.olvera</t>
+  </si>
+  <si>
+    <t>jesus.avalos</t>
+  </si>
+  <si>
+    <t>mauricio.rodriguez</t>
+  </si>
+  <si>
+    <t>jose.lopez</t>
+  </si>
+  <si>
+    <t>miguel.caro</t>
+  </si>
+  <si>
+    <t>oliver.yanez</t>
+  </si>
+  <si>
+    <t>maria.ramirez</t>
+  </si>
+  <si>
+    <t>brenda.velasco</t>
+  </si>
+  <si>
+    <t>juliana.martin</t>
+  </si>
+  <si>
+    <t>cesar.araiza</t>
+  </si>
+  <si>
+    <t>luis.villegas</t>
+  </si>
+  <si>
+    <t>jesus.sanchez</t>
+  </si>
+  <si>
+    <t>perla.gonzalez</t>
+  </si>
+  <si>
+    <t>katerine.jimenez</t>
+  </si>
+  <si>
+    <t>maria.cerrilla</t>
+  </si>
+  <si>
+    <t>francisco.brunet</t>
   </si>
 </sst>
 </file>
@@ -746,7 +752,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -760,6 +766,7 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -775,6 +782,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1101,10 +1112,12 @@
     <col min="2" max="2" width="12" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="33.42578125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="14.140625" hidden="1" customWidth="1"/>
+    <col min="5" max="5" width="0" hidden="1" customWidth="1"/>
     <col min="6" max="17" width="10.85546875" hidden="1" customWidth="1"/>
     <col min="18" max="19" width="0" hidden="1" customWidth="1"/>
     <col min="20" max="20" width="18" hidden="1" customWidth="1"/>
     <col min="21" max="21" width="18" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="0" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:24" x14ac:dyDescent="0.25">
@@ -1179,7 +1192,7 @@
       <c r="B4" s="2">
         <v>100922046</v>
       </c>
-      <c r="C4" s="7" t="s">
+      <c r="C4" s="9" t="s">
         <v>19</v>
       </c>
       <c r="D4" s="4">
@@ -1245,17 +1258,17 @@
       </c>
       <c r="X4" t="str">
         <f>"INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,""PASSWORD"",CORREO,DIRECTOR) VALUES (" &amp;
-"SEQ_TB_SAM_USUARIOS.NEXTVAL, 2, '" &amp;
+B4 &amp; ", 2, '" &amp;
 SUBSTITUTE(C4,"'","''") &amp; "', 'MEX Prevencion de PLD', 'Contraloria Normativa', '" &amp;
-SUBSTITUTE(U4,"'","''") &amp; "', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);"</f>
-        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (SEQ_TB_SAM_USUARIOS.NEXTVAL, 2, 'ALEJANDRO MARTINEZ FERES', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'alejandro.martinez', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
+SUBSTITUTE(U4,"'","''") &amp; "', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0)"</f>
+        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (100922046, 2, 'ALEJANDRO MARTINEZ FERES', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'alejandro.martinez', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0)</v>
       </c>
     </row>
     <row r="5" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B5" s="2">
         <v>100004927</v>
       </c>
-      <c r="C5" s="5" t="s">
+      <c r="C5" s="6" t="s">
         <v>22</v>
       </c>
       <c r="D5" s="4"/>
@@ -1301,17 +1314,17 @@
       </c>
       <c r="X5" t="str">
         <f t="shared" ref="X5:X68" si="1">"INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,""PASSWORD"",CORREO,DIRECTOR) VALUES (" &amp;
-"SEQ_TB_SAM_USUARIOS.NEXTVAL, 2, '" &amp;
+B5 &amp; ", 2, '" &amp;
 SUBSTITUTE(C5,"'","''") &amp; "', 'MEX Prevencion de PLD', 'Contraloria Normativa', '" &amp;
-SUBSTITUTE(U5,"'","''") &amp; "', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);"</f>
-        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (SEQ_TB_SAM_USUARIOS.NEXTVAL, 2, 'VIANCA ROSALBA ESPINOSA ROMAN', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'vianca.rosalba', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
+SUBSTITUTE(U5,"'","''") &amp; "', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0)"</f>
+        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (100004927, 2, 'VIANCA ROSALBA ESPINOSA ROMAN', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'vianca.rosalba', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0)</v>
       </c>
     </row>
     <row r="6" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B6" s="2">
         <v>100500870</v>
       </c>
-      <c r="C6" s="5" t="s">
+      <c r="C6" s="6" t="s">
         <v>24</v>
       </c>
       <c r="D6" s="4">
@@ -1359,7 +1372,7 @@
       </c>
       <c r="X6" t="str">
         <f t="shared" si="1"/>
-        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (SEQ_TB_SAM_USUARIOS.NEXTVAL, 2, 'NOEMI NATALY TELLEZ CORREA', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'noemi.nataly', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
+        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (100500870, 2, 'NOEMI NATALY TELLEZ CORREA', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'noemi.nataly', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0)</v>
       </c>
     </row>
     <row r="7" spans="2:24" x14ac:dyDescent="0.25">
@@ -1423,7 +1436,7 @@
       </c>
       <c r="X7" t="str">
         <f t="shared" si="1"/>
-        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (SEQ_TB_SAM_USUARIOS.NEXTVAL, 2, 'MARIAELENA ALAMILLA ALVAREZ', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'mariaelena.alamilla', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
+        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (100018886, 2, 'MARIAELENA ALAMILLA ALVAREZ', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'mariaelena.alamilla', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0)</v>
       </c>
     </row>
     <row r="8" spans="2:24" x14ac:dyDescent="0.25">
@@ -1487,7 +1500,7 @@
       </c>
       <c r="X8" t="str">
         <f t="shared" si="1"/>
-        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (SEQ_TB_SAM_USUARIOS.NEXTVAL, 2, 'DINA ROMAN LIZARRAGA', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'dina.roman', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
+        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (100675883, 2, 'DINA ROMAN LIZARRAGA', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'dina.roman', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0)</v>
       </c>
     </row>
     <row r="9" spans="2:24" x14ac:dyDescent="0.25">
@@ -1551,14 +1564,14 @@
       </c>
       <c r="X9" t="str">
         <f t="shared" si="1"/>
-        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (SEQ_TB_SAM_USUARIOS.NEXTVAL, 2, 'ALEJANDRO PEREZ JIMENEZ', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'alejandro.perez', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
+        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (100572137, 2, 'ALEJANDRO PEREZ JIMENEZ', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'alejandro.perez', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0)</v>
       </c>
     </row>
     <row r="10" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B10" s="2">
         <v>100985454</v>
       </c>
-      <c r="C10" s="7" t="s">
+      <c r="C10" s="9" t="s">
         <v>29</v>
       </c>
       <c r="D10" s="4">
@@ -1617,15 +1630,18 @@
         <v>124</v>
       </c>
       <c r="X10" t="str">
-        <f t="shared" si="1"/>
-        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (SEQ_TB_SAM_USUARIOS.NEXTVAL, 2, 'ALEJANDRO CALANDA MORALES', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'alejandro.calanda', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
+        <f>"INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,""PASSWORD"",CORREO,DIRECTOR) VALUES (" &amp;
+B10 &amp; ", 2, '" &amp;
+SUBSTITUTE(C10,"'","''") &amp; "', 'NA', 'NA', '" &amp;
+SUBSTITUTE(U10,"'","''") &amp; "', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0)"</f>
+        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (100985454, 2, 'ALEJANDRO CALANDA MORALES', 'NA', 'NA', 'alejandro.calanda', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0)</v>
       </c>
     </row>
     <row r="11" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B11" s="2">
         <v>100677152</v>
       </c>
-      <c r="C11" s="5" t="s">
+      <c r="C11" s="6" t="s">
         <v>30</v>
       </c>
       <c r="D11" s="4">
@@ -1681,15 +1697,18 @@
         <v>124</v>
       </c>
       <c r="X11" t="str">
-        <f t="shared" si="1"/>
-        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (SEQ_TB_SAM_USUARIOS.NEXTVAL, 2, 'CARLOS AGUAYO SANCHEZ', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'carlos.aguayo', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
+        <f t="shared" ref="X11:X74" si="2">"INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,""PASSWORD"",CORREO,DIRECTOR) VALUES (" &amp;
+B11 &amp; ", 2, '" &amp;
+SUBSTITUTE(C11,"'","''") &amp; "', 'NA', 'NA', '" &amp;
+SUBSTITUTE(U11,"'","''") &amp; "', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0)"</f>
+        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (100677152, 2, 'CARLOS AGUAYO SANCHEZ', 'NA', 'NA', 'carlos.aguayo', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0)</v>
       </c>
     </row>
     <row r="12" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B12" s="2">
         <v>100000263</v>
       </c>
-      <c r="C12" s="5" t="s">
+      <c r="C12" s="6" t="s">
         <v>31</v>
       </c>
       <c r="D12" s="4"/>
@@ -1750,15 +1769,15 @@
         <v>124</v>
       </c>
       <c r="X12" t="str">
-        <f t="shared" si="1"/>
-        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (SEQ_TB_SAM_USUARIOS.NEXTVAL, 2, 'ADRIANA TAPIA GONZALEZ', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'adriana.tapia', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
+        <f t="shared" si="2"/>
+        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (100000263, 2, 'ADRIANA TAPIA GONZALEZ', 'NA', 'NA', 'adriana.tapia', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0)</v>
       </c>
     </row>
     <row r="13" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B13" s="2">
         <v>100854877</v>
       </c>
-      <c r="C13" s="7" t="s">
+      <c r="C13" s="9" t="s">
         <v>33</v>
       </c>
       <c r="D13" s="4">
@@ -1821,15 +1840,15 @@
         <v>124</v>
       </c>
       <c r="X13" t="str">
-        <f t="shared" si="1"/>
-        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (SEQ_TB_SAM_USUARIOS.NEXTVAL, 2, 'JOSE FERNANDO PUENTE PLATA', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'jose.fernando', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
+        <f t="shared" si="2"/>
+        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (100854877, 2, 'JOSE FERNANDO PUENTE PLATA', 'NA', 'NA', 'jose.fernando', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0)</v>
       </c>
     </row>
     <row r="14" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B14" s="2">
         <v>100019203</v>
       </c>
-      <c r="C14" s="5" t="s">
+      <c r="C14" s="6" t="s">
         <v>34</v>
       </c>
       <c r="D14" s="4">
@@ -1884,15 +1903,15 @@
         <v>124</v>
       </c>
       <c r="X14" t="str">
-        <f t="shared" si="1"/>
-        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (SEQ_TB_SAM_USUARIOS.NEXTVAL, 2, 'CARLOS RAMON SANDOVAL MINERO', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'carlos.ramon', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
+        <f t="shared" si="2"/>
+        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (100019203, 2, 'CARLOS RAMON SANDOVAL MINERO', 'NA', 'NA', 'carlos.ramon', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0)</v>
       </c>
     </row>
     <row r="15" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B15" s="2">
         <v>100019200</v>
       </c>
-      <c r="C15" s="5" t="s">
+      <c r="C15" s="6" t="s">
         <v>36</v>
       </c>
       <c r="D15" s="4">
@@ -1947,15 +1966,15 @@
         <v>124</v>
       </c>
       <c r="X15" t="str">
-        <f t="shared" si="1"/>
-        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (SEQ_TB_SAM_USUARIOS.NEXTVAL, 2, 'GRACIELA AGUILAR MARTINEZ', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'graciela.aguilar', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
+        <f t="shared" si="2"/>
+        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (100019200, 2, 'GRACIELA AGUILAR MARTINEZ', 'NA', 'NA', 'graciela.aguilar', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0)</v>
       </c>
     </row>
     <row r="16" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B16" s="2">
         <v>100019204</v>
       </c>
-      <c r="C16" s="2" t="s">
+      <c r="C16" s="6" t="s">
         <v>37</v>
       </c>
       <c r="D16" s="4">
@@ -2010,15 +2029,15 @@
         <v>124</v>
       </c>
       <c r="X16" t="str">
-        <f t="shared" si="1"/>
-        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (SEQ_TB_SAM_USUARIOS.NEXTVAL, 2, 'ALEJANDRO CESAR SANCHEZ CERVANTES', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'alejandro.cesar', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
+        <f t="shared" si="2"/>
+        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (100019204, 2, 'ALEJANDRO CESAR SANCHEZ CERVANTES', 'NA', 'NA', 'alejandro.cesar', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0)</v>
       </c>
     </row>
     <row r="17" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B17" s="2">
         <v>100327492</v>
       </c>
-      <c r="C17" s="2" t="s">
+      <c r="C17" s="6" t="s">
         <v>38</v>
       </c>
       <c r="D17" s="4">
@@ -2073,15 +2092,15 @@
         <v>124</v>
       </c>
       <c r="X17" t="str">
-        <f t="shared" si="1"/>
-        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (SEQ_TB_SAM_USUARIOS.NEXTVAL, 2, 'LEONARDO DAVID PLATA MARTINEZ', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'leonardo.david', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
+        <f t="shared" si="2"/>
+        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (100327492, 2, 'LEONARDO DAVID PLATA MARTINEZ', 'NA', 'NA', 'leonardo.david', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0)</v>
       </c>
     </row>
     <row r="18" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B18" s="2">
         <v>100327494</v>
       </c>
-      <c r="C18" s="2" t="s">
+      <c r="C18" s="6" t="s">
         <v>39</v>
       </c>
       <c r="D18" s="4"/>
@@ -2132,15 +2151,15 @@
         <v>124</v>
       </c>
       <c r="X18" t="str">
-        <f t="shared" si="1"/>
-        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (SEQ_TB_SAM_USUARIOS.NEXTVAL, 2, 'VERONICA MARTELL ESPINOSA', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'veronica.martell', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
+        <f t="shared" si="2"/>
+        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (100327494, 2, 'VERONICA MARTELL ESPINOSA', 'NA', 'NA', 'veronica.martell', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0)</v>
       </c>
     </row>
     <row r="19" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B19" s="2">
         <v>100000056</v>
       </c>
-      <c r="C19" s="2" t="s">
+      <c r="C19" s="6" t="s">
         <v>40</v>
       </c>
       <c r="D19" s="4">
@@ -2195,15 +2214,15 @@
         <v>124</v>
       </c>
       <c r="X19" t="str">
-        <f t="shared" si="1"/>
-        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (SEQ_TB_SAM_USUARIOS.NEXTVAL, 2, 'CARLOS ALBERTO RAMIREZ JUAREZ', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'carlos.alberto', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
+        <f t="shared" si="2"/>
+        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (100000056, 2, 'CARLOS ALBERTO RAMIREZ JUAREZ', 'NA', 'NA', 'carlos.alberto', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0)</v>
       </c>
     </row>
     <row r="20" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B20" s="2">
         <v>100384479</v>
       </c>
-      <c r="C20" s="2" t="s">
+      <c r="C20" s="6" t="s">
         <v>41</v>
       </c>
       <c r="D20" s="4">
@@ -2258,15 +2277,15 @@
         <v>124</v>
       </c>
       <c r="X20" t="str">
-        <f t="shared" si="1"/>
-        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (SEQ_TB_SAM_USUARIOS.NEXTVAL, 2, 'OCTAVIO AUGUSTO DIAZ LOPEZ', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'octavio.augusto', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
+        <f t="shared" si="2"/>
+        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (100384479, 2, 'OCTAVIO AUGUSTO DIAZ LOPEZ', 'NA', 'NA', 'octavio.augusto', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0)</v>
       </c>
     </row>
     <row r="21" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B21" s="2">
         <v>100545348</v>
       </c>
-      <c r="C21" s="2" t="s">
+      <c r="C21" s="6" t="s">
         <v>42</v>
       </c>
       <c r="D21" s="4">
@@ -2321,15 +2340,15 @@
         <v>124</v>
       </c>
       <c r="X21" t="str">
-        <f t="shared" si="1"/>
-        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (SEQ_TB_SAM_USUARIOS.NEXTVAL, 2, 'ANGEL DANIEL RUIZ ACUÑA', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'angel.daniel', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
+        <f t="shared" si="2"/>
+        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (100545348, 2, 'ANGEL DANIEL RUIZ ACUÑA', 'NA', 'NA', 'angel.daniel', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0)</v>
       </c>
     </row>
     <row r="22" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B22" s="2">
         <v>100003814</v>
       </c>
-      <c r="C22" s="2" t="s">
+      <c r="C22" s="6" t="s">
         <v>43</v>
       </c>
       <c r="D22" s="4">
@@ -2390,15 +2409,15 @@
         <v>124</v>
       </c>
       <c r="X22" t="str">
-        <f t="shared" si="1"/>
-        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (SEQ_TB_SAM_USUARIOS.NEXTVAL, 2, 'SARA MALDONADO VILCHIS', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'sara.maldonado', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
+        <f t="shared" si="2"/>
+        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (100003814, 2, 'SARA MALDONADO VILCHIS', 'NA', 'NA', 'sara.maldonado', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0)</v>
       </c>
     </row>
     <row r="23" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B23" s="2">
         <v>100019864</v>
       </c>
-      <c r="C23" s="2" t="s">
+      <c r="C23" s="6" t="s">
         <v>45</v>
       </c>
       <c r="D23" s="4">
@@ -2459,15 +2478,15 @@
         <v>124</v>
       </c>
       <c r="X23" t="str">
-        <f t="shared" si="1"/>
-        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (SEQ_TB_SAM_USUARIOS.NEXTVAL, 2, 'PAOLA MARIANA DOMINGUEZ MAS', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'paola.mariana', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
+        <f t="shared" si="2"/>
+        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (100019864, 2, 'PAOLA MARIANA DOMINGUEZ MAS', 'NA', 'NA', 'paola.mariana', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0)</v>
       </c>
     </row>
     <row r="24" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B24" s="2">
         <v>100018887</v>
       </c>
-      <c r="C24" s="2" t="s">
+      <c r="C24" s="6" t="s">
         <v>46</v>
       </c>
       <c r="D24" s="4">
@@ -2528,15 +2547,15 @@
         <v>124</v>
       </c>
       <c r="X24" t="str">
-        <f t="shared" si="1"/>
-        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (SEQ_TB_SAM_USUARIOS.NEXTVAL, 2, 'ANDRES IGNACIO MUÑETON RODRIGUEZ', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'andres.ignacio', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
+        <f t="shared" si="2"/>
+        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (100018887, 2, 'ANDRES IGNACIO MUÑETON RODRIGUEZ', 'NA', 'NA', 'andres.ignacio', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0)</v>
       </c>
     </row>
     <row r="25" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B25" s="2">
         <v>100018888</v>
       </c>
-      <c r="C25" s="2" t="s">
+      <c r="C25" s="6" t="s">
         <v>47</v>
       </c>
       <c r="D25" s="4">
@@ -2597,15 +2616,15 @@
         <v>124</v>
       </c>
       <c r="X25" t="str">
-        <f t="shared" si="1"/>
-        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (SEQ_TB_SAM_USUARIOS.NEXTVAL, 2, 'JOSE URIBE CEDILLO', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'jose.uribe', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
+        <f t="shared" si="2"/>
+        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (100018888, 2, 'JOSE URIBE CEDILLO', 'NA', 'NA', 'jose.uribe', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0)</v>
       </c>
     </row>
     <row r="26" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B26" s="2">
         <v>100015250</v>
       </c>
-      <c r="C26" s="2" t="s">
+      <c r="C26" s="6" t="s">
         <v>48</v>
       </c>
       <c r="D26" s="4">
@@ -2666,15 +2685,15 @@
         <v>124</v>
       </c>
       <c r="X26" t="str">
-        <f t="shared" si="1"/>
-        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (SEQ_TB_SAM_USUARIOS.NEXTVAL, 2, 'MARCOS CAMACHO PARADA', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'marcos.camacho', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
+        <f t="shared" si="2"/>
+        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (100015250, 2, 'MARCOS CAMACHO PARADA', 'NA', 'NA', 'marcos.camacho', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0)</v>
       </c>
     </row>
     <row r="27" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B27" s="2">
         <v>100018636</v>
       </c>
-      <c r="C27" s="2" t="s">
+      <c r="C27" s="6" t="s">
         <v>49</v>
       </c>
       <c r="D27" s="4">
@@ -2735,15 +2754,15 @@
         <v>124</v>
       </c>
       <c r="X27" t="str">
-        <f t="shared" si="1"/>
-        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (SEQ_TB_SAM_USUARIOS.NEXTVAL, 2, 'LUIS ARTURO FLORES SANCHEZ', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'luis.arturo', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
+        <f t="shared" si="2"/>
+        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (100018636, 2, 'LUIS ARTURO FLORES SANCHEZ', 'NA', 'NA', 'luis.arturo', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0)</v>
       </c>
     </row>
     <row r="28" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B28" s="2">
         <v>100009066</v>
       </c>
-      <c r="C28" s="2" t="s">
+      <c r="C28" s="6" t="s">
         <v>50</v>
       </c>
       <c r="D28" s="4">
@@ -2804,15 +2823,15 @@
         <v>124</v>
       </c>
       <c r="X28" t="str">
-        <f t="shared" si="1"/>
-        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (SEQ_TB_SAM_USUARIOS.NEXTVAL, 2, 'RAFAEL BUERBA GOMEZ', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'rafael.buerba', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
+        <f t="shared" si="2"/>
+        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (100009066, 2, 'RAFAEL BUERBA GOMEZ', 'NA', 'NA', 'rafael.buerba', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0)</v>
       </c>
     </row>
     <row r="29" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B29" s="2">
         <v>100401809</v>
       </c>
-      <c r="C29" s="2" t="s">
+      <c r="C29" s="6" t="s">
         <v>51</v>
       </c>
       <c r="D29" s="4">
@@ -2873,15 +2892,15 @@
         <v>124</v>
       </c>
       <c r="X29" t="str">
-        <f t="shared" si="1"/>
-        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (SEQ_TB_SAM_USUARIOS.NEXTVAL, 2, 'JUAN PABLO ARIZALETA BARQUIN', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'juan.pablo', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
+        <f t="shared" si="2"/>
+        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (100401809, 2, 'JUAN PABLO ARIZALETA BARQUIN', 'NA', 'NA', 'juan.pablo', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0)</v>
       </c>
     </row>
     <row r="30" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B30" s="2">
         <v>100416647</v>
       </c>
-      <c r="C30" s="2" t="s">
+      <c r="C30" s="6" t="s">
         <v>52</v>
       </c>
       <c r="D30" s="4">
@@ -2942,15 +2961,15 @@
         <v>124</v>
       </c>
       <c r="X30" t="str">
-        <f t="shared" si="1"/>
-        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (SEQ_TB_SAM_USUARIOS.NEXTVAL, 2, 'ALEJANDRO LAVIN TREVIÑO', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'alejandro.lavin', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
+        <f t="shared" si="2"/>
+        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (100416647, 2, 'ALEJANDRO LAVIN TREVIÑO', 'NA', 'NA', 'alejandro.lavin', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0)</v>
       </c>
     </row>
     <row r="31" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B31" s="2">
         <v>100253304</v>
       </c>
-      <c r="C31" s="2" t="s">
+      <c r="C31" s="6" t="s">
         <v>53</v>
       </c>
       <c r="D31" s="4">
@@ -3011,15 +3030,15 @@
         <v>124</v>
       </c>
       <c r="X31" t="str">
-        <f t="shared" si="1"/>
-        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (SEQ_TB_SAM_USUARIOS.NEXTVAL, 2, 'RAFAEL BENJAMIN VEGA ORTEGA', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'rafael.benjamin', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
+        <f t="shared" si="2"/>
+        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (100253304, 2, 'RAFAEL BENJAMIN VEGA ORTEGA', 'NA', 'NA', 'rafael.benjamin', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0)</v>
       </c>
     </row>
     <row r="32" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B32" s="2">
         <v>100523258</v>
       </c>
-      <c r="C32" s="2" t="s">
+      <c r="C32" s="6" t="s">
         <v>54</v>
       </c>
       <c r="D32" s="4">
@@ -3080,15 +3099,15 @@
         <v>124</v>
       </c>
       <c r="X32" t="str">
-        <f t="shared" si="1"/>
-        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (SEQ_TB_SAM_USUARIOS.NEXTVAL, 2, 'LUIS FERNANDO YANCE CHARRIA', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'luis.fernando', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
+        <f t="shared" si="2"/>
+        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (100523258, 2, 'LUIS FERNANDO YANCE CHARRIA', 'NA', 'NA', 'luis.fernando', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0)</v>
       </c>
     </row>
     <row r="33" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B33" s="2">
         <v>100016803</v>
       </c>
-      <c r="C33" s="2" t="s">
+      <c r="C33" s="6" t="s">
         <v>55</v>
       </c>
       <c r="D33" s="4">
@@ -3149,15 +3168,15 @@
         <v>124</v>
       </c>
       <c r="X33" t="str">
-        <f t="shared" si="1"/>
-        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (SEQ_TB_SAM_USUARIOS.NEXTVAL, 2, 'MAURO VAZQUEZ FLORES', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'mauro.vazquez', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
+        <f t="shared" si="2"/>
+        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (100016803, 2, 'MAURO VAZQUEZ FLORES', 'NA', 'NA', 'mauro.vazquez', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0)</v>
       </c>
     </row>
     <row r="34" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B34" s="2">
         <v>100574048</v>
       </c>
-      <c r="C34" s="2" t="s">
+      <c r="C34" s="6" t="s">
         <v>56</v>
       </c>
       <c r="D34" s="4">
@@ -3218,15 +3237,15 @@
         <v>124</v>
       </c>
       <c r="X34" t="str">
-        <f t="shared" si="1"/>
-        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (SEQ_TB_SAM_USUARIOS.NEXTVAL, 2, 'JORGE OMAR VARGAS VEGA', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'jorge.omar', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
+        <f t="shared" si="2"/>
+        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (100574048, 2, 'JORGE OMAR VARGAS VEGA', 'NA', 'NA', 'jorge.omar', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0)</v>
       </c>
     </row>
     <row r="35" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B35" s="2">
         <v>100613246</v>
       </c>
-      <c r="C35" s="2" t="s">
+      <c r="C35" s="6" t="s">
         <v>57</v>
       </c>
       <c r="D35" s="4">
@@ -3287,15 +3306,15 @@
         <v>124</v>
       </c>
       <c r="X35" t="str">
-        <f t="shared" si="1"/>
-        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (SEQ_TB_SAM_USUARIOS.NEXTVAL, 2, 'BERNARDO MALPICA DONDE', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'bernardo.malpica', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
+        <f t="shared" si="2"/>
+        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (100613246, 2, 'BERNARDO MALPICA DONDE', 'NA', 'NA', 'bernardo.malpica', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0)</v>
       </c>
     </row>
     <row r="36" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B36" s="2">
         <v>100854836</v>
       </c>
-      <c r="C36" s="2" t="s">
+      <c r="C36" s="5" t="s">
         <v>58</v>
       </c>
       <c r="D36" s="4">
@@ -3358,15 +3377,15 @@
         <v>124</v>
       </c>
       <c r="X36" t="str">
-        <f t="shared" si="1"/>
-        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (SEQ_TB_SAM_USUARIOS.NEXTVAL, 2, 'MONICA BARRIGA ROBLES', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'monica.barriga', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
+        <f t="shared" si="2"/>
+        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (100854836, 2, 'MONICA BARRIGA ROBLES', 'NA', 'NA', 'monica.barriga', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0)</v>
       </c>
     </row>
     <row r="37" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B37" s="2">
         <v>100861962</v>
       </c>
-      <c r="C37" s="2" t="s">
+      <c r="C37" s="5" t="s">
         <v>59</v>
       </c>
       <c r="D37" s="4">
@@ -3429,15 +3448,15 @@
         <v>124</v>
       </c>
       <c r="X37" t="str">
-        <f t="shared" si="1"/>
-        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (SEQ_TB_SAM_USUARIOS.NEXTVAL, 2, 'PATRICIA MARTINEZ GUTIERREZ', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'patricia.martinez', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
+        <f t="shared" si="2"/>
+        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (100861962, 2, 'PATRICIA MARTINEZ GUTIERREZ', 'NA', 'NA', 'patricia.martinez', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0)</v>
       </c>
     </row>
     <row r="38" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B38" s="2">
         <v>100362615</v>
       </c>
-      <c r="C38" s="2" t="s">
+      <c r="C38" s="6" t="s">
         <v>60</v>
       </c>
       <c r="D38" s="4">
@@ -3498,15 +3517,15 @@
         <v>124</v>
       </c>
       <c r="X38" t="str">
-        <f t="shared" si="1"/>
-        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (SEQ_TB_SAM_USUARIOS.NEXTVAL, 2, 'BRENDA GISELL GIRON MAY', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'brenda.gisell', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
+        <f t="shared" si="2"/>
+        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (100362615, 2, 'BRENDA GISELL GIRON MAY', 'NA', 'NA', 'brenda.gisell', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0)</v>
       </c>
     </row>
     <row r="39" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B39" s="2">
         <v>100591294</v>
       </c>
-      <c r="C39" s="2" t="s">
+      <c r="C39" s="6" t="s">
         <v>61</v>
       </c>
       <c r="D39" s="4">
@@ -3567,15 +3586,15 @@
         <v>124</v>
       </c>
       <c r="X39" t="str">
-        <f t="shared" si="1"/>
-        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (SEQ_TB_SAM_USUARIOS.NEXTVAL, 2, 'SANTIAGO PALAZUELOS VON BERTRAB', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'santiago.palazuelos', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
+        <f t="shared" si="2"/>
+        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (100591294, 2, 'SANTIAGO PALAZUELOS VON BERTRAB', 'NA', 'NA', 'santiago.palazuelos', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0)</v>
       </c>
     </row>
     <row r="40" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B40" s="2">
         <v>100685301</v>
       </c>
-      <c r="C40" s="2" t="s">
+      <c r="C40" s="6" t="s">
         <v>62</v>
       </c>
       <c r="D40" s="4">
@@ -3636,15 +3655,15 @@
         <v>124</v>
       </c>
       <c r="X40" t="str">
-        <f t="shared" si="1"/>
-        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (SEQ_TB_SAM_USUARIOS.NEXTVAL, 2, 'RODRIGO EDUARDO SANHUEZA VEGA', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'rodrigo.eduardo', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
+        <f t="shared" si="2"/>
+        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (100685301, 2, 'RODRIGO EDUARDO SANHUEZA VEGA', 'NA', 'NA', 'rodrigo.eduardo', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0)</v>
       </c>
     </row>
     <row r="41" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B41" s="2">
         <v>100559745</v>
       </c>
-      <c r="C41" s="2" t="s">
+      <c r="C41" s="6" t="s">
         <v>63</v>
       </c>
       <c r="D41" s="4">
@@ -3705,15 +3724,15 @@
         <v>124</v>
       </c>
       <c r="X41" t="str">
-        <f t="shared" si="1"/>
-        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (SEQ_TB_SAM_USUARIOS.NEXTVAL, 2, 'NADINE ORNELAS ESQUINCA', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'nadine.ornelas', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
+        <f t="shared" si="2"/>
+        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (100559745, 2, 'NADINE ORNELAS ESQUINCA', 'NA', 'NA', 'nadine.ornelas', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0)</v>
       </c>
     </row>
     <row r="42" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B42" s="2">
         <v>100251487</v>
       </c>
-      <c r="C42" s="2" t="s">
+      <c r="C42" s="6" t="s">
         <v>64</v>
       </c>
       <c r="D42" s="4">
@@ -3770,15 +3789,15 @@
         <v>124</v>
       </c>
       <c r="X42" t="str">
-        <f t="shared" si="1"/>
-        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (SEQ_TB_SAM_USUARIOS.NEXTVAL, 2, 'LUIS ANTONIO TOVAR ACUÑA', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'luis.antonio', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
+        <f t="shared" si="2"/>
+        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (100251487, 2, 'LUIS ANTONIO TOVAR ACUÑA', 'NA', 'NA', 'luis.antonio', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0)</v>
       </c>
     </row>
     <row r="43" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B43" s="2">
         <v>100014520</v>
       </c>
-      <c r="C43" s="2" t="s">
+      <c r="C43" s="6" t="s">
         <v>66</v>
       </c>
       <c r="D43" s="4">
@@ -3835,15 +3854,15 @@
         <v>124</v>
       </c>
       <c r="X43" t="str">
-        <f t="shared" si="1"/>
-        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (SEQ_TB_SAM_USUARIOS.NEXTVAL, 2, 'DANIEL LOPEZ IBARRA', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'daniel.lopez', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
+        <f t="shared" si="2"/>
+        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (100014520, 2, 'DANIEL LOPEZ IBARRA', 'NA', 'NA', 'daniel.lopez', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0)</v>
       </c>
     </row>
     <row r="44" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B44" s="2">
         <v>100014960</v>
       </c>
-      <c r="C44" s="2" t="s">
+      <c r="C44" s="6" t="s">
         <v>67</v>
       </c>
       <c r="D44" s="4">
@@ -3900,15 +3919,15 @@
         <v>124</v>
       </c>
       <c r="X44" t="str">
-        <f t="shared" si="1"/>
-        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (SEQ_TB_SAM_USUARIOS.NEXTVAL, 2, 'PABLO RUIZ HERRERA', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'pablo.ruiz', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
+        <f t="shared" si="2"/>
+        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (100014960, 2, 'PABLO RUIZ HERRERA', 'NA', 'NA', 'pablo.ruiz', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0)</v>
       </c>
     </row>
     <row r="45" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B45" s="2">
         <v>100015893</v>
       </c>
-      <c r="C45" s="2" t="s">
+      <c r="C45" s="6" t="s">
         <v>68</v>
       </c>
       <c r="D45" s="4"/>
@@ -3963,15 +3982,15 @@
         <v>124</v>
       </c>
       <c r="X45" t="str">
-        <f t="shared" si="1"/>
-        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (SEQ_TB_SAM_USUARIOS.NEXTVAL, 2, 'ADRIANA GONZALEZ PALACIOS', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'adriana.gonzalez', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
+        <f t="shared" si="2"/>
+        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (100015893, 2, 'ADRIANA GONZALEZ PALACIOS', 'NA', 'NA', 'adriana.gonzalez', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0)</v>
       </c>
     </row>
     <row r="46" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B46" s="2">
         <v>100017815</v>
       </c>
-      <c r="C46" s="2" t="s">
+      <c r="C46" s="6" t="s">
         <v>69</v>
       </c>
       <c r="D46" s="4">
@@ -4024,15 +4043,15 @@
         <v>124</v>
       </c>
       <c r="X46" t="str">
-        <f t="shared" si="1"/>
-        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (SEQ_TB_SAM_USUARIOS.NEXTVAL, 2, 'ALVARO ALBERTO OCHOA PICHARDO', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'alvaro.alberto', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
+        <f t="shared" si="2"/>
+        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (100017815, 2, 'ALVARO ALBERTO OCHOA PICHARDO', 'NA', 'NA', 'alvaro.alberto', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0)</v>
       </c>
     </row>
     <row r="47" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B47" s="2">
         <v>100267204</v>
       </c>
-      <c r="C47" s="2" t="s">
+      <c r="C47" s="6" t="s">
         <v>70</v>
       </c>
       <c r="D47" s="4">
@@ -4085,15 +4104,15 @@
         <v>124</v>
       </c>
       <c r="X47" t="str">
-        <f t="shared" si="1"/>
-        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (SEQ_TB_SAM_USUARIOS.NEXTVAL, 2, 'JAVIER PACHECO LOPEZ', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'javier.pacheco', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
+        <f t="shared" si="2"/>
+        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (100267204, 2, 'JAVIER PACHECO LOPEZ', 'NA', 'NA', 'javier.pacheco', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0)</v>
       </c>
     </row>
     <row r="48" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B48" s="2">
         <v>100018765</v>
       </c>
-      <c r="C48" s="2" t="s">
+      <c r="C48" s="6" t="s">
         <v>71</v>
       </c>
       <c r="D48" s="4">
@@ -4150,15 +4169,15 @@
         <v>124</v>
       </c>
       <c r="X48" t="str">
-        <f t="shared" si="1"/>
-        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (SEQ_TB_SAM_USUARIOS.NEXTVAL, 2, 'BRENDA LIZBETH MONTEAGUDO RAMIREZ', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'brenda.lizbeth', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
+        <f t="shared" si="2"/>
+        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (100018765, 2, 'BRENDA LIZBETH MONTEAGUDO RAMIREZ', 'NA', 'NA', 'brenda.lizbeth', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0)</v>
       </c>
     </row>
     <row r="49" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B49" s="2">
         <v>100383461</v>
       </c>
-      <c r="C49" s="2" t="s">
+      <c r="C49" s="6" t="s">
         <v>72</v>
       </c>
       <c r="D49" s="4">
@@ -4215,15 +4234,15 @@
         <v>124</v>
       </c>
       <c r="X49" t="str">
-        <f t="shared" si="1"/>
-        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (SEQ_TB_SAM_USUARIOS.NEXTVAL, 2, 'ROQUE DANIEL TORRES TENORIO', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'roque.daniel', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
+        <f t="shared" si="2"/>
+        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (100383461, 2, 'ROQUE DANIEL TORRES TENORIO', 'NA', 'NA', 'roque.daniel', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0)</v>
       </c>
     </row>
     <row r="50" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B50" s="2">
         <v>100383462</v>
       </c>
-      <c r="C50" s="2" t="s">
+      <c r="C50" s="6" t="s">
         <v>73</v>
       </c>
       <c r="D50" s="4">
@@ -4280,15 +4299,15 @@
         <v>124</v>
       </c>
       <c r="X50" t="str">
-        <f t="shared" si="1"/>
-        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (SEQ_TB_SAM_USUARIOS.NEXTVAL, 2, 'KATHIA AIDEE SOLIS ESCOBAR', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'kathia.aidee', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
+        <f t="shared" si="2"/>
+        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (100383462, 2, 'KATHIA AIDEE SOLIS ESCOBAR', 'NA', 'NA', 'kathia.aidee', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0)</v>
       </c>
     </row>
     <row r="51" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B51" s="2">
         <v>100018274</v>
       </c>
-      <c r="C51" s="2" t="s">
+      <c r="C51" s="6" t="s">
         <v>74</v>
       </c>
       <c r="D51" s="4"/>
@@ -4343,15 +4362,15 @@
         <v>124</v>
       </c>
       <c r="X51" t="str">
-        <f t="shared" si="1"/>
-        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (SEQ_TB_SAM_USUARIOS.NEXTVAL, 2, 'VERONICA INES LEON MOCTEZUMA', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'veronica.ines', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
+        <f t="shared" si="2"/>
+        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (100018274, 2, 'VERONICA INES LEON MOCTEZUMA', 'NA', 'NA', 'veronica.ines', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0)</v>
       </c>
     </row>
     <row r="52" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B52" s="2">
         <v>100404797</v>
       </c>
-      <c r="C52" s="2" t="s">
+      <c r="C52" s="6" t="s">
         <v>75</v>
       </c>
       <c r="D52" s="4">
@@ -4408,15 +4427,15 @@
         <v>124</v>
       </c>
       <c r="X52" t="str">
-        <f t="shared" si="1"/>
-        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (SEQ_TB_SAM_USUARIOS.NEXTVAL, 2, 'DANIELA ARAIZA MACIAS', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'daniela.araiza', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
+        <f t="shared" si="2"/>
+        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (100404797, 2, 'DANIELA ARAIZA MACIAS', 'NA', 'NA', 'daniela.araiza', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0)</v>
       </c>
     </row>
     <row r="53" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B53" s="2">
         <v>100533479</v>
       </c>
-      <c r="C53" s="2" t="s">
+      <c r="C53" s="6" t="s">
         <v>76</v>
       </c>
       <c r="D53" s="4">
@@ -4473,15 +4492,15 @@
         <v>124</v>
       </c>
       <c r="X53" t="str">
-        <f t="shared" si="1"/>
-        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (SEQ_TB_SAM_USUARIOS.NEXTVAL, 2, 'LAURA SARAI NAJERA HERNANDEZ', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'laura.sarai', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
+        <f t="shared" si="2"/>
+        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (100533479, 2, 'LAURA SARAI NAJERA HERNANDEZ', 'NA', 'NA', 'laura.sarai', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0)</v>
       </c>
     </row>
     <row r="54" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B54" s="2">
         <v>100533482</v>
       </c>
-      <c r="C54" s="2" t="s">
+      <c r="C54" s="6" t="s">
         <v>77</v>
       </c>
       <c r="D54" s="4">
@@ -4538,15 +4557,15 @@
         <v>124</v>
       </c>
       <c r="X54" t="str">
-        <f t="shared" si="1"/>
-        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (SEQ_TB_SAM_USUARIOS.NEXTVAL, 2, 'ALFREDO MARQUEZ GUTIERREZ', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'alfredo.marquez', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
+        <f t="shared" si="2"/>
+        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (100533482, 2, 'ALFREDO MARQUEZ GUTIERREZ', 'NA', 'NA', 'alfredo.marquez', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0)</v>
       </c>
     </row>
     <row r="55" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B55" s="2">
         <v>100549886</v>
       </c>
-      <c r="C55" s="2" t="s">
+      <c r="C55" s="6" t="s">
         <v>78</v>
       </c>
       <c r="D55" s="4">
@@ -4603,15 +4622,15 @@
         <v>124</v>
       </c>
       <c r="X55" t="str">
-        <f t="shared" si="1"/>
-        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (SEQ_TB_SAM_USUARIOS.NEXTVAL, 2, 'RICARDO MENDOZA VILLEGAS', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'ricardo.mendoza', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
+        <f t="shared" si="2"/>
+        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (100549886, 2, 'RICARDO MENDOZA VILLEGAS', 'NA', 'NA', 'ricardo.mendoza', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0)</v>
       </c>
     </row>
     <row r="56" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B56" s="2">
         <v>100664258</v>
       </c>
-      <c r="C56" s="2" t="s">
+      <c r="C56" s="6" t="s">
         <v>79</v>
       </c>
       <c r="D56" s="4">
@@ -4668,15 +4687,15 @@
         <v>124</v>
       </c>
       <c r="X56" t="str">
-        <f t="shared" si="1"/>
-        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (SEQ_TB_SAM_USUARIOS.NEXTVAL, 2, 'EDGAR RENDON RAMIREZ', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'edgar.rendon', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
+        <f t="shared" si="2"/>
+        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (100664258, 2, 'EDGAR RENDON RAMIREZ', 'NA', 'NA', 'edgar.rendon', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0)</v>
       </c>
     </row>
     <row r="57" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B57" s="2">
         <v>100696339</v>
       </c>
-      <c r="C57" s="2" t="s">
+      <c r="C57" s="6" t="s">
         <v>80</v>
       </c>
       <c r="D57" s="4">
@@ -4733,15 +4752,15 @@
         <v>124</v>
       </c>
       <c r="X57" t="str">
-        <f t="shared" si="1"/>
-        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (SEQ_TB_SAM_USUARIOS.NEXTVAL, 2, 'LUIS IGNACIO HERNANDEZ SANTIAGO', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'luis.ignacio', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
+        <f t="shared" si="2"/>
+        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (100696339, 2, 'LUIS IGNACIO HERNANDEZ SANTIAGO', 'NA', 'NA', 'luis.ignacio', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0)</v>
       </c>
     </row>
     <row r="58" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B58" s="2">
         <v>100854847</v>
       </c>
-      <c r="C58" s="2" t="s">
+      <c r="C58" s="5" t="s">
         <v>81</v>
       </c>
       <c r="D58" s="4">
@@ -4800,15 +4819,15 @@
         <v>124</v>
       </c>
       <c r="X58" t="str">
-        <f t="shared" si="1"/>
-        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (SEQ_TB_SAM_USUARIOS.NEXTVAL, 2, 'MIGUEL GONZALEZ MARTINEZ', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'miguel.gonzalez', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
+        <f t="shared" si="2"/>
+        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (100854847, 2, 'MIGUEL GONZALEZ MARTINEZ', 'NA', 'NA', 'miguel.gonzalez', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0)</v>
       </c>
     </row>
     <row r="59" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B59" s="2">
         <v>100854852</v>
       </c>
-      <c r="C59" s="2" t="s">
+      <c r="C59" s="7" t="s">
         <v>82</v>
       </c>
       <c r="D59" s="4">
@@ -4867,15 +4886,15 @@
         <v>124</v>
       </c>
       <c r="X59" t="str">
-        <f t="shared" si="1"/>
-        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (SEQ_TB_SAM_USUARIOS.NEXTVAL, 2, 'JOSE ANGEL GASPAR ANDRADE', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'jose.angel', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
+        <f t="shared" si="2"/>
+        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (100854852, 2, 'JOSE ANGEL GASPAR ANDRADE', 'NA', 'NA', 'jose.angel', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0)</v>
       </c>
     </row>
     <row r="60" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B60" s="2">
         <v>100854866</v>
       </c>
-      <c r="C60" s="2" t="s">
+      <c r="C60" s="7" t="s">
         <v>83</v>
       </c>
       <c r="D60" s="4">
@@ -4934,15 +4953,15 @@
         <v>124</v>
       </c>
       <c r="X60" t="str">
-        <f t="shared" si="1"/>
-        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (SEQ_TB_SAM_USUARIOS.NEXTVAL, 2, 'JOSE LUIS ZAVALA NAVARRO', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'jose.luis', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
+        <f t="shared" si="2"/>
+        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (100854866, 2, 'JOSE LUIS ZAVALA NAVARRO', 'NA', 'NA', 'jose.luis', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0)</v>
       </c>
     </row>
     <row r="61" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B61" s="2">
         <v>100861981</v>
       </c>
-      <c r="C61" s="2" t="s">
+      <c r="C61" s="5" t="s">
         <v>84</v>
       </c>
       <c r="D61" s="4">
@@ -4992,7 +5011,7 @@
         <v>laura.cecilia</v>
       </c>
       <c r="U61" t="s">
-        <v>182</v>
+        <v>194</v>
       </c>
       <c r="V61" s="3" t="s">
         <v>123</v>
@@ -5001,15 +5020,15 @@
         <v>124</v>
       </c>
       <c r="X61" t="str">
-        <f t="shared" si="1"/>
-        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (SEQ_TB_SAM_USUARIOS.NEXTVAL, 2, 'LAURA CECILIA HERNANDEZ FERREYRA', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'laura.cecilia', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
+        <f t="shared" si="2"/>
+        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (100861981, 2, 'LAURA CECILIA HERNANDEZ FERREYRA', 'NA', 'NA', 'laura.hernandez', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0)</v>
       </c>
     </row>
     <row r="62" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B62" s="2">
         <v>100861980</v>
       </c>
-      <c r="C62" s="2" t="s">
+      <c r="C62" s="5" t="s">
         <v>85</v>
       </c>
       <c r="D62" s="4">
@@ -5055,7 +5074,7 @@
         <v>adriana.valdovinos</v>
       </c>
       <c r="U62" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="V62" s="3" t="s">
         <v>123</v>
@@ -5064,15 +5083,15 @@
         <v>124</v>
       </c>
       <c r="X62" t="str">
-        <f t="shared" si="1"/>
-        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (SEQ_TB_SAM_USUARIOS.NEXTVAL, 2, 'ADRIANA VALDOVINOS MACIEL', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'adriana.valdovinos', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
+        <f t="shared" si="2"/>
+        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (100861980, 2, 'ADRIANA VALDOVINOS MACIEL', 'NA', 'NA', 'adriana.valdovinos', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0)</v>
       </c>
     </row>
     <row r="63" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B63" s="2">
         <v>100358833</v>
       </c>
-      <c r="C63" s="2" t="s">
+      <c r="C63" s="6" t="s">
         <v>86</v>
       </c>
       <c r="D63" s="4">
@@ -5120,7 +5139,7 @@
         <v>carlos.ivan</v>
       </c>
       <c r="U63" t="s">
-        <v>184</v>
+        <v>195</v>
       </c>
       <c r="V63" s="3" t="s">
         <v>123</v>
@@ -5129,15 +5148,15 @@
         <v>124</v>
       </c>
       <c r="X63" t="str">
-        <f t="shared" si="1"/>
-        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (SEQ_TB_SAM_USUARIOS.NEXTVAL, 2, 'CARLOS IVAN REVILLA FACIO', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'carlos.ivan', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
+        <f t="shared" si="2"/>
+        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (100358833, 2, 'CARLOS IVAN REVILLA FACIO', 'NA', 'NA', 'carlos.revilla', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0)</v>
       </c>
     </row>
     <row r="64" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B64" s="2">
         <v>100009612</v>
       </c>
-      <c r="C64" s="2" t="s">
+      <c r="C64" s="6" t="s">
         <v>87</v>
       </c>
       <c r="D64" s="4">
@@ -5181,7 +5200,7 @@
         <v>marina.josa</v>
       </c>
       <c r="U64" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="V64" s="3" t="s">
         <v>123</v>
@@ -5190,15 +5209,15 @@
         <v>124</v>
       </c>
       <c r="X64" t="str">
-        <f t="shared" si="1"/>
-        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (SEQ_TB_SAM_USUARIOS.NEXTVAL, 2, 'MARINA JOSA ALMELA', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'marina.josa', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
+        <f t="shared" si="2"/>
+        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (100009612, 2, 'MARINA JOSA ALMELA', 'NA', 'NA', 'marina.josa', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0)</v>
       </c>
     </row>
     <row r="65" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B65" s="2">
         <v>100327493</v>
       </c>
-      <c r="C65" s="2" t="s">
+      <c r="C65" s="6" t="s">
         <v>89</v>
       </c>
       <c r="D65" s="4">
@@ -5242,7 +5261,7 @@
         <v>luz.maria</v>
       </c>
       <c r="U65" t="s">
-        <v>186</v>
+        <v>196</v>
       </c>
       <c r="V65" s="3" t="s">
         <v>123</v>
@@ -5251,15 +5270,15 @@
         <v>124</v>
       </c>
       <c r="X65" t="str">
-        <f t="shared" si="1"/>
-        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (SEQ_TB_SAM_USUARIOS.NEXTVAL, 2, 'LUZ MARIA DE LA LUZ TELLES DIAZ', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'luz.maria', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
+        <f t="shared" si="2"/>
+        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (100327493, 2, 'LUZ MARIA DE LA LUZ TELLES DIAZ', 'NA', 'NA', 'luz.telles', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0)</v>
       </c>
     </row>
     <row r="66" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B66" s="2">
         <v>100348704</v>
       </c>
-      <c r="C66" s="2" t="s">
+      <c r="C66" s="5" t="s">
         <v>90</v>
       </c>
       <c r="D66" s="4">
@@ -5313,7 +5332,7 @@
         <v>gloria.paola</v>
       </c>
       <c r="U66" t="s">
-        <v>187</v>
+        <v>197</v>
       </c>
       <c r="V66" s="3" t="s">
         <v>123</v>
@@ -5322,15 +5341,15 @@
         <v>124</v>
       </c>
       <c r="X66" t="str">
-        <f t="shared" si="1"/>
-        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (SEQ_TB_SAM_USUARIOS.NEXTVAL, 2, 'GLORIA PAOLA FRAGOSO CONTRERAS', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'gloria.paola', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
+        <f t="shared" si="2"/>
+        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (100348704, 2, 'GLORIA PAOLA FRAGOSO CONTRERAS', 'NA', 'NA', 'gloria.fragoso', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0)</v>
       </c>
     </row>
     <row r="67" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B67" s="2">
         <v>100695304</v>
       </c>
-      <c r="C67" s="2" t="s">
+      <c r="C67" s="6" t="s">
         <v>91</v>
       </c>
       <c r="D67" s="4">
@@ -5374,7 +5393,7 @@
         <v>javier.vilchis</v>
       </c>
       <c r="U67" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="V67" s="3" t="s">
         <v>123</v>
@@ -5383,15 +5402,15 @@
         <v>124</v>
       </c>
       <c r="X67" t="str">
-        <f t="shared" si="1"/>
-        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (SEQ_TB_SAM_USUARIOS.NEXTVAL, 2, 'JAVIER VILCHIS GARCIA', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'javier.vilchis', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
+        <f t="shared" si="2"/>
+        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (100695304, 2, 'JAVIER VILCHIS GARCIA', 'NA', 'NA', 'javier.vilchis', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0)</v>
       </c>
     </row>
     <row r="68" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B68" s="2">
         <v>100980209</v>
       </c>
-      <c r="C68" s="2" t="s">
+      <c r="C68" s="5" t="s">
         <v>93</v>
       </c>
       <c r="D68" s="4">
@@ -5437,7 +5456,7 @@
         <v>juan.pablo</v>
       </c>
       <c r="U68" t="s">
-        <v>150</v>
+        <v>198</v>
       </c>
       <c r="V68" s="3" t="s">
         <v>123</v>
@@ -5446,15 +5465,15 @@
         <v>124</v>
       </c>
       <c r="X68" t="str">
-        <f t="shared" si="1"/>
-        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (SEQ_TB_SAM_USUARIOS.NEXTVAL, 2, 'JUAN PABLO OLIVERA CATRIP', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'juan.pablo', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
+        <f t="shared" si="2"/>
+        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (100980209, 2, 'JUAN PABLO OLIVERA CATRIP', 'NA', 'NA', 'juan.olvera', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0)</v>
       </c>
     </row>
     <row r="69" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B69" s="2">
         <v>100980197</v>
       </c>
-      <c r="C69" s="2" t="s">
+      <c r="C69" s="5" t="s">
         <v>94</v>
       </c>
       <c r="D69" s="4">
@@ -5496,11 +5515,11 @@
         <v>21</v>
       </c>
       <c r="T69" t="str">
-        <f t="shared" ref="T69:T92" si="2">LOWER(LEFT(C69,FIND(" ",C69)-1) &amp; "." &amp; MID(C69,FIND(" ",C69)+1,FIND(" ",C69,FIND(" ",C69)+1)-FIND(" ",C69)-1))</f>
+        <f t="shared" ref="T69:T92" si="3">LOWER(LEFT(C69,FIND(" ",C69)-1) &amp; "." &amp; MID(C69,FIND(" ",C69)+1,FIND(" ",C69,FIND(" ",C69)+1)-FIND(" ",C69)-1))</f>
         <v>sofia.ginebra</v>
       </c>
       <c r="U69" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="V69" s="3" t="s">
         <v>123</v>
@@ -5509,18 +5528,15 @@
         <v>124</v>
       </c>
       <c r="X69" t="str">
-        <f t="shared" ref="X69:X92" si="3">"INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,""PASSWORD"",CORREO,DIRECTOR) VALUES (" &amp;
-"SEQ_TB_SAM_USUARIOS.NEXTVAL, 2, '" &amp;
-SUBSTITUTE(C69,"'","''") &amp; "', 'MEX Prevencion de PLD', 'Contraloria Normativa', '" &amp;
-SUBSTITUTE(U69,"'","''") &amp; "', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);"</f>
-        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (SEQ_TB_SAM_USUARIOS.NEXTVAL, 2, 'SOFIA GINEBRA ZARANDONA', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'sofia.ginebra', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
+        <f t="shared" si="2"/>
+        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (100980197, 2, 'SOFIA GINEBRA ZARANDONA', 'NA', 'NA', 'sofia.ginebra', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0)</v>
       </c>
     </row>
     <row r="70" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B70" s="2">
         <v>100980202</v>
       </c>
-      <c r="C70" s="2" t="s">
+      <c r="C70" s="5" t="s">
         <v>95</v>
       </c>
       <c r="D70" s="4">
@@ -5562,28 +5578,28 @@
         <v>21</v>
       </c>
       <c r="T70" t="str">
+        <f t="shared" si="3"/>
+        <v>jesus.patricio</v>
+      </c>
+      <c r="U70" t="s">
+        <v>199</v>
+      </c>
+      <c r="V70" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="W70" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="X70" t="str">
         <f t="shared" si="2"/>
-        <v>jesus.patricio</v>
-      </c>
-      <c r="U70" t="s">
-        <v>190</v>
-      </c>
-      <c r="V70" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="W70" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="X70" t="str">
-        <f t="shared" si="3"/>
-        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (SEQ_TB_SAM_USUARIOS.NEXTVAL, 2, 'JESUS PATRICIO AVALOS DIAZ BARREIRO', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'jesus.patricio', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
+        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (100980202, 2, 'JESUS PATRICIO AVALOS DIAZ BARREIRO', 'NA', 'NA', 'jesus.avalos', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0)</v>
       </c>
     </row>
     <row r="71" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B71" s="2">
         <v>100980206</v>
       </c>
-      <c r="C71" s="2" t="s">
+      <c r="C71" s="5" t="s">
         <v>96</v>
       </c>
       <c r="D71" s="4">
@@ -5625,28 +5641,28 @@
         <v>21</v>
       </c>
       <c r="T71" t="str">
+        <f t="shared" si="3"/>
+        <v>mauricio.fabian</v>
+      </c>
+      <c r="U71" t="s">
+        <v>200</v>
+      </c>
+      <c r="V71" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="W71" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="X71" t="str">
         <f t="shared" si="2"/>
-        <v>mauricio.fabian</v>
-      </c>
-      <c r="U71" t="s">
-        <v>191</v>
-      </c>
-      <c r="V71" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="W71" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="X71" t="str">
-        <f t="shared" si="3"/>
-        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (SEQ_TB_SAM_USUARIOS.NEXTVAL, 2, 'MAURICIO FABIAN RODRIGUEZ JUAREZ', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'mauricio.fabian', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
+        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (100980206, 2, 'MAURICIO FABIAN RODRIGUEZ JUAREZ', 'NA', 'NA', 'mauricio.rodriguez', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0)</v>
       </c>
     </row>
     <row r="72" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B72" s="2">
         <v>100854856</v>
       </c>
-      <c r="C72" s="2" t="s">
+      <c r="C72" s="5" t="s">
         <v>97</v>
       </c>
       <c r="D72" s="4">
@@ -5694,28 +5710,28 @@
         <v>21</v>
       </c>
       <c r="T72" t="str">
+        <f t="shared" si="3"/>
+        <v>jose.juan</v>
+      </c>
+      <c r="U72" t="s">
+        <v>201</v>
+      </c>
+      <c r="V72" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="W72" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="X72" t="str">
         <f t="shared" si="2"/>
-        <v>jose.juan</v>
-      </c>
-      <c r="U72" t="s">
-        <v>192</v>
-      </c>
-      <c r="V72" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="W72" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="X72" t="str">
-        <f t="shared" si="3"/>
-        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (SEQ_TB_SAM_USUARIOS.NEXTVAL, 2, 'JOSE JUAN LOPEZ PIÑERO', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'jose.juan', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
+        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (100854856, 2, 'JOSE JUAN LOPEZ PIÑERO', 'NA', 'NA', 'jose.lopez', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0)</v>
       </c>
     </row>
     <row r="73" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B73" s="2">
         <v>100002387</v>
       </c>
-      <c r="C73" s="2" t="s">
+      <c r="C73" s="6" t="s">
         <v>99</v>
       </c>
       <c r="D73" s="4">
@@ -5761,28 +5777,28 @@
       </c>
       <c r="S73" s="3"/>
       <c r="T73" t="str">
+        <f t="shared" si="3"/>
+        <v>miguel.angel</v>
+      </c>
+      <c r="U73" t="s">
+        <v>202</v>
+      </c>
+      <c r="V73" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="W73" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="X73" t="str">
         <f t="shared" si="2"/>
-        <v>miguel.angel</v>
-      </c>
-      <c r="U73" t="s">
-        <v>193</v>
-      </c>
-      <c r="V73" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="W73" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="X73" t="str">
-        <f t="shared" si="3"/>
-        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (SEQ_TB_SAM_USUARIOS.NEXTVAL, 2, 'MIGUEL ANGEL CARO DEL CASTILLO TREVIÑO', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'miguel.angel', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
+        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (100002387, 2, 'MIGUEL ANGEL CARO DEL CASTILLO TREVIÑO', 'NA', 'NA', 'miguel.caro', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0)</v>
       </c>
     </row>
     <row r="74" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B74" s="2">
         <v>100003523</v>
       </c>
-      <c r="C74" s="2" t="s">
+      <c r="C74" s="6" t="s">
         <v>100</v>
       </c>
       <c r="D74" s="4">
@@ -5828,28 +5844,28 @@
       </c>
       <c r="S74" s="3"/>
       <c r="T74" t="str">
+        <f t="shared" si="3"/>
+        <v>oliver.igor</v>
+      </c>
+      <c r="U74" t="s">
+        <v>203</v>
+      </c>
+      <c r="V74" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="W74" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="X74" t="str">
         <f t="shared" si="2"/>
-        <v>oliver.igor</v>
-      </c>
-      <c r="U74" t="s">
-        <v>194</v>
-      </c>
-      <c r="V74" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="W74" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="X74" t="str">
-        <f t="shared" si="3"/>
-        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (SEQ_TB_SAM_USUARIOS.NEXTVAL, 2, 'OLIVER IGOR YAÑEZ GONZALEZ', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'oliver.igor', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
+        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (100003523, 2, 'OLIVER IGOR YAÑEZ GONZALEZ', 'NA', 'NA', 'oliver.yanez', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0)</v>
       </c>
     </row>
     <row r="75" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B75" s="2">
         <v>100008885</v>
       </c>
-      <c r="C75" s="2" t="s">
+      <c r="C75" s="6" t="s">
         <v>101</v>
       </c>
       <c r="D75" s="4">
@@ -5893,11 +5909,11 @@
       <c r="R75" s="3"/>
       <c r="S75" s="3"/>
       <c r="T75" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>maria.del</v>
       </c>
       <c r="U75" t="s">
-        <v>195</v>
+        <v>204</v>
       </c>
       <c r="V75" s="3" t="s">
         <v>123</v>
@@ -5906,15 +5922,18 @@
         <v>124</v>
       </c>
       <c r="X75" t="str">
-        <f t="shared" si="3"/>
-        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (SEQ_TB_SAM_USUARIOS.NEXTVAL, 2, 'MARIA DEL SOCORRO RAMIREZ RICARDEZ', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'maria.del', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
+        <f t="shared" ref="X75:X92" si="4">"INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,""PASSWORD"",CORREO,DIRECTOR) VALUES (" &amp;
+B75 &amp; ", 2, '" &amp;
+SUBSTITUTE(C75,"'","''") &amp; "', 'NA', 'NA', '" &amp;
+SUBSTITUTE(U75,"'","''") &amp; "', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0)"</f>
+        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (100008885, 2, 'MARIA DEL SOCORRO RAMIREZ RICARDEZ', 'NA', 'NA', 'maria.ramirez', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0)</v>
       </c>
     </row>
     <row r="76" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B76" s="2">
         <v>100009187</v>
       </c>
-      <c r="C76" s="2" t="s">
+      <c r="C76" s="6" t="s">
         <v>102</v>
       </c>
       <c r="D76" s="4">
@@ -5960,11 +5979,11 @@
       </c>
       <c r="S76" s="3"/>
       <c r="T76" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>mikhail.mora</v>
       </c>
       <c r="U76" t="s">
-        <v>196</v>
+        <v>186</v>
       </c>
       <c r="V76" s="3" t="s">
         <v>123</v>
@@ -5973,15 +5992,15 @@
         <v>124</v>
       </c>
       <c r="X76" t="str">
-        <f t="shared" si="3"/>
-        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (SEQ_TB_SAM_USUARIOS.NEXTVAL, 2, 'MIKHAIL MORA APONTE', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'mikhail.mora', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
+        <f t="shared" si="4"/>
+        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (100009187, 2, 'MIKHAIL MORA APONTE', 'NA', 'NA', 'mikhail.mora', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0)</v>
       </c>
     </row>
     <row r="77" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B77" s="2">
         <v>100396371</v>
       </c>
-      <c r="C77" s="2" t="s">
+      <c r="C77" s="6" t="s">
         <v>103</v>
       </c>
       <c r="D77" s="4">
@@ -6025,11 +6044,11 @@
       <c r="R77" s="3"/>
       <c r="S77" s="3"/>
       <c r="T77" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>brenda.daniela</v>
       </c>
       <c r="U77" t="s">
-        <v>197</v>
+        <v>205</v>
       </c>
       <c r="V77" s="3" t="s">
         <v>123</v>
@@ -6038,15 +6057,15 @@
         <v>124</v>
       </c>
       <c r="X77" t="str">
-        <f t="shared" si="3"/>
-        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (SEQ_TB_SAM_USUARIOS.NEXTVAL, 2, 'BRENDA DANIELA VELASCO ROJAS', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'brenda.daniela', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
+        <f t="shared" si="4"/>
+        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (100396371, 2, 'BRENDA DANIELA VELASCO ROJAS', 'NA', 'NA', 'brenda.velasco', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0)</v>
       </c>
     </row>
     <row r="78" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B78" s="2">
         <v>100539130</v>
       </c>
-      <c r="C78" s="2" t="s">
+      <c r="C78" s="6" t="s">
         <v>104</v>
       </c>
       <c r="D78" s="4">
@@ -6092,11 +6111,11 @@
       </c>
       <c r="S78" s="3"/>
       <c r="T78" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>elizandra.cardoso</v>
       </c>
       <c r="U78" t="s">
-        <v>198</v>
+        <v>187</v>
       </c>
       <c r="V78" s="3" t="s">
         <v>123</v>
@@ -6105,15 +6124,15 @@
         <v>124</v>
       </c>
       <c r="X78" t="str">
-        <f t="shared" si="3"/>
-        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (SEQ_TB_SAM_USUARIOS.NEXTVAL, 2, 'ELIZANDRA CARDOSO AZCOITIA', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'elizandra.cardoso', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
+        <f t="shared" si="4"/>
+        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (100539130, 2, 'ELIZANDRA CARDOSO AZCOITIA', 'NA', 'NA', 'elizandra.cardoso', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0)</v>
       </c>
     </row>
     <row r="79" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B79" s="2">
         <v>100018885</v>
       </c>
-      <c r="C79" s="2" t="s">
+      <c r="C79" s="6" t="s">
         <v>105</v>
       </c>
       <c r="D79" s="4">
@@ -6157,11 +6176,11 @@
       </c>
       <c r="S79" s="3"/>
       <c r="T79" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>juliana.perez</v>
       </c>
       <c r="U79" t="s">
-        <v>199</v>
+        <v>206</v>
       </c>
       <c r="V79" s="3" t="s">
         <v>123</v>
@@ -6170,15 +6189,15 @@
         <v>124</v>
       </c>
       <c r="X79" t="str">
-        <f t="shared" si="3"/>
-        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (SEQ_TB_SAM_USUARIOS.NEXTVAL, 2, 'JULIANA PEREZ MARTIN DEL CAMPO', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'juliana.perez', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
+        <f t="shared" si="4"/>
+        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (100018885, 2, 'JULIANA PEREZ MARTIN DEL CAMPO', 'NA', 'NA', 'juliana.martin', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0)</v>
       </c>
     </row>
     <row r="80" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B80" s="2">
         <v>100005847</v>
       </c>
-      <c r="C80" s="2" t="s">
+      <c r="C80" s="6" t="s">
         <v>107</v>
       </c>
       <c r="D80" s="4">
@@ -6218,11 +6237,11 @@
       <c r="R80" s="3"/>
       <c r="S80" s="3"/>
       <c r="T80" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>diego.martinez</v>
       </c>
       <c r="U80" t="s">
-        <v>200</v>
+        <v>188</v>
       </c>
       <c r="V80" s="3" t="s">
         <v>123</v>
@@ -6231,15 +6250,15 @@
         <v>124</v>
       </c>
       <c r="X80" t="str">
-        <f t="shared" si="3"/>
-        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (SEQ_TB_SAM_USUARIOS.NEXTVAL, 2, 'DIEGO MARTINEZ CORTES', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'diego.martinez', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
+        <f t="shared" si="4"/>
+        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (100005847, 2, 'DIEGO MARTINEZ CORTES', 'NA', 'NA', 'diego.martinez', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0)</v>
       </c>
     </row>
     <row r="81" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B81" s="2">
         <v>100018889</v>
       </c>
-      <c r="C81" s="2" t="s">
+      <c r="C81" s="6" t="s">
         <v>108</v>
       </c>
       <c r="D81" s="4"/>
@@ -6281,11 +6300,11 @@
       </c>
       <c r="S81" s="3"/>
       <c r="T81" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>yolanda.perdomo</v>
       </c>
       <c r="U81" t="s">
-        <v>201</v>
+        <v>189</v>
       </c>
       <c r="V81" s="3" t="s">
         <v>123</v>
@@ -6294,15 +6313,15 @@
         <v>124</v>
       </c>
       <c r="X81" t="str">
-        <f t="shared" si="3"/>
-        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (SEQ_TB_SAM_USUARIOS.NEXTVAL, 2, 'YOLANDA PERDOMO JIMENEZ', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'yolanda.perdomo', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
+        <f t="shared" si="4"/>
+        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (100018889, 2, 'YOLANDA PERDOMO JIMENEZ', 'NA', 'NA', 'yolanda.perdomo', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0)</v>
       </c>
     </row>
     <row r="82" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B82" s="2">
         <v>100546470</v>
       </c>
-      <c r="C82" s="2" t="s">
+      <c r="C82" s="6" t="s">
         <v>109</v>
       </c>
       <c r="D82" s="4">
@@ -6344,11 +6363,11 @@
       </c>
       <c r="S82" s="3"/>
       <c r="T82" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>mercedes.sanchez</v>
       </c>
       <c r="U82" t="s">
-        <v>202</v>
+        <v>190</v>
       </c>
       <c r="V82" s="3" t="s">
         <v>123</v>
@@ -6357,15 +6376,15 @@
         <v>124</v>
       </c>
       <c r="X82" t="str">
-        <f t="shared" si="3"/>
-        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (SEQ_TB_SAM_USUARIOS.NEXTVAL, 2, 'MERCEDES SANCHEZ REYES RETANA', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'mercedes.sanchez', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
+        <f t="shared" si="4"/>
+        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (100546470, 2, 'MERCEDES SANCHEZ REYES RETANA', 'NA', 'NA', 'mercedes.sanchez', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0)</v>
       </c>
     </row>
     <row r="83" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B83" s="2">
         <v>100550630</v>
       </c>
-      <c r="C83" s="2" t="s">
+      <c r="C83" s="6" t="s">
         <v>110</v>
       </c>
       <c r="D83" s="4">
@@ -6409,11 +6428,11 @@
       </c>
       <c r="S83" s="3"/>
       <c r="T83" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>alejandra.martinez</v>
       </c>
       <c r="U83" t="s">
-        <v>203</v>
+        <v>191</v>
       </c>
       <c r="V83" s="3" t="s">
         <v>123</v>
@@ -6422,15 +6441,15 @@
         <v>124</v>
       </c>
       <c r="X83" t="str">
-        <f t="shared" si="3"/>
-        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (SEQ_TB_SAM_USUARIOS.NEXTVAL, 2, 'ALEJANDRA MARTINEZ NIETO', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'alejandra.martinez', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
+        <f t="shared" si="4"/>
+        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (100550630, 2, 'ALEJANDRA MARTINEZ NIETO', 'NA', 'NA', 'alejandra.martinez', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0)</v>
       </c>
     </row>
     <row r="84" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B84" s="2">
         <v>100015156</v>
       </c>
-      <c r="C84" s="2" t="s">
+      <c r="C84" s="6" t="s">
         <v>111</v>
       </c>
       <c r="D84" s="4">
@@ -6478,11 +6497,11 @@
       </c>
       <c r="S84" s="3"/>
       <c r="T84" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>julian.gomez</v>
       </c>
       <c r="U84" t="s">
-        <v>204</v>
+        <v>192</v>
       </c>
       <c r="V84" s="3" t="s">
         <v>123</v>
@@ -6491,15 +6510,15 @@
         <v>124</v>
       </c>
       <c r="X84" t="str">
-        <f t="shared" si="3"/>
-        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (SEQ_TB_SAM_USUARIOS.NEXTVAL, 2, 'JULIAN GOMEZ FAUSTINO', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'julian.gomez', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
+        <f t="shared" si="4"/>
+        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (100015156, 2, 'JULIAN GOMEZ FAUSTINO', 'NA', 'NA', 'julian.gomez', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0)</v>
       </c>
     </row>
     <row r="85" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B85" s="2">
         <v>100019199</v>
       </c>
-      <c r="C85" s="2" t="s">
+      <c r="C85" s="6" t="s">
         <v>113</v>
       </c>
       <c r="D85" s="4">
@@ -6545,11 +6564,11 @@
       <c r="R85" s="3"/>
       <c r="S85" s="3"/>
       <c r="T85" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>cesar.alejandro</v>
       </c>
       <c r="U85" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="V85" s="3" t="s">
         <v>123</v>
@@ -6558,15 +6577,15 @@
         <v>124</v>
       </c>
       <c r="X85" t="str">
-        <f t="shared" si="3"/>
-        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (SEQ_TB_SAM_USUARIOS.NEXTVAL, 2, 'CESAR ALEJANDRO ARAIZA ITURRIA', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'cesar.alejandro', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
+        <f t="shared" si="4"/>
+        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (100019199, 2, 'CESAR ALEJANDRO ARAIZA ITURRIA', 'NA', 'NA', 'cesar.araiza', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0)</v>
       </c>
     </row>
     <row r="86" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B86" s="2">
         <v>100404799</v>
       </c>
-      <c r="C86" s="2" t="s">
+      <c r="C86" s="6" t="s">
         <v>114</v>
       </c>
       <c r="D86" s="4">
@@ -6612,11 +6631,11 @@
       <c r="R86" s="3"/>
       <c r="S86" s="3"/>
       <c r="T86" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>mariana.chavez</v>
       </c>
       <c r="U86" t="s">
-        <v>206</v>
+        <v>193</v>
       </c>
       <c r="V86" s="3" t="s">
         <v>123</v>
@@ -6625,15 +6644,15 @@
         <v>124</v>
       </c>
       <c r="X86" t="str">
-        <f t="shared" si="3"/>
-        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (SEQ_TB_SAM_USUARIOS.NEXTVAL, 2, 'MARIANA CHAVEZ GARCIA', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'mariana.chavez', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
+        <f t="shared" si="4"/>
+        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (100404799, 2, 'MARIANA CHAVEZ GARCIA', 'NA', 'NA', 'mariana.chavez', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0)</v>
       </c>
     </row>
     <row r="87" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B87" s="2">
         <v>100019201</v>
       </c>
-      <c r="C87" s="2" t="s">
+      <c r="C87" s="6" t="s">
         <v>115</v>
       </c>
       <c r="D87" s="4">
@@ -6679,11 +6698,11 @@
       <c r="R87" s="3"/>
       <c r="S87" s="3"/>
       <c r="T87" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>luis.alfonso</v>
       </c>
       <c r="U87" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="V87" s="3" t="s">
         <v>123</v>
@@ -6692,15 +6711,15 @@
         <v>124</v>
       </c>
       <c r="X87" t="str">
-        <f t="shared" si="3"/>
-        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (SEQ_TB_SAM_USUARIOS.NEXTVAL, 2, 'LUIS ALFONSO VILLEGAS MORENO', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'luis.alfonso', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
+        <f t="shared" si="4"/>
+        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (100019201, 2, 'LUIS ALFONSO VILLEGAS MORENO', 'NA', 'NA', 'luis.villegas', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0)</v>
       </c>
     </row>
     <row r="88" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B88" s="2">
         <v>100462092</v>
       </c>
-      <c r="C88" s="2" t="s">
+      <c r="C88" s="6" t="s">
         <v>116</v>
       </c>
       <c r="D88" s="4">
@@ -6746,11 +6765,11 @@
       <c r="R88" s="3"/>
       <c r="S88" s="3"/>
       <c r="T88" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>jesus.gabriel</v>
       </c>
       <c r="U88" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="V88" s="3" t="s">
         <v>123</v>
@@ -6759,15 +6778,15 @@
         <v>124</v>
       </c>
       <c r="X88" t="str">
-        <f t="shared" si="3"/>
-        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (SEQ_TB_SAM_USUARIOS.NEXTVAL, 2, 'JESUS GABRIEL SANCHEZ CANALES', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'jesus.gabriel', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
+        <f t="shared" si="4"/>
+        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (100462092, 2, 'JESUS GABRIEL SANCHEZ CANALES', 'NA', 'NA', 'jesus.sanchez', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0)</v>
       </c>
     </row>
     <row r="89" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B89" s="2">
         <v>100861987</v>
       </c>
-      <c r="C89" s="2" t="s">
+      <c r="C89" s="5" t="s">
         <v>117</v>
       </c>
       <c r="D89" s="4">
@@ -6815,11 +6834,11 @@
         <v>21</v>
       </c>
       <c r="T89" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>perla.cristina</v>
       </c>
       <c r="U89" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="V89" s="3" t="s">
         <v>123</v>
@@ -6828,15 +6847,15 @@
         <v>124</v>
       </c>
       <c r="X89" t="str">
-        <f t="shared" si="3"/>
-        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (SEQ_TB_SAM_USUARIOS.NEXTVAL, 2, 'PERLA CRISTINA GONZALEZ ESPINOSA', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'perla.cristina', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
+        <f t="shared" si="4"/>
+        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (100861987, 2, 'PERLA CRISTINA GONZALEZ ESPINOSA', 'NA', 'NA', 'perla.gonzalez', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0)</v>
       </c>
     </row>
     <row r="90" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B90" s="2">
         <v>100664282</v>
       </c>
-      <c r="C90" s="2" t="s">
+      <c r="C90" s="6" t="s">
         <v>118</v>
       </c>
       <c r="D90" s="4">
@@ -6882,11 +6901,11 @@
       <c r="R90" s="3"/>
       <c r="S90" s="3"/>
       <c r="T90" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>katerine.itzel</v>
       </c>
       <c r="U90" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="V90" s="3" t="s">
         <v>123</v>
@@ -6895,15 +6914,15 @@
         <v>124</v>
       </c>
       <c r="X90" t="str">
-        <f t="shared" si="3"/>
-        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (SEQ_TB_SAM_USUARIOS.NEXTVAL, 2, 'KATERINE ITZEL JIMENEZ MIGUEL', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'katerine.itzel', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
+        <f t="shared" si="4"/>
+        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (100664282, 2, 'KATERINE ITZEL JIMENEZ MIGUEL', 'NA', 'NA', 'katerine.jimenez', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0)</v>
       </c>
     </row>
     <row r="91" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B91" s="2">
         <v>100019224</v>
       </c>
-      <c r="C91" s="2" t="s">
+      <c r="C91" s="6" t="s">
         <v>119</v>
       </c>
       <c r="D91" s="4">
@@ -6943,11 +6962,11 @@
       <c r="R91" s="3"/>
       <c r="S91" s="3"/>
       <c r="T91" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>maria.del</v>
       </c>
       <c r="U91" t="s">
-        <v>195</v>
+        <v>212</v>
       </c>
       <c r="V91" s="3" t="s">
         <v>123</v>
@@ -6956,15 +6975,15 @@
         <v>124</v>
       </c>
       <c r="X91" t="str">
-        <f t="shared" si="3"/>
-        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (SEQ_TB_SAM_USUARIOS.NEXTVAL, 2, 'MARIA DEL PILAR CERRILLA NORIEGA', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'maria.del', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
+        <f t="shared" si="4"/>
+        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (100019224, 2, 'MARIA DEL PILAR CERRILLA NORIEGA', 'NA', 'NA', 'maria.cerrilla', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0)</v>
       </c>
     </row>
     <row r="92" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B92" s="2">
         <v>100561793</v>
       </c>
-      <c r="C92" s="2" t="s">
+      <c r="C92" s="6" t="s">
         <v>121</v>
       </c>
       <c r="D92" s="4">
@@ -7010,11 +7029,11 @@
       </c>
       <c r="S92" s="3"/>
       <c r="T92" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>francisco.jose</v>
       </c>
       <c r="U92" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="V92" s="3" t="s">
         <v>123</v>
@@ -7023,8 +7042,8 @@
         <v>124</v>
       </c>
       <c r="X92" t="str">
-        <f t="shared" si="3"/>
-        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (SEQ_TB_SAM_USUARIOS.NEXTVAL, 2, 'FRANCISCO JOSE BRUNET NAVARRETE', 'MEX Prevencion de PLD', 'Contraloria Normativa', 'francisco.jose', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0);</v>
+        <f t="shared" si="4"/>
+        <v>INSERT INTO tb_sam_usuarios_w (ID_USUARIO,ID_TIPOUSUARIO,NOMBRE,PUESTO,DEPARTAMENTO,USRLOCAL,FECHACREACION,HABILITADO,ID_AREA,"PASSWORD",CORREO,DIRECTOR) VALUES (100561793, 2, 'FRANCISCO JOSE BRUNET NAVARRETE', 'NA', 'NA', 'francisco.brunet', SYSDATE, 1, 1, 'SAM_RH', 'NA', 0)</v>
       </c>
     </row>
     <row r="93" spans="2:24" x14ac:dyDescent="0.25">
